--- a/public/sample-onboarding-import.xlsx
+++ b/public/sample-onboarding-import.xlsx
@@ -605,10 +605,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Rent</v>
+        <v>Health</v>
       </c>
       <c r="B7">
-        <v>28000</v>
+        <v>4500</v>
       </c>
       <c r="C7">
         <v>10</v>
@@ -617,7 +617,7 @@
         <v>2025</v>
       </c>
       <c r="E7">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F7" t="str">
         <v>Axis Salary Account</v>
@@ -725,10 +725,10 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Rent</v>
+        <v>Health</v>
       </c>
       <c r="B13">
-        <v>28000</v>
+        <v>4500</v>
       </c>
       <c r="C13">
         <v>11</v>
@@ -737,7 +737,7 @@
         <v>2025</v>
       </c>
       <c r="E13">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F13" t="str">
         <v>Axis Salary Account</v>
@@ -845,10 +845,10 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Rent</v>
+        <v>Health</v>
       </c>
       <c r="B19">
-        <v>28000</v>
+        <v>4500</v>
       </c>
       <c r="C19">
         <v>12</v>
@@ -857,7 +857,7 @@
         <v>2025</v>
       </c>
       <c r="E19">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F19" t="str">
         <v>Axis Salary Account</v>
@@ -965,10 +965,10 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Rent</v>
+        <v>Health</v>
       </c>
       <c r="B25">
-        <v>28000</v>
+        <v>4500</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -977,7 +977,7 @@
         <v>2026</v>
       </c>
       <c r="E25">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F25" t="str">
         <v>Axis Salary Account</v>
@@ -1085,10 +1085,10 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Rent</v>
+        <v>Health</v>
       </c>
       <c r="B31">
-        <v>28000</v>
+        <v>4500</v>
       </c>
       <c r="C31">
         <v>2</v>
@@ -1097,7 +1097,7 @@
         <v>2026</v>
       </c>
       <c r="E31">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F31" t="str">
         <v>Axis Salary Account</v>
@@ -1108,7 +1108,7 @@
         <v>Food</v>
       </c>
       <c r="B32">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="C32">
         <v>3</v>
@@ -1148,7 +1148,7 @@
         <v>Shopping</v>
       </c>
       <c r="B34">
-        <v>9000</v>
+        <v>11000</v>
       </c>
       <c r="C34">
         <v>3</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Rent</v>
+        <v>Health</v>
       </c>
       <c r="B37">
-        <v>28000</v>
+        <v>4500</v>
       </c>
       <c r="C37">
         <v>3</v>
@@ -1217,7 +1217,7 @@
         <v>2026</v>
       </c>
       <c r="E37">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F37" t="str">
         <v>Axis Salary Account</v>
@@ -1268,7 +1268,7 @@
         <v>350000</v>
       </c>
       <c r="C2">
-        <v>210000</v>
+        <v>225000</v>
       </c>
       <c r="D2" t="str">
         <v>2026-12-31</v>
@@ -1294,7 +1294,7 @@
         <v>180000</v>
       </c>
       <c r="C3">
-        <v>62000</v>
+        <v>76000</v>
       </c>
       <c r="D3" t="str">
         <v>2026-10-15</v>
@@ -1320,7 +1320,7 @@
         <v>140000</v>
       </c>
       <c r="C4">
-        <v>45000</v>
+        <v>52000</v>
       </c>
       <c r="D4" t="str">
         <v>2026-07-30</v>
@@ -1347,7 +1347,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J163"/>
+  <dimension ref="A1:J91"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1392,7 +1392,7 @@
         <v>98000</v>
       </c>
       <c r="D2" t="str">
-        <v>2025-10-01</v>
+        <v>2025-09-30</v>
       </c>
       <c r="E2" t="str">
         <v>Salary</v>
@@ -1418,31 +1418,31 @@
         <v>Axis Salary Account</v>
       </c>
       <c r="B3" t="str">
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="C3">
-        <v>28000</v>
+        <v>12000</v>
       </c>
       <c r="D3" t="str">
-        <v>2025-10-03</v>
+        <v>2025-10-17</v>
       </c>
       <c r="E3" t="str">
-        <v>Rent</v>
+        <v>Freelance</v>
       </c>
       <c r="F3" t="str">
         <v/>
       </c>
       <c r="G3" t="str">
-        <v>Sunrise Residency</v>
+        <v>Consulting Client</v>
       </c>
       <c r="H3" t="str">
-        <v>Monthly apartment rent</v>
+        <v>Side project payout</v>
       </c>
       <c r="I3" t="str">
-        <v>UPI</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="J3" t="str">
-        <v>housing,fixed</v>
+        <v>freelance,side-income</v>
       </c>
     </row>
     <row r="4">
@@ -1453,28 +1453,28 @@
         <v>Expense</v>
       </c>
       <c r="C4">
-        <v>3200</v>
+        <v>28000</v>
       </c>
       <c r="D4" t="str">
-        <v>2025-10-04</v>
+        <v>2025-10-02</v>
       </c>
       <c r="E4" t="str">
-        <v>Utilities</v>
+        <v>Rent</v>
       </c>
       <c r="F4" t="str">
         <v/>
       </c>
       <c r="G4" t="str">
-        <v>BESCOM</v>
+        <v>Sunrise Residency</v>
       </c>
       <c r="H4" t="str">
-        <v>Electricity bill</v>
+        <v>Monthly apartment rent</v>
       </c>
       <c r="I4" t="str">
-        <v>Net Banking</v>
+        <v>UPI</v>
       </c>
       <c r="J4" t="str">
-        <v>utilities,bill</v>
+        <v>housing,fixed</v>
       </c>
     </row>
     <row r="5">
@@ -1485,10 +1485,10 @@
         <v>Expense</v>
       </c>
       <c r="C5">
-        <v>1199</v>
+        <v>3200</v>
       </c>
       <c r="D5" t="str">
-        <v>2025-10-05</v>
+        <v>2025-10-03</v>
       </c>
       <c r="E5" t="str">
         <v>Utilities</v>
@@ -1497,16 +1497,16 @@
         <v/>
       </c>
       <c r="G5" t="str">
-        <v>Airtel Fiber</v>
+        <v>BESCOM</v>
       </c>
       <c r="H5" t="str">
-        <v>Internet payment</v>
+        <v>Electricity bill</v>
       </c>
       <c r="I5" t="str">
-        <v>UPI</v>
+        <v>Net Banking</v>
       </c>
       <c r="J5" t="str">
-        <v>internet,utility</v>
+        <v>utilities,bill</v>
       </c>
     </row>
     <row r="6">
@@ -1517,28 +1517,28 @@
         <v>Expense</v>
       </c>
       <c r="C6">
-        <v>4800</v>
+        <v>1199</v>
       </c>
       <c r="D6" t="str">
-        <v>2025-10-06</v>
+        <v>2025-10-04</v>
       </c>
       <c r="E6" t="str">
-        <v>Food</v>
+        <v>Utilities</v>
       </c>
       <c r="F6" t="str">
         <v/>
       </c>
       <c r="G6" t="str">
-        <v>BigBasket</v>
+        <v>Airtel Fiber</v>
       </c>
       <c r="H6" t="str">
-        <v>Groceries stock-up</v>
+        <v>Internet payment</v>
       </c>
       <c r="I6" t="str">
-        <v>Card</v>
+        <v>UPI</v>
       </c>
       <c r="J6" t="str">
-        <v>groceries,home</v>
+        <v>internet,utility</v>
       </c>
     </row>
     <row r="7">
@@ -1549,28 +1549,28 @@
         <v>Expense</v>
       </c>
       <c r="C7">
-        <v>420</v>
+        <v>4700</v>
       </c>
       <c r="D7" t="str">
-        <v>2025-10-07</v>
+        <v>2025-10-05</v>
       </c>
       <c r="E7" t="str">
-        <v>Transport</v>
+        <v>Food</v>
       </c>
       <c r="F7" t="str">
         <v/>
       </c>
       <c r="G7" t="str">
-        <v>Uber</v>
+        <v>BigBasket</v>
       </c>
       <c r="H7" t="str">
-        <v>Office commute</v>
+        <v>Groceries stock-up</v>
       </c>
       <c r="I7" t="str">
-        <v>UPI</v>
+        <v>Card</v>
       </c>
       <c r="J7" t="str">
-        <v>commute,cab</v>
+        <v>groceries,home</v>
       </c>
     </row>
     <row r="8">
@@ -1578,31 +1578,31 @@
         <v>Axis Salary Account</v>
       </c>
       <c r="B8" t="str">
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="C8">
-        <v>12500</v>
+        <v>2400</v>
       </c>
       <c r="D8" t="str">
-        <v>2025-10-08</v>
+        <v>2025-10-11</v>
       </c>
       <c r="E8" t="str">
-        <v>Freelance</v>
+        <v>Food</v>
       </c>
       <c r="F8" t="str">
         <v/>
       </c>
       <c r="G8" t="str">
-        <v>Product Design Client</v>
+        <v>Swiggy</v>
       </c>
       <c r="H8" t="str">
-        <v>Freelance milestone payment</v>
+        <v>Dining and delivery</v>
       </c>
       <c r="I8" t="str">
-        <v>Bank Transfer</v>
+        <v>UPI</v>
       </c>
       <c r="J8" t="str">
-        <v>freelance,design</v>
+        <v>food,lifestyle</v>
       </c>
     </row>
     <row r="9">
@@ -1610,63 +1610,63 @@
         <v>Axis Salary Account</v>
       </c>
       <c r="B9" t="str">
-        <v>Transfer</v>
+        <v>Expense</v>
       </c>
       <c r="C9">
-        <v>3500</v>
+        <v>3100</v>
       </c>
       <c r="D9" t="str">
-        <v>2025-10-09</v>
+        <v>2025-10-08</v>
       </c>
       <c r="E9" t="str">
-        <v/>
+        <v>Transport</v>
       </c>
       <c r="F9" t="str">
-        <v>Cash Wallet</v>
+        <v/>
       </c>
       <c r="G9" t="str">
-        <v>ATM Withdrawal</v>
+        <v>Uber</v>
       </c>
       <c r="H9" t="str">
-        <v>Wallet cash top-up</v>
+        <v>Office commute</v>
       </c>
       <c r="I9" t="str">
-        <v>Transfer</v>
+        <v>UPI</v>
       </c>
       <c r="J9" t="str">
-        <v>cash,transfer</v>
+        <v>transport,commute</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Cash Wallet</v>
+        <v>HDFC Rewards Card</v>
       </c>
       <c r="B10" t="str">
         <v>Expense</v>
       </c>
       <c r="C10">
-        <v>240</v>
+        <v>1800</v>
       </c>
       <c r="D10" t="str">
-        <v>2025-10-10</v>
+        <v>2025-10-13</v>
       </c>
       <c r="E10" t="str">
-        <v>Transport</v>
+        <v>Shopping</v>
       </c>
       <c r="F10" t="str">
         <v/>
       </c>
       <c r="G10" t="str">
-        <v>Auto Rickshaw</v>
+        <v>Amazon</v>
       </c>
       <c r="H10" t="str">
-        <v>Local commute</v>
+        <v>Shopping order</v>
       </c>
       <c r="I10" t="str">
-        <v>Cash</v>
+        <v>Card</v>
       </c>
       <c r="J10" t="str">
-        <v>local,transport</v>
+        <v>shopping,online</v>
       </c>
     </row>
     <row r="11">
@@ -1677,28 +1677,28 @@
         <v>Expense</v>
       </c>
       <c r="C11">
-        <v>2199</v>
+        <v>1700</v>
       </c>
       <c r="D11" t="str">
-        <v>2025-10-11</v>
+        <v>2025-10-19</v>
       </c>
       <c r="E11" t="str">
-        <v>Shopping</v>
+        <v>Entertainment</v>
       </c>
       <c r="F11" t="str">
         <v/>
       </c>
       <c r="G11" t="str">
-        <v>Amazon</v>
+        <v>BookMyShow</v>
       </c>
       <c r="H11" t="str">
-        <v>Home office accessories</v>
+        <v>Weekend entertainment</v>
       </c>
       <c r="I11" t="str">
-        <v>Credit Card</v>
+        <v>Card</v>
       </c>
       <c r="J11" t="str">
-        <v>shopping,office</v>
+        <v>fun,weekend</v>
       </c>
     </row>
     <row r="12">
@@ -1709,60 +1709,60 @@
         <v>Expense</v>
       </c>
       <c r="C12">
-        <v>950</v>
+        <v>900</v>
       </c>
       <c r="D12" t="str">
-        <v>2025-10-12</v>
+        <v>2025-10-21</v>
       </c>
       <c r="E12" t="str">
-        <v>Food</v>
+        <v>Health</v>
       </c>
       <c r="F12" t="str">
         <v/>
       </c>
       <c r="G12" t="str">
-        <v>Swiggy</v>
+        <v>Apollo Pharmacy</v>
       </c>
       <c r="H12" t="str">
-        <v>Late dinner order</v>
+        <v>Health and pharmacy</v>
       </c>
       <c r="I12" t="str">
         <v>UPI</v>
       </c>
       <c r="J12" t="str">
-        <v>food,delivery</v>
+        <v>health,care</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>Axis Salary Account</v>
       </c>
       <c r="B13" t="str">
-        <v>Expense</v>
+        <v>Transfer</v>
       </c>
       <c r="C13">
-        <v>499</v>
+        <v>17000</v>
       </c>
       <c r="D13" t="str">
-        <v>2025-10-13</v>
+        <v>2025-10-06</v>
       </c>
       <c r="E13" t="str">
-        <v>Entertainment</v>
+        <v/>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>Emergency Savings</v>
       </c>
       <c r="G13" t="str">
-        <v>Netflix</v>
+        <v>Self Transfer</v>
       </c>
       <c r="H13" t="str">
-        <v>Monthly subscription</v>
+        <v>Move to emergency fund</v>
       </c>
       <c r="I13" t="str">
-        <v>Credit Card</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="J13" t="str">
-        <v>subscription,ott</v>
+        <v>saving,transfer</v>
       </c>
     </row>
     <row r="14">
@@ -1770,31 +1770,31 @@
         <v>Axis Salary Account</v>
       </c>
       <c r="B14" t="str">
-        <v>Expense</v>
+        <v>Transfer</v>
       </c>
       <c r="C14">
-        <v>680</v>
+        <v>3500</v>
       </c>
       <c r="D14" t="str">
-        <v>2025-10-14</v>
+        <v>2025-10-23</v>
       </c>
       <c r="E14" t="str">
-        <v>Transport</v>
+        <v/>
       </c>
       <c r="F14" t="str">
-        <v/>
+        <v>Cash Wallet</v>
       </c>
       <c r="G14" t="str">
-        <v>Metro Card</v>
+        <v>Self Transfer</v>
       </c>
       <c r="H14" t="str">
-        <v>Recharge</v>
+        <v>Save for Japan trip</v>
       </c>
       <c r="I14" t="str">
-        <v>UPI</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="J14" t="str">
-        <v>metro,commute</v>
+        <v>goal,travel</v>
       </c>
     </row>
     <row r="15">
@@ -1805,42 +1805,42 @@
         <v>Expense</v>
       </c>
       <c r="C15">
-        <v>2750</v>
+        <v>2500</v>
       </c>
       <c r="D15" t="str">
-        <v>2025-10-15</v>
+        <v>2025-10-07</v>
       </c>
       <c r="E15" t="str">
-        <v>Food</v>
+        <v>Transport</v>
       </c>
       <c r="F15" t="str">
         <v/>
       </c>
       <c r="G15" t="str">
-        <v>Reliance Fresh</v>
+        <v>ATM Withdrawal</v>
       </c>
       <c r="H15" t="str">
-        <v>Mid-month groceries</v>
+        <v>Cash for local expenses</v>
       </c>
       <c r="I15" t="str">
-        <v>Card</v>
+        <v>ATM</v>
       </c>
       <c r="J15" t="str">
-        <v>groceries,weekly</v>
+        <v>cash,atm</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>Axis Salary Account</v>
       </c>
       <c r="B16" t="str">
         <v>Expense</v>
       </c>
       <c r="C16">
-        <v>1899</v>
+        <v>6200</v>
       </c>
       <c r="D16" t="str">
-        <v>2025-10-16</v>
+        <v>2025-10-25</v>
       </c>
       <c r="E16" t="str">
         <v>Shopping</v>
@@ -1849,48 +1849,48 @@
         <v/>
       </c>
       <c r="G16" t="str">
-        <v>Myntra</v>
+        <v>HDFC Card Payment</v>
       </c>
       <c r="H16" t="str">
-        <v>Clothing order</v>
+        <v>Credit card bill payment</v>
       </c>
       <c r="I16" t="str">
-        <v>Credit Card</v>
+        <v>Net Banking</v>
       </c>
       <c r="J16" t="str">
-        <v>shopping,fashion</v>
+        <v>card,bill</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Cash Wallet</v>
+        <v>Axis Salary Account</v>
       </c>
       <c r="B17" t="str">
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="C17">
-        <v>160</v>
+        <v>99500</v>
       </c>
       <c r="D17" t="str">
-        <v>2025-10-17</v>
+        <v>2025-10-31</v>
       </c>
       <c r="E17" t="str">
-        <v>Food</v>
+        <v>Salary</v>
       </c>
       <c r="F17" t="str">
         <v/>
       </c>
       <c r="G17" t="str">
-        <v>Tea Point</v>
+        <v>Employer Payroll</v>
       </c>
       <c r="H17" t="str">
-        <v>Snacks and tea</v>
+        <v>Monthly salary credit</v>
       </c>
       <c r="I17" t="str">
-        <v>Cash</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="J17" t="str">
-        <v>snacks,cash</v>
+        <v>salary,monthly</v>
       </c>
     </row>
     <row r="18">
@@ -1901,28 +1901,28 @@
         <v>Expense</v>
       </c>
       <c r="C18">
-        <v>1450</v>
+        <v>28000</v>
       </c>
       <c r="D18" t="str">
-        <v>2025-10-18</v>
+        <v>2025-11-02</v>
       </c>
       <c r="E18" t="str">
-        <v>Utilities</v>
+        <v>Rent</v>
       </c>
       <c r="F18" t="str">
         <v/>
       </c>
       <c r="G18" t="str">
-        <v>Jio Mobile</v>
+        <v>Sunrise Residency</v>
       </c>
       <c r="H18" t="str">
-        <v>Mobile recharge and add-ons</v>
+        <v>Monthly apartment rent</v>
       </c>
       <c r="I18" t="str">
         <v>UPI</v>
       </c>
       <c r="J18" t="str">
-        <v>mobile,utility</v>
+        <v>housing,fixed</v>
       </c>
     </row>
     <row r="19">
@@ -1930,63 +1930,63 @@
         <v>Axis Salary Account</v>
       </c>
       <c r="B19" t="str">
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="C19">
-        <v>6000</v>
+        <v>3290</v>
       </c>
       <c r="D19" t="str">
-        <v>2025-10-19</v>
+        <v>2025-11-03</v>
       </c>
       <c r="E19" t="str">
-        <v>Others</v>
+        <v>Utilities</v>
       </c>
       <c r="F19" t="str">
         <v/>
       </c>
       <c r="G19" t="str">
-        <v>Cashback + Refunds</v>
+        <v>BESCOM</v>
       </c>
       <c r="H19" t="str">
-        <v>Credit card cashback and vendor refund</v>
+        <v>Electricity bill</v>
       </c>
       <c r="I19" t="str">
-        <v>Bank Transfer</v>
+        <v>Net Banking</v>
       </c>
       <c r="J19" t="str">
-        <v>refund,cashback</v>
+        <v>utilities,bill</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>Axis Salary Account</v>
       </c>
       <c r="B20" t="str">
         <v>Expense</v>
       </c>
       <c r="C20">
-        <v>899</v>
+        <v>1199</v>
       </c>
       <c r="D20" t="str">
-        <v>2025-10-20</v>
+        <v>2025-11-04</v>
       </c>
       <c r="E20" t="str">
-        <v>Entertainment</v>
+        <v>Utilities</v>
       </c>
       <c r="F20" t="str">
         <v/>
       </c>
       <c r="G20" t="str">
-        <v>PVR Cinemas</v>
+        <v>Airtel Fiber</v>
       </c>
       <c r="H20" t="str">
-        <v>Weekend movie</v>
+        <v>Internet payment</v>
       </c>
       <c r="I20" t="str">
-        <v>Credit Card</v>
+        <v>UPI</v>
       </c>
       <c r="J20" t="str">
-        <v>movie,leisure</v>
+        <v>internet,utility</v>
       </c>
     </row>
     <row r="21">
@@ -1997,28 +1997,28 @@
         <v>Expense</v>
       </c>
       <c r="C21">
-        <v>2100</v>
+        <v>4950</v>
       </c>
       <c r="D21" t="str">
-        <v>2025-10-21</v>
+        <v>2025-11-05</v>
       </c>
       <c r="E21" t="str">
-        <v>Transport</v>
+        <v>Food</v>
       </c>
       <c r="F21" t="str">
         <v/>
       </c>
       <c r="G21" t="str">
-        <v>Indian Oil</v>
+        <v>BigBasket</v>
       </c>
       <c r="H21" t="str">
-        <v>Fuel refill</v>
+        <v>Groceries stock-up</v>
       </c>
       <c r="I21" t="str">
         <v>Card</v>
       </c>
       <c r="J21" t="str">
-        <v>fuel,car</v>
+        <v>groceries,home</v>
       </c>
     </row>
     <row r="22">
@@ -2029,10 +2029,10 @@
         <v>Expense</v>
       </c>
       <c r="C22">
-        <v>3900</v>
+        <v>2560</v>
       </c>
       <c r="D22" t="str">
-        <v>2025-10-22</v>
+        <v>2025-11-11</v>
       </c>
       <c r="E22" t="str">
         <v>Food</v>
@@ -2041,16 +2041,16 @@
         <v/>
       </c>
       <c r="G22" t="str">
-        <v>DMart</v>
+        <v>Swiggy</v>
       </c>
       <c r="H22" t="str">
-        <v>Household and groceries</v>
+        <v>Dining and delivery</v>
       </c>
       <c r="I22" t="str">
-        <v>Card</v>
+        <v>UPI</v>
       </c>
       <c r="J22" t="str">
-        <v>groceries,household</v>
+        <v>food,lifestyle</v>
       </c>
     </row>
     <row r="23">
@@ -2058,63 +2058,63 @@
         <v>Axis Salary Account</v>
       </c>
       <c r="B23" t="str">
-        <v>Transfer</v>
+        <v>Expense</v>
       </c>
       <c r="C23">
-        <v>15000</v>
+        <v>3280</v>
       </c>
       <c r="D23" t="str">
-        <v>2025-10-23</v>
+        <v>2025-11-08</v>
       </c>
       <c r="E23" t="str">
-        <v/>
+        <v>Transport</v>
       </c>
       <c r="F23" t="str">
-        <v>Emergency Savings</v>
+        <v/>
       </c>
       <c r="G23" t="str">
-        <v>Savings Sweep</v>
+        <v>Uber</v>
       </c>
       <c r="H23" t="str">
-        <v>Move surplus into emergency savings</v>
+        <v>Office commute</v>
       </c>
       <c r="I23" t="str">
-        <v>Transfer</v>
+        <v>UPI</v>
       </c>
       <c r="J23" t="str">
-        <v>savings,transfer</v>
+        <v>transport,commute</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Emergency Savings</v>
+        <v>HDFC Rewards Card</v>
       </c>
       <c r="B24" t="str">
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="C24">
-        <v>950</v>
+        <v>1940</v>
       </c>
       <c r="D24" t="str">
-        <v>2025-10-24</v>
+        <v>2025-11-13</v>
       </c>
       <c r="E24" t="str">
-        <v>Others</v>
+        <v>Shopping</v>
       </c>
       <c r="F24" t="str">
         <v/>
       </c>
       <c r="G24" t="str">
-        <v>Interest Credit</v>
+        <v>Amazon</v>
       </c>
       <c r="H24" t="str">
-        <v>Monthly interest credit</v>
+        <v>Shopping order</v>
       </c>
       <c r="I24" t="str">
-        <v>Bank Transfer</v>
+        <v>Card</v>
       </c>
       <c r="J24" t="str">
-        <v>interest,savings</v>
+        <v>shopping,online</v>
       </c>
     </row>
     <row r="25">
@@ -2125,28 +2125,28 @@
         <v>Expense</v>
       </c>
       <c r="C25">
-        <v>1799</v>
+        <v>1830</v>
       </c>
       <c r="D25" t="str">
-        <v>2025-10-25</v>
+        <v>2025-11-19</v>
       </c>
       <c r="E25" t="str">
-        <v>Shopping</v>
+        <v>Entertainment</v>
       </c>
       <c r="F25" t="str">
         <v/>
       </c>
       <c r="G25" t="str">
-        <v>Croma</v>
+        <v>BookMyShow</v>
       </c>
       <c r="H25" t="str">
-        <v>Electronics accessories</v>
+        <v>Weekend entertainment</v>
       </c>
       <c r="I25" t="str">
-        <v>Credit Card</v>
+        <v>Card</v>
       </c>
       <c r="J25" t="str">
-        <v>electronics,shopping</v>
+        <v>fun,weekend</v>
       </c>
     </row>
     <row r="26">
@@ -2157,60 +2157,60 @@
         <v>Expense</v>
       </c>
       <c r="C26">
-        <v>720</v>
+        <v>980</v>
       </c>
       <c r="D26" t="str">
-        <v>2025-10-26</v>
+        <v>2025-11-21</v>
       </c>
       <c r="E26" t="str">
-        <v>Food</v>
+        <v>Health</v>
       </c>
       <c r="F26" t="str">
         <v/>
       </c>
       <c r="G26" t="str">
-        <v>Cafe Coffee Day</v>
+        <v>Apollo Pharmacy</v>
       </c>
       <c r="H26" t="str">
-        <v>Client catch-up</v>
+        <v>Health and pharmacy</v>
       </c>
       <c r="I26" t="str">
         <v>UPI</v>
       </c>
       <c r="J26" t="str">
-        <v>coffee,meeting</v>
+        <v>health,care</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Cash Wallet</v>
+        <v>Axis Salary Account</v>
       </c>
       <c r="B27" t="str">
-        <v>Expense</v>
+        <v>Transfer</v>
       </c>
       <c r="C27">
-        <v>310</v>
+        <v>18000</v>
       </c>
       <c r="D27" t="str">
-        <v>2025-10-27</v>
+        <v>2025-11-06</v>
       </c>
       <c r="E27" t="str">
-        <v>Food</v>
+        <v/>
       </c>
       <c r="F27" t="str">
-        <v/>
+        <v>Emergency Savings</v>
       </c>
       <c r="G27" t="str">
-        <v>Street Food</v>
+        <v>Self Transfer</v>
       </c>
       <c r="H27" t="str">
-        <v>Quick dinner</v>
+        <v>Move to emergency fund</v>
       </c>
       <c r="I27" t="str">
-        <v>Cash</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="J27" t="str">
-        <v>food,cash</v>
+        <v>saving,transfer</v>
       </c>
     </row>
     <row r="28">
@@ -2218,31 +2218,31 @@
         <v>Axis Salary Account</v>
       </c>
       <c r="B28" t="str">
-        <v>Expense</v>
+        <v>Transfer</v>
       </c>
       <c r="C28">
-        <v>1600</v>
+        <v>4000</v>
       </c>
       <c r="D28" t="str">
-        <v>2025-10-28</v>
+        <v>2025-11-23</v>
       </c>
       <c r="E28" t="str">
-        <v>Utilities</v>
+        <v/>
       </c>
       <c r="F28" t="str">
-        <v/>
+        <v>Cash Wallet</v>
       </c>
       <c r="G28" t="str">
-        <v>Health Insurance</v>
+        <v>Self Transfer</v>
       </c>
       <c r="H28" t="str">
-        <v>Insurance auto debit</v>
+        <v>Save for Japan trip</v>
       </c>
       <c r="I28" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="J28" t="str">
-        <v>insurance,health</v>
+        <v>goal,travel</v>
       </c>
     </row>
     <row r="29">
@@ -2250,31 +2250,31 @@
         <v>Axis Salary Account</v>
       </c>
       <c r="B29" t="str">
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="C29">
-        <v>98000</v>
+        <v>2500</v>
       </c>
       <c r="D29" t="str">
-        <v>2025-11-01</v>
+        <v>2025-11-07</v>
       </c>
       <c r="E29" t="str">
-        <v>Salary</v>
+        <v>Transport</v>
       </c>
       <c r="F29" t="str">
         <v/>
       </c>
       <c r="G29" t="str">
-        <v>Employer Payroll</v>
+        <v>ATM Withdrawal</v>
       </c>
       <c r="H29" t="str">
-        <v>Monthly salary credit</v>
+        <v>Cash for local expenses</v>
       </c>
       <c r="I29" t="str">
-        <v>Bank Transfer</v>
+        <v>ATM</v>
       </c>
       <c r="J29" t="str">
-        <v>salary,monthly</v>
+        <v>cash,atm</v>
       </c>
     </row>
     <row r="30">
@@ -2285,28 +2285,28 @@
         <v>Expense</v>
       </c>
       <c r="C30">
-        <v>28000</v>
+        <v>6600</v>
       </c>
       <c r="D30" t="str">
-        <v>2025-11-03</v>
+        <v>2025-11-25</v>
       </c>
       <c r="E30" t="str">
-        <v>Rent</v>
+        <v>Shopping</v>
       </c>
       <c r="F30" t="str">
         <v/>
       </c>
       <c r="G30" t="str">
-        <v>Sunrise Residency</v>
+        <v>HDFC Card Payment</v>
       </c>
       <c r="H30" t="str">
-        <v>Monthly apartment rent</v>
+        <v>Credit card bill payment</v>
       </c>
       <c r="I30" t="str">
-        <v>UPI</v>
+        <v>Net Banking</v>
       </c>
       <c r="J30" t="str">
-        <v>housing,fixed</v>
+        <v>card,bill</v>
       </c>
     </row>
     <row r="31">
@@ -2314,31 +2314,31 @@
         <v>Axis Salary Account</v>
       </c>
       <c r="B31" t="str">
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="C31">
-        <v>3200</v>
+        <v>101000</v>
       </c>
       <c r="D31" t="str">
-        <v>2025-11-04</v>
+        <v>2025-11-30</v>
       </c>
       <c r="E31" t="str">
-        <v>Utilities</v>
+        <v>Salary</v>
       </c>
       <c r="F31" t="str">
         <v/>
       </c>
       <c r="G31" t="str">
-        <v>BESCOM</v>
+        <v>Employer Payroll</v>
       </c>
       <c r="H31" t="str">
-        <v>Electricity bill</v>
+        <v>Monthly salary credit</v>
       </c>
       <c r="I31" t="str">
-        <v>Net Banking</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="J31" t="str">
-        <v>utilities,bill</v>
+        <v>salary,monthly</v>
       </c>
     </row>
     <row r="32">
@@ -2346,31 +2346,31 @@
         <v>Axis Salary Account</v>
       </c>
       <c r="B32" t="str">
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="C32">
-        <v>1199</v>
+        <v>13200</v>
       </c>
       <c r="D32" t="str">
-        <v>2025-11-05</v>
+        <v>2025-12-17</v>
       </c>
       <c r="E32" t="str">
-        <v>Utilities</v>
+        <v>Freelance</v>
       </c>
       <c r="F32" t="str">
         <v/>
       </c>
       <c r="G32" t="str">
-        <v>Airtel Fiber</v>
+        <v>Consulting Client</v>
       </c>
       <c r="H32" t="str">
-        <v>Internet payment</v>
+        <v>Side project payout</v>
       </c>
       <c r="I32" t="str">
-        <v>UPI</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="J32" t="str">
-        <v>internet,utility</v>
+        <v>freelance,side-income</v>
       </c>
     </row>
     <row r="33">
@@ -2381,28 +2381,28 @@
         <v>Expense</v>
       </c>
       <c r="C33">
-        <v>4800</v>
+        <v>28000</v>
       </c>
       <c r="D33" t="str">
-        <v>2025-11-06</v>
+        <v>2025-12-02</v>
       </c>
       <c r="E33" t="str">
-        <v>Food</v>
+        <v>Rent</v>
       </c>
       <c r="F33" t="str">
         <v/>
       </c>
       <c r="G33" t="str">
-        <v>BigBasket</v>
+        <v>Sunrise Residency</v>
       </c>
       <c r="H33" t="str">
-        <v>Groceries stock-up</v>
+        <v>Monthly apartment rent</v>
       </c>
       <c r="I33" t="str">
-        <v>Card</v>
+        <v>UPI</v>
       </c>
       <c r="J33" t="str">
-        <v>groceries,home</v>
+        <v>housing,fixed</v>
       </c>
     </row>
     <row r="34">
@@ -2413,28 +2413,28 @@
         <v>Expense</v>
       </c>
       <c r="C34">
-        <v>420</v>
+        <v>3380</v>
       </c>
       <c r="D34" t="str">
-        <v>2025-11-07</v>
+        <v>2025-12-03</v>
       </c>
       <c r="E34" t="str">
-        <v>Transport</v>
+        <v>Utilities</v>
       </c>
       <c r="F34" t="str">
         <v/>
       </c>
       <c r="G34" t="str">
-        <v>Uber</v>
+        <v>BESCOM</v>
       </c>
       <c r="H34" t="str">
-        <v>Office commute</v>
+        <v>Electricity bill</v>
       </c>
       <c r="I34" t="str">
-        <v>UPI</v>
+        <v>Net Banking</v>
       </c>
       <c r="J34" t="str">
-        <v>commute,cab</v>
+        <v>utilities,bill</v>
       </c>
     </row>
     <row r="35">
@@ -2442,31 +2442,31 @@
         <v>Axis Salary Account</v>
       </c>
       <c r="B35" t="str">
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="C35">
-        <v>12500</v>
+        <v>1199</v>
       </c>
       <c r="D35" t="str">
-        <v>2025-11-08</v>
+        <v>2025-12-04</v>
       </c>
       <c r="E35" t="str">
-        <v>Freelance</v>
+        <v>Utilities</v>
       </c>
       <c r="F35" t="str">
         <v/>
       </c>
       <c r="G35" t="str">
-        <v>Product Design Client</v>
+        <v>Airtel Fiber</v>
       </c>
       <c r="H35" t="str">
-        <v>Freelance milestone payment</v>
+        <v>Internet payment</v>
       </c>
       <c r="I35" t="str">
-        <v>Bank Transfer</v>
+        <v>UPI</v>
       </c>
       <c r="J35" t="str">
-        <v>freelance,design</v>
+        <v>internet,utility</v>
       </c>
     </row>
     <row r="36">
@@ -2474,127 +2474,127 @@
         <v>Axis Salary Account</v>
       </c>
       <c r="B36" t="str">
-        <v>Transfer</v>
+        <v>Expense</v>
       </c>
       <c r="C36">
-        <v>3500</v>
+        <v>5200</v>
       </c>
       <c r="D36" t="str">
-        <v>2025-11-09</v>
+        <v>2025-12-05</v>
       </c>
       <c r="E36" t="str">
-        <v/>
+        <v>Food</v>
       </c>
       <c r="F36" t="str">
-        <v>Cash Wallet</v>
+        <v/>
       </c>
       <c r="G36" t="str">
-        <v>ATM Withdrawal</v>
+        <v>BigBasket</v>
       </c>
       <c r="H36" t="str">
-        <v>Wallet cash top-up</v>
+        <v>Groceries stock-up</v>
       </c>
       <c r="I36" t="str">
-        <v>Transfer</v>
+        <v>Card</v>
       </c>
       <c r="J36" t="str">
-        <v>cash,transfer</v>
+        <v>groceries,home</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Cash Wallet</v>
+        <v>Axis Salary Account</v>
       </c>
       <c r="B37" t="str">
         <v>Expense</v>
       </c>
       <c r="C37">
-        <v>240</v>
+        <v>2720</v>
       </c>
       <c r="D37" t="str">
-        <v>2025-11-10</v>
+        <v>2025-12-11</v>
       </c>
       <c r="E37" t="str">
-        <v>Transport</v>
+        <v>Food</v>
       </c>
       <c r="F37" t="str">
         <v/>
       </c>
       <c r="G37" t="str">
-        <v>Auto Rickshaw</v>
+        <v>Swiggy</v>
       </c>
       <c r="H37" t="str">
-        <v>Local commute</v>
+        <v>Dining and delivery</v>
       </c>
       <c r="I37" t="str">
-        <v>Cash</v>
+        <v>UPI</v>
       </c>
       <c r="J37" t="str">
-        <v>local,transport</v>
+        <v>food,lifestyle</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>Axis Salary Account</v>
       </c>
       <c r="B38" t="str">
         <v>Expense</v>
       </c>
       <c r="C38">
-        <v>2199</v>
+        <v>3460</v>
       </c>
       <c r="D38" t="str">
-        <v>2025-11-11</v>
+        <v>2025-12-08</v>
       </c>
       <c r="E38" t="str">
-        <v>Shopping</v>
+        <v>Transport</v>
       </c>
       <c r="F38" t="str">
         <v/>
       </c>
       <c r="G38" t="str">
-        <v>Amazon</v>
+        <v>Uber</v>
       </c>
       <c r="H38" t="str">
-        <v>Home office accessories</v>
+        <v>Office commute</v>
       </c>
       <c r="I38" t="str">
-        <v>Credit Card</v>
+        <v>UPI</v>
       </c>
       <c r="J38" t="str">
-        <v>shopping,office</v>
+        <v>transport,commute</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Axis Salary Account</v>
+        <v>HDFC Rewards Card</v>
       </c>
       <c r="B39" t="str">
         <v>Expense</v>
       </c>
       <c r="C39">
-        <v>950</v>
+        <v>2080</v>
       </c>
       <c r="D39" t="str">
-        <v>2025-11-12</v>
+        <v>2025-12-13</v>
       </c>
       <c r="E39" t="str">
-        <v>Food</v>
+        <v>Shopping</v>
       </c>
       <c r="F39" t="str">
         <v/>
       </c>
       <c r="G39" t="str">
-        <v>Swiggy</v>
+        <v>Amazon</v>
       </c>
       <c r="H39" t="str">
-        <v>Late dinner order</v>
+        <v>Shopping order</v>
       </c>
       <c r="I39" t="str">
-        <v>UPI</v>
+        <v>Card</v>
       </c>
       <c r="J39" t="str">
-        <v>food,delivery</v>
+        <v>shopping,online</v>
       </c>
     </row>
     <row r="40">
@@ -2605,10 +2605,10 @@
         <v>Expense</v>
       </c>
       <c r="C40">
-        <v>499</v>
+        <v>1960</v>
       </c>
       <c r="D40" t="str">
-        <v>2025-11-13</v>
+        <v>2025-12-19</v>
       </c>
       <c r="E40" t="str">
         <v>Entertainment</v>
@@ -2617,16 +2617,16 @@
         <v/>
       </c>
       <c r="G40" t="str">
-        <v>Netflix</v>
+        <v>BookMyShow</v>
       </c>
       <c r="H40" t="str">
-        <v>Monthly subscription</v>
+        <v>Weekend entertainment</v>
       </c>
       <c r="I40" t="str">
-        <v>Credit Card</v>
+        <v>Card</v>
       </c>
       <c r="J40" t="str">
-        <v>subscription,ott</v>
+        <v>fun,weekend</v>
       </c>
     </row>
     <row r="41">
@@ -2637,28 +2637,28 @@
         <v>Expense</v>
       </c>
       <c r="C41">
-        <v>680</v>
+        <v>4200</v>
       </c>
       <c r="D41" t="str">
-        <v>2025-11-14</v>
+        <v>2025-12-21</v>
       </c>
       <c r="E41" t="str">
-        <v>Transport</v>
+        <v>Health</v>
       </c>
       <c r="F41" t="str">
         <v/>
       </c>
       <c r="G41" t="str">
-        <v>Metro Card</v>
+        <v>Apollo Pharmacy</v>
       </c>
       <c r="H41" t="str">
-        <v>Recharge</v>
+        <v>Health and pharmacy</v>
       </c>
       <c r="I41" t="str">
         <v>UPI</v>
       </c>
       <c r="J41" t="str">
-        <v>metro,commute</v>
+        <v>health,care</v>
       </c>
     </row>
     <row r="42">
@@ -2666,95 +2666,95 @@
         <v>Axis Salary Account</v>
       </c>
       <c r="B42" t="str">
-        <v>Expense</v>
+        <v>Transfer</v>
       </c>
       <c r="C42">
-        <v>2750</v>
+        <v>19000</v>
       </c>
       <c r="D42" t="str">
-        <v>2025-11-15</v>
+        <v>2025-12-06</v>
       </c>
       <c r="E42" t="str">
-        <v>Food</v>
+        <v/>
       </c>
       <c r="F42" t="str">
-        <v/>
+        <v>Emergency Savings</v>
       </c>
       <c r="G42" t="str">
-        <v>Reliance Fresh</v>
+        <v>Self Transfer</v>
       </c>
       <c r="H42" t="str">
-        <v>Mid-month groceries</v>
+        <v>Move to emergency fund</v>
       </c>
       <c r="I42" t="str">
-        <v>Card</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="J42" t="str">
-        <v>groceries,weekly</v>
+        <v>saving,transfer</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>Axis Salary Account</v>
       </c>
       <c r="B43" t="str">
-        <v>Expense</v>
+        <v>Transfer</v>
       </c>
       <c r="C43">
-        <v>1899</v>
+        <v>4500</v>
       </c>
       <c r="D43" t="str">
-        <v>2025-11-16</v>
+        <v>2025-12-23</v>
       </c>
       <c r="E43" t="str">
-        <v>Shopping</v>
+        <v/>
       </c>
       <c r="F43" t="str">
-        <v/>
+        <v>Cash Wallet</v>
       </c>
       <c r="G43" t="str">
-        <v>Myntra</v>
+        <v>Self Transfer</v>
       </c>
       <c r="H43" t="str">
-        <v>Clothing order</v>
+        <v>Save for Japan trip</v>
       </c>
       <c r="I43" t="str">
-        <v>Credit Card</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="J43" t="str">
-        <v>shopping,fashion</v>
+        <v>goal,travel</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Cash Wallet</v>
+        <v>Axis Salary Account</v>
       </c>
       <c r="B44" t="str">
         <v>Expense</v>
       </c>
       <c r="C44">
-        <v>160</v>
+        <v>2500</v>
       </c>
       <c r="D44" t="str">
-        <v>2025-11-17</v>
+        <v>2025-12-07</v>
       </c>
       <c r="E44" t="str">
-        <v>Food</v>
+        <v>Transport</v>
       </c>
       <c r="F44" t="str">
         <v/>
       </c>
       <c r="G44" t="str">
-        <v>Tea Point</v>
+        <v>ATM Withdrawal</v>
       </c>
       <c r="H44" t="str">
-        <v>Snacks and tea</v>
+        <v>Cash for local expenses</v>
       </c>
       <c r="I44" t="str">
-        <v>Cash</v>
+        <v>ATM</v>
       </c>
       <c r="J44" t="str">
-        <v>snacks,cash</v>
+        <v>cash,atm</v>
       </c>
     </row>
     <row r="45">
@@ -2765,28 +2765,28 @@
         <v>Expense</v>
       </c>
       <c r="C45">
-        <v>1450</v>
+        <v>7000</v>
       </c>
       <c r="D45" t="str">
-        <v>2025-11-18</v>
+        <v>2025-12-25</v>
       </c>
       <c r="E45" t="str">
-        <v>Utilities</v>
+        <v>Shopping</v>
       </c>
       <c r="F45" t="str">
         <v/>
       </c>
       <c r="G45" t="str">
-        <v>Jio Mobile</v>
+        <v>HDFC Card Payment</v>
       </c>
       <c r="H45" t="str">
-        <v>Mobile recharge and add-ons</v>
+        <v>Credit card bill payment</v>
       </c>
       <c r="I45" t="str">
-        <v>UPI</v>
+        <v>Net Banking</v>
       </c>
       <c r="J45" t="str">
-        <v>mobile,utility</v>
+        <v>card,bill</v>
       </c>
     </row>
     <row r="46">
@@ -2797,60 +2797,60 @@
         <v>Income</v>
       </c>
       <c r="C46">
-        <v>6000</v>
+        <v>102500</v>
       </c>
       <c r="D46" t="str">
-        <v>2025-11-19</v>
+        <v>2025-12-31</v>
       </c>
       <c r="E46" t="str">
-        <v>Others</v>
+        <v>Salary</v>
       </c>
       <c r="F46" t="str">
         <v/>
       </c>
       <c r="G46" t="str">
-        <v>Cashback + Refunds</v>
+        <v>Employer Payroll</v>
       </c>
       <c r="H46" t="str">
-        <v>Credit card cashback and vendor refund</v>
+        <v>Monthly salary credit</v>
       </c>
       <c r="I46" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="J46" t="str">
-        <v>refund,cashback</v>
+        <v>salary,monthly</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>Axis Salary Account</v>
       </c>
       <c r="B47" t="str">
         <v>Expense</v>
       </c>
       <c r="C47">
-        <v>899</v>
+        <v>28000</v>
       </c>
       <c r="D47" t="str">
-        <v>2025-11-20</v>
+        <v>2026-01-02</v>
       </c>
       <c r="E47" t="str">
-        <v>Entertainment</v>
+        <v>Rent</v>
       </c>
       <c r="F47" t="str">
         <v/>
       </c>
       <c r="G47" t="str">
-        <v>PVR Cinemas</v>
+        <v>Sunrise Residency</v>
       </c>
       <c r="H47" t="str">
-        <v>Weekend movie</v>
+        <v>Monthly apartment rent</v>
       </c>
       <c r="I47" t="str">
-        <v>Credit Card</v>
+        <v>UPI</v>
       </c>
       <c r="J47" t="str">
-        <v>movie,leisure</v>
+        <v>housing,fixed</v>
       </c>
     </row>
     <row r="48">
@@ -2861,28 +2861,28 @@
         <v>Expense</v>
       </c>
       <c r="C48">
-        <v>2100</v>
+        <v>3470</v>
       </c>
       <c r="D48" t="str">
-        <v>2025-11-21</v>
+        <v>2026-01-03</v>
       </c>
       <c r="E48" t="str">
-        <v>Transport</v>
+        <v>Utilities</v>
       </c>
       <c r="F48" t="str">
         <v/>
       </c>
       <c r="G48" t="str">
-        <v>Indian Oil</v>
+        <v>BESCOM</v>
       </c>
       <c r="H48" t="str">
-        <v>Fuel refill</v>
+        <v>Electricity bill</v>
       </c>
       <c r="I48" t="str">
-        <v>Card</v>
+        <v>Net Banking</v>
       </c>
       <c r="J48" t="str">
-        <v>fuel,car</v>
+        <v>utilities,bill</v>
       </c>
     </row>
     <row r="49">
@@ -2893,28 +2893,28 @@
         <v>Expense</v>
       </c>
       <c r="C49">
-        <v>3900</v>
+        <v>1199</v>
       </c>
       <c r="D49" t="str">
-        <v>2025-11-22</v>
+        <v>2026-01-04</v>
       </c>
       <c r="E49" t="str">
-        <v>Food</v>
+        <v>Utilities</v>
       </c>
       <c r="F49" t="str">
         <v/>
       </c>
       <c r="G49" t="str">
-        <v>DMart</v>
+        <v>Airtel Fiber</v>
       </c>
       <c r="H49" t="str">
-        <v>Household and groceries</v>
+        <v>Internet payment</v>
       </c>
       <c r="I49" t="str">
-        <v>Card</v>
+        <v>UPI</v>
       </c>
       <c r="J49" t="str">
-        <v>groceries,household</v>
+        <v>internet,utility</v>
       </c>
     </row>
     <row r="50">
@@ -2922,159 +2922,159 @@
         <v>Axis Salary Account</v>
       </c>
       <c r="B50" t="str">
-        <v>Transfer</v>
+        <v>Expense</v>
       </c>
       <c r="C50">
-        <v>15000</v>
+        <v>5450</v>
       </c>
       <c r="D50" t="str">
-        <v>2025-11-23</v>
+        <v>2026-01-05</v>
       </c>
       <c r="E50" t="str">
-        <v/>
+        <v>Food</v>
       </c>
       <c r="F50" t="str">
-        <v>Emergency Savings</v>
+        <v/>
       </c>
       <c r="G50" t="str">
-        <v>Savings Sweep</v>
+        <v>BigBasket</v>
       </c>
       <c r="H50" t="str">
-        <v>Move surplus into emergency savings</v>
+        <v>Groceries stock-up</v>
       </c>
       <c r="I50" t="str">
-        <v>Transfer</v>
+        <v>Card</v>
       </c>
       <c r="J50" t="str">
-        <v>savings,transfer</v>
+        <v>groceries,home</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Emergency Savings</v>
+        <v>Axis Salary Account</v>
       </c>
       <c r="B51" t="str">
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="C51">
-        <v>950</v>
+        <v>2880</v>
       </c>
       <c r="D51" t="str">
-        <v>2025-11-24</v>
+        <v>2026-01-11</v>
       </c>
       <c r="E51" t="str">
-        <v>Others</v>
+        <v>Food</v>
       </c>
       <c r="F51" t="str">
         <v/>
       </c>
       <c r="G51" t="str">
-        <v>Interest Credit</v>
+        <v>Swiggy</v>
       </c>
       <c r="H51" t="str">
-        <v>Monthly interest credit</v>
+        <v>Dining and delivery</v>
       </c>
       <c r="I51" t="str">
-        <v>Bank Transfer</v>
+        <v>UPI</v>
       </c>
       <c r="J51" t="str">
-        <v>interest,savings</v>
+        <v>food,lifestyle</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>Axis Salary Account</v>
       </c>
       <c r="B52" t="str">
         <v>Expense</v>
       </c>
       <c r="C52">
-        <v>1799</v>
+        <v>3640</v>
       </c>
       <c r="D52" t="str">
-        <v>2025-11-25</v>
+        <v>2026-01-08</v>
       </c>
       <c r="E52" t="str">
-        <v>Shopping</v>
+        <v>Transport</v>
       </c>
       <c r="F52" t="str">
         <v/>
       </c>
       <c r="G52" t="str">
-        <v>Croma</v>
+        <v>Uber</v>
       </c>
       <c r="H52" t="str">
-        <v>Electronics accessories</v>
+        <v>Office commute</v>
       </c>
       <c r="I52" t="str">
-        <v>Credit Card</v>
+        <v>UPI</v>
       </c>
       <c r="J52" t="str">
-        <v>electronics,shopping</v>
+        <v>transport,commute</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Axis Salary Account</v>
+        <v>HDFC Rewards Card</v>
       </c>
       <c r="B53" t="str">
         <v>Expense</v>
       </c>
       <c r="C53">
-        <v>720</v>
+        <v>2220</v>
       </c>
       <c r="D53" t="str">
-        <v>2025-11-26</v>
+        <v>2026-01-13</v>
       </c>
       <c r="E53" t="str">
-        <v>Food</v>
+        <v>Shopping</v>
       </c>
       <c r="F53" t="str">
         <v/>
       </c>
       <c r="G53" t="str">
-        <v>Cafe Coffee Day</v>
+        <v>Amazon</v>
       </c>
       <c r="H53" t="str">
-        <v>Client catch-up</v>
+        <v>Shopping order</v>
       </c>
       <c r="I53" t="str">
-        <v>UPI</v>
+        <v>Card</v>
       </c>
       <c r="J53" t="str">
-        <v>coffee,meeting</v>
+        <v>shopping,online</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Cash Wallet</v>
+        <v>HDFC Rewards Card</v>
       </c>
       <c r="B54" t="str">
         <v>Expense</v>
       </c>
       <c r="C54">
-        <v>310</v>
+        <v>2090</v>
       </c>
       <c r="D54" t="str">
-        <v>2025-11-27</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E54" t="str">
-        <v>Food</v>
+        <v>Entertainment</v>
       </c>
       <c r="F54" t="str">
         <v/>
       </c>
       <c r="G54" t="str">
-        <v>Street Food</v>
+        <v>BookMyShow</v>
       </c>
       <c r="H54" t="str">
-        <v>Quick dinner</v>
+        <v>Weekend entertainment</v>
       </c>
       <c r="I54" t="str">
-        <v>Cash</v>
+        <v>Card</v>
       </c>
       <c r="J54" t="str">
-        <v>food,cash</v>
+        <v>fun,weekend</v>
       </c>
     </row>
     <row r="55">
@@ -3085,28 +3085,28 @@
         <v>Expense</v>
       </c>
       <c r="C55">
-        <v>1600</v>
+        <v>1140</v>
       </c>
       <c r="D55" t="str">
-        <v>2025-11-28</v>
+        <v>2026-01-21</v>
       </c>
       <c r="E55" t="str">
-        <v>Utilities</v>
+        <v>Health</v>
       </c>
       <c r="F55" t="str">
         <v/>
       </c>
       <c r="G55" t="str">
-        <v>Health Insurance</v>
+        <v>Apollo Pharmacy</v>
       </c>
       <c r="H55" t="str">
-        <v>Insurance auto debit</v>
+        <v>Health and pharmacy</v>
       </c>
       <c r="I55" t="str">
-        <v>Bank Transfer</v>
+        <v>UPI</v>
       </c>
       <c r="J55" t="str">
-        <v>insurance,health</v>
+        <v>health,care</v>
       </c>
     </row>
     <row r="56">
@@ -3114,31 +3114,31 @@
         <v>Axis Salary Account</v>
       </c>
       <c r="B56" t="str">
-        <v>Income</v>
+        <v>Transfer</v>
       </c>
       <c r="C56">
-        <v>98000</v>
+        <v>20000</v>
       </c>
       <c r="D56" t="str">
-        <v>2025-12-01</v>
+        <v>2026-01-06</v>
       </c>
       <c r="E56" t="str">
-        <v>Salary</v>
+        <v/>
       </c>
       <c r="F56" t="str">
-        <v/>
+        <v>Emergency Savings</v>
       </c>
       <c r="G56" t="str">
-        <v>Employer Payroll</v>
+        <v>Self Transfer</v>
       </c>
       <c r="H56" t="str">
-        <v>Monthly salary credit</v>
+        <v>Move to emergency fund</v>
       </c>
       <c r="I56" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="J56" t="str">
-        <v>salary,monthly</v>
+        <v>saving,transfer</v>
       </c>
     </row>
     <row r="57">
@@ -3146,31 +3146,31 @@
         <v>Axis Salary Account</v>
       </c>
       <c r="B57" t="str">
-        <v>Expense</v>
+        <v>Transfer</v>
       </c>
       <c r="C57">
-        <v>28000</v>
+        <v>5000</v>
       </c>
       <c r="D57" t="str">
-        <v>2025-12-03</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E57" t="str">
-        <v>Rent</v>
+        <v/>
       </c>
       <c r="F57" t="str">
-        <v/>
+        <v>Cash Wallet</v>
       </c>
       <c r="G57" t="str">
-        <v>Sunrise Residency</v>
+        <v>Self Transfer</v>
       </c>
       <c r="H57" t="str">
-        <v>Monthly apartment rent</v>
+        <v>Save for Japan trip</v>
       </c>
       <c r="I57" t="str">
-        <v>UPI</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="J57" t="str">
-        <v>housing,fixed</v>
+        <v>goal,travel</v>
       </c>
     </row>
     <row r="58">
@@ -3181,28 +3181,28 @@
         <v>Expense</v>
       </c>
       <c r="C58">
-        <v>3200</v>
+        <v>2500</v>
       </c>
       <c r="D58" t="str">
-        <v>2025-12-04</v>
+        <v>2026-01-07</v>
       </c>
       <c r="E58" t="str">
-        <v>Utilities</v>
+        <v>Transport</v>
       </c>
       <c r="F58" t="str">
         <v/>
       </c>
       <c r="G58" t="str">
-        <v>BESCOM</v>
+        <v>ATM Withdrawal</v>
       </c>
       <c r="H58" t="str">
-        <v>Electricity bill</v>
+        <v>Cash for local expenses</v>
       </c>
       <c r="I58" t="str">
-        <v>Net Banking</v>
+        <v>ATM</v>
       </c>
       <c r="J58" t="str">
-        <v>utilities,bill</v>
+        <v>cash,atm</v>
       </c>
     </row>
     <row r="59">
@@ -3213,28 +3213,28 @@
         <v>Expense</v>
       </c>
       <c r="C59">
-        <v>1199</v>
+        <v>7400</v>
       </c>
       <c r="D59" t="str">
-        <v>2025-12-05</v>
+        <v>2026-01-25</v>
       </c>
       <c r="E59" t="str">
-        <v>Utilities</v>
+        <v>Shopping</v>
       </c>
       <c r="F59" t="str">
         <v/>
       </c>
       <c r="G59" t="str">
-        <v>Airtel Fiber</v>
+        <v>HDFC Card Payment</v>
       </c>
       <c r="H59" t="str">
-        <v>Internet payment</v>
+        <v>Credit card bill payment</v>
       </c>
       <c r="I59" t="str">
-        <v>UPI</v>
+        <v>Net Banking</v>
       </c>
       <c r="J59" t="str">
-        <v>internet,utility</v>
+        <v>card,bill</v>
       </c>
     </row>
     <row r="60">
@@ -3242,31 +3242,31 @@
         <v>Axis Salary Account</v>
       </c>
       <c r="B60" t="str">
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="C60">
-        <v>4800</v>
+        <v>104000</v>
       </c>
       <c r="D60" t="str">
-        <v>2025-12-06</v>
+        <v>2026-01-31</v>
       </c>
       <c r="E60" t="str">
-        <v>Food</v>
+        <v>Salary</v>
       </c>
       <c r="F60" t="str">
         <v/>
       </c>
       <c r="G60" t="str">
-        <v>BigBasket</v>
+        <v>Employer Payroll</v>
       </c>
       <c r="H60" t="str">
-        <v>Groceries stock-up</v>
+        <v>Monthly salary credit</v>
       </c>
       <c r="I60" t="str">
-        <v>Card</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="J60" t="str">
-        <v>groceries,home</v>
+        <v>salary,monthly</v>
       </c>
     </row>
     <row r="61">
@@ -3274,31 +3274,31 @@
         <v>Axis Salary Account</v>
       </c>
       <c r="B61" t="str">
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="C61">
-        <v>420</v>
+        <v>14400</v>
       </c>
       <c r="D61" t="str">
-        <v>2025-12-07</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E61" t="str">
-        <v>Transport</v>
+        <v>Freelance</v>
       </c>
       <c r="F61" t="str">
         <v/>
       </c>
       <c r="G61" t="str">
-        <v>Uber</v>
+        <v>Consulting Client</v>
       </c>
       <c r="H61" t="str">
-        <v>Office commute</v>
+        <v>Side project payout</v>
       </c>
       <c r="I61" t="str">
-        <v>UPI</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="J61" t="str">
-        <v>commute,cab</v>
+        <v>freelance,side-income</v>
       </c>
     </row>
     <row r="62">
@@ -3306,31 +3306,31 @@
         <v>Axis Salary Account</v>
       </c>
       <c r="B62" t="str">
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="C62">
-        <v>12500</v>
+        <v>28000</v>
       </c>
       <c r="D62" t="str">
-        <v>2025-12-08</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E62" t="str">
-        <v>Freelance</v>
+        <v>Rent</v>
       </c>
       <c r="F62" t="str">
         <v/>
       </c>
       <c r="G62" t="str">
-        <v>Product Design Client</v>
+        <v>Sunrise Residency</v>
       </c>
       <c r="H62" t="str">
-        <v>Freelance milestone payment</v>
+        <v>Monthly apartment rent</v>
       </c>
       <c r="I62" t="str">
-        <v>Bank Transfer</v>
+        <v>UPI</v>
       </c>
       <c r="J62" t="str">
-        <v>freelance,design</v>
+        <v>housing,fixed</v>
       </c>
     </row>
     <row r="63">
@@ -3338,95 +3338,95 @@
         <v>Axis Salary Account</v>
       </c>
       <c r="B63" t="str">
-        <v>Transfer</v>
+        <v>Expense</v>
       </c>
       <c r="C63">
-        <v>3500</v>
+        <v>3560</v>
       </c>
       <c r="D63" t="str">
-        <v>2025-12-09</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E63" t="str">
-        <v/>
+        <v>Utilities</v>
       </c>
       <c r="F63" t="str">
-        <v>Cash Wallet</v>
+        <v/>
       </c>
       <c r="G63" t="str">
-        <v>ATM Withdrawal</v>
+        <v>BESCOM</v>
       </c>
       <c r="H63" t="str">
-        <v>Wallet cash top-up</v>
+        <v>Electricity bill</v>
       </c>
       <c r="I63" t="str">
-        <v>Transfer</v>
+        <v>Net Banking</v>
       </c>
       <c r="J63" t="str">
-        <v>cash,transfer</v>
+        <v>utilities,bill</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Cash Wallet</v>
+        <v>Axis Salary Account</v>
       </c>
       <c r="B64" t="str">
         <v>Expense</v>
       </c>
       <c r="C64">
-        <v>240</v>
+        <v>1199</v>
       </c>
       <c r="D64" t="str">
-        <v>2025-12-10</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E64" t="str">
-        <v>Transport</v>
+        <v>Utilities</v>
       </c>
       <c r="F64" t="str">
         <v/>
       </c>
       <c r="G64" t="str">
-        <v>Auto Rickshaw</v>
+        <v>Airtel Fiber</v>
       </c>
       <c r="H64" t="str">
-        <v>Local commute</v>
+        <v>Internet payment</v>
       </c>
       <c r="I64" t="str">
-        <v>Cash</v>
+        <v>UPI</v>
       </c>
       <c r="J64" t="str">
-        <v>local,transport</v>
+        <v>internet,utility</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>Axis Salary Account</v>
       </c>
       <c r="B65" t="str">
         <v>Expense</v>
       </c>
       <c r="C65">
-        <v>2199</v>
+        <v>5700</v>
       </c>
       <c r="D65" t="str">
-        <v>2025-12-11</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E65" t="str">
-        <v>Shopping</v>
+        <v>Food</v>
       </c>
       <c r="F65" t="str">
         <v/>
       </c>
       <c r="G65" t="str">
-        <v>Amazon</v>
+        <v>BigBasket</v>
       </c>
       <c r="H65" t="str">
-        <v>Home office accessories</v>
+        <v>Groceries stock-up</v>
       </c>
       <c r="I65" t="str">
-        <v>Credit Card</v>
+        <v>Card</v>
       </c>
       <c r="J65" t="str">
-        <v>shopping,office</v>
+        <v>groceries,home</v>
       </c>
     </row>
     <row r="66">
@@ -3437,10 +3437,10 @@
         <v>Expense</v>
       </c>
       <c r="C66">
-        <v>950</v>
+        <v>3040</v>
       </c>
       <c r="D66" t="str">
-        <v>2025-12-12</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E66" t="str">
         <v>Food</v>
@@ -3452,173 +3452,173 @@
         <v>Swiggy</v>
       </c>
       <c r="H66" t="str">
-        <v>Late dinner order</v>
+        <v>Dining and delivery</v>
       </c>
       <c r="I66" t="str">
         <v>UPI</v>
       </c>
       <c r="J66" t="str">
-        <v>food,delivery</v>
+        <v>food,lifestyle</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>Axis Salary Account</v>
       </c>
       <c r="B67" t="str">
         <v>Expense</v>
       </c>
       <c r="C67">
-        <v>499</v>
+        <v>3820</v>
       </c>
       <c r="D67" t="str">
-        <v>2025-12-13</v>
+        <v>2026-02-08</v>
       </c>
       <c r="E67" t="str">
-        <v>Entertainment</v>
+        <v>Transport</v>
       </c>
       <c r="F67" t="str">
         <v/>
       </c>
       <c r="G67" t="str">
-        <v>Netflix</v>
+        <v>Uber</v>
       </c>
       <c r="H67" t="str">
-        <v>Monthly subscription</v>
+        <v>Office commute</v>
       </c>
       <c r="I67" t="str">
-        <v>Credit Card</v>
+        <v>UPI</v>
       </c>
       <c r="J67" t="str">
-        <v>subscription,ott</v>
+        <v>transport,commute</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Axis Salary Account</v>
+        <v>HDFC Rewards Card</v>
       </c>
       <c r="B68" t="str">
         <v>Expense</v>
       </c>
       <c r="C68">
-        <v>680</v>
+        <v>2600</v>
       </c>
       <c r="D68" t="str">
-        <v>2025-12-14</v>
+        <v>2026-02-13</v>
       </c>
       <c r="E68" t="str">
-        <v>Transport</v>
+        <v>Shopping</v>
       </c>
       <c r="F68" t="str">
         <v/>
       </c>
       <c r="G68" t="str">
-        <v>Metro Card</v>
+        <v>Amazon</v>
       </c>
       <c r="H68" t="str">
-        <v>Recharge</v>
+        <v>Shopping order</v>
       </c>
       <c r="I68" t="str">
-        <v>UPI</v>
+        <v>Card</v>
       </c>
       <c r="J68" t="str">
-        <v>metro,commute</v>
+        <v>shopping,online</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Axis Salary Account</v>
+        <v>HDFC Rewards Card</v>
       </c>
       <c r="B69" t="str">
         <v>Expense</v>
       </c>
       <c r="C69">
-        <v>2750</v>
+        <v>2220</v>
       </c>
       <c r="D69" t="str">
-        <v>2025-12-15</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E69" t="str">
-        <v>Food</v>
+        <v>Entertainment</v>
       </c>
       <c r="F69" t="str">
         <v/>
       </c>
       <c r="G69" t="str">
-        <v>Reliance Fresh</v>
+        <v>BookMyShow</v>
       </c>
       <c r="H69" t="str">
-        <v>Mid-month groceries</v>
+        <v>Weekend entertainment</v>
       </c>
       <c r="I69" t="str">
         <v>Card</v>
       </c>
       <c r="J69" t="str">
-        <v>groceries,weekly</v>
+        <v>fun,weekend</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>Axis Salary Account</v>
       </c>
       <c r="B70" t="str">
         <v>Expense</v>
       </c>
       <c r="C70">
-        <v>1899</v>
+        <v>1220</v>
       </c>
       <c r="D70" t="str">
-        <v>2025-12-16</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E70" t="str">
-        <v>Shopping</v>
+        <v>Health</v>
       </c>
       <c r="F70" t="str">
         <v/>
       </c>
       <c r="G70" t="str">
-        <v>Myntra</v>
+        <v>Apollo Pharmacy</v>
       </c>
       <c r="H70" t="str">
-        <v>Clothing order</v>
+        <v>Health and pharmacy</v>
       </c>
       <c r="I70" t="str">
-        <v>Credit Card</v>
+        <v>UPI</v>
       </c>
       <c r="J70" t="str">
-        <v>shopping,fashion</v>
+        <v>health,care</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Cash Wallet</v>
+        <v>Axis Salary Account</v>
       </c>
       <c r="B71" t="str">
-        <v>Expense</v>
+        <v>Transfer</v>
       </c>
       <c r="C71">
-        <v>160</v>
+        <v>21000</v>
       </c>
       <c r="D71" t="str">
-        <v>2025-12-17</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E71" t="str">
-        <v>Food</v>
+        <v/>
       </c>
       <c r="F71" t="str">
-        <v/>
+        <v>Emergency Savings</v>
       </c>
       <c r="G71" t="str">
-        <v>Tea Point</v>
+        <v>Self Transfer</v>
       </c>
       <c r="H71" t="str">
-        <v>Snacks and tea</v>
+        <v>Move to emergency fund</v>
       </c>
       <c r="I71" t="str">
-        <v>Cash</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="J71" t="str">
-        <v>snacks,cash</v>
+        <v>saving,transfer</v>
       </c>
     </row>
     <row r="72">
@@ -3626,31 +3626,31 @@
         <v>Axis Salary Account</v>
       </c>
       <c r="B72" t="str">
-        <v>Expense</v>
+        <v>Transfer</v>
       </c>
       <c r="C72">
-        <v>1450</v>
+        <v>5500</v>
       </c>
       <c r="D72" t="str">
-        <v>2025-12-18</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E72" t="str">
-        <v>Utilities</v>
+        <v/>
       </c>
       <c r="F72" t="str">
-        <v/>
+        <v>Cash Wallet</v>
       </c>
       <c r="G72" t="str">
-        <v>Jio Mobile</v>
+        <v>Self Transfer</v>
       </c>
       <c r="H72" t="str">
-        <v>Mobile recharge and add-ons</v>
+        <v>Save for Japan trip</v>
       </c>
       <c r="I72" t="str">
-        <v>UPI</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="J72" t="str">
-        <v>mobile,utility</v>
+        <v>goal,travel</v>
       </c>
     </row>
     <row r="73">
@@ -3658,63 +3658,63 @@
         <v>Axis Salary Account</v>
       </c>
       <c r="B73" t="str">
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="C73">
-        <v>6000</v>
+        <v>2500</v>
       </c>
       <c r="D73" t="str">
-        <v>2025-12-19</v>
+        <v>2026-02-07</v>
       </c>
       <c r="E73" t="str">
-        <v>Others</v>
+        <v>Transport</v>
       </c>
       <c r="F73" t="str">
         <v/>
       </c>
       <c r="G73" t="str">
-        <v>Cashback + Refunds</v>
+        <v>ATM Withdrawal</v>
       </c>
       <c r="H73" t="str">
-        <v>Credit card cashback and vendor refund</v>
+        <v>Cash for local expenses</v>
       </c>
       <c r="I73" t="str">
-        <v>Bank Transfer</v>
+        <v>ATM</v>
       </c>
       <c r="J73" t="str">
-        <v>refund,cashback</v>
+        <v>cash,atm</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>Axis Salary Account</v>
       </c>
       <c r="B74" t="str">
         <v>Expense</v>
       </c>
       <c r="C74">
-        <v>899</v>
+        <v>7800</v>
       </c>
       <c r="D74" t="str">
-        <v>2025-12-20</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E74" t="str">
-        <v>Entertainment</v>
+        <v>Shopping</v>
       </c>
       <c r="F74" t="str">
         <v/>
       </c>
       <c r="G74" t="str">
-        <v>PVR Cinemas</v>
+        <v>HDFC Card Payment</v>
       </c>
       <c r="H74" t="str">
-        <v>Weekend movie</v>
+        <v>Credit card bill payment</v>
       </c>
       <c r="I74" t="str">
-        <v>Credit Card</v>
+        <v>Net Banking</v>
       </c>
       <c r="J74" t="str">
-        <v>movie,leisure</v>
+        <v>card,bill</v>
       </c>
     </row>
     <row r="75">
@@ -3722,31 +3722,31 @@
         <v>Axis Salary Account</v>
       </c>
       <c r="B75" t="str">
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="C75">
-        <v>2100</v>
+        <v>105500</v>
       </c>
       <c r="D75" t="str">
-        <v>2025-12-21</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E75" t="str">
-        <v>Transport</v>
+        <v>Salary</v>
       </c>
       <c r="F75" t="str">
         <v/>
       </c>
       <c r="G75" t="str">
-        <v>Indian Oil</v>
+        <v>Employer Payroll</v>
       </c>
       <c r="H75" t="str">
-        <v>Fuel refill</v>
+        <v>Monthly salary credit</v>
       </c>
       <c r="I75" t="str">
-        <v>Card</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="J75" t="str">
-        <v>fuel,car</v>
+        <v>salary,monthly</v>
       </c>
     </row>
     <row r="76">
@@ -3757,28 +3757,28 @@
         <v>Expense</v>
       </c>
       <c r="C76">
-        <v>3900</v>
+        <v>28000</v>
       </c>
       <c r="D76" t="str">
-        <v>2025-12-22</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E76" t="str">
-        <v>Food</v>
+        <v>Rent</v>
       </c>
       <c r="F76" t="str">
         <v/>
       </c>
       <c r="G76" t="str">
-        <v>DMart</v>
+        <v>Sunrise Residency</v>
       </c>
       <c r="H76" t="str">
-        <v>Household and groceries</v>
+        <v>Monthly apartment rent</v>
       </c>
       <c r="I76" t="str">
-        <v>Card</v>
+        <v>UPI</v>
       </c>
       <c r="J76" t="str">
-        <v>groceries,household</v>
+        <v>housing,fixed</v>
       </c>
     </row>
     <row r="77">
@@ -3786,95 +3786,95 @@
         <v>Axis Salary Account</v>
       </c>
       <c r="B77" t="str">
-        <v>Transfer</v>
+        <v>Expense</v>
       </c>
       <c r="C77">
-        <v>15000</v>
+        <v>3650</v>
       </c>
       <c r="D77" t="str">
-        <v>2025-12-23</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E77" t="str">
-        <v/>
+        <v>Utilities</v>
       </c>
       <c r="F77" t="str">
-        <v>Emergency Savings</v>
+        <v/>
       </c>
       <c r="G77" t="str">
-        <v>Savings Sweep</v>
+        <v>BESCOM</v>
       </c>
       <c r="H77" t="str">
-        <v>Move surplus into emergency savings</v>
+        <v>Electricity bill</v>
       </c>
       <c r="I77" t="str">
-        <v>Transfer</v>
+        <v>Net Banking</v>
       </c>
       <c r="J77" t="str">
-        <v>savings,transfer</v>
+        <v>utilities,bill</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Emergency Savings</v>
+        <v>Axis Salary Account</v>
       </c>
       <c r="B78" t="str">
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="C78">
-        <v>950</v>
+        <v>1199</v>
       </c>
       <c r="D78" t="str">
-        <v>2025-12-24</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E78" t="str">
-        <v>Others</v>
+        <v>Utilities</v>
       </c>
       <c r="F78" t="str">
         <v/>
       </c>
       <c r="G78" t="str">
-        <v>Interest Credit</v>
+        <v>Airtel Fiber</v>
       </c>
       <c r="H78" t="str">
-        <v>Monthly interest credit</v>
+        <v>Internet payment</v>
       </c>
       <c r="I78" t="str">
-        <v>Bank Transfer</v>
+        <v>UPI</v>
       </c>
       <c r="J78" t="str">
-        <v>interest,savings</v>
+        <v>internet,utility</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>Axis Salary Account</v>
       </c>
       <c r="B79" t="str">
         <v>Expense</v>
       </c>
       <c r="C79">
-        <v>1799</v>
+        <v>6900</v>
       </c>
       <c r="D79" t="str">
-        <v>2025-12-25</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E79" t="str">
-        <v>Shopping</v>
+        <v>Food</v>
       </c>
       <c r="F79" t="str">
         <v/>
       </c>
       <c r="G79" t="str">
-        <v>Croma</v>
+        <v>BigBasket</v>
       </c>
       <c r="H79" t="str">
-        <v>Electronics accessories</v>
+        <v>Groceries stock-up</v>
       </c>
       <c r="I79" t="str">
-        <v>Credit Card</v>
+        <v>Card</v>
       </c>
       <c r="J79" t="str">
-        <v>electronics,shopping</v>
+        <v>groceries,home</v>
       </c>
     </row>
     <row r="80">
@@ -3885,10 +3885,10 @@
         <v>Expense</v>
       </c>
       <c r="C80">
-        <v>720</v>
+        <v>5200</v>
       </c>
       <c r="D80" t="str">
-        <v>2025-12-26</v>
+        <v>2026-03-11</v>
       </c>
       <c r="E80" t="str">
         <v>Food</v>
@@ -3897,112 +3897,112 @@
         <v/>
       </c>
       <c r="G80" t="str">
-        <v>Cafe Coffee Day</v>
+        <v>Swiggy</v>
       </c>
       <c r="H80" t="str">
-        <v>Client catch-up</v>
+        <v>Dining and delivery</v>
       </c>
       <c r="I80" t="str">
         <v>UPI</v>
       </c>
       <c r="J80" t="str">
-        <v>coffee,meeting</v>
+        <v>food,lifestyle</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Cash Wallet</v>
+        <v>Axis Salary Account</v>
       </c>
       <c r="B81" t="str">
         <v>Expense</v>
       </c>
       <c r="C81">
-        <v>310</v>
+        <v>4000</v>
       </c>
       <c r="D81" t="str">
-        <v>2025-12-27</v>
+        <v>2026-03-08</v>
       </c>
       <c r="E81" t="str">
-        <v>Food</v>
+        <v>Transport</v>
       </c>
       <c r="F81" t="str">
         <v/>
       </c>
       <c r="G81" t="str">
-        <v>Street Food</v>
+        <v>Uber</v>
       </c>
       <c r="H81" t="str">
-        <v>Quick dinner</v>
+        <v>Office commute</v>
       </c>
       <c r="I81" t="str">
-        <v>Cash</v>
+        <v>UPI</v>
       </c>
       <c r="J81" t="str">
-        <v>food,cash</v>
+        <v>transport,commute</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Axis Salary Account</v>
+        <v>HDFC Rewards Card</v>
       </c>
       <c r="B82" t="str">
         <v>Expense</v>
       </c>
       <c r="C82">
-        <v>1600</v>
+        <v>8800</v>
       </c>
       <c r="D82" t="str">
-        <v>2025-12-28</v>
+        <v>2026-03-13</v>
       </c>
       <c r="E82" t="str">
-        <v>Utilities</v>
+        <v>Shopping</v>
       </c>
       <c r="F82" t="str">
         <v/>
       </c>
       <c r="G82" t="str">
-        <v>Health Insurance</v>
+        <v>Amazon</v>
       </c>
       <c r="H82" t="str">
-        <v>Insurance auto debit</v>
+        <v>Shopping order</v>
       </c>
       <c r="I82" t="str">
-        <v>Bank Transfer</v>
+        <v>Card</v>
       </c>
       <c r="J82" t="str">
-        <v>insurance,health</v>
+        <v>shopping,online</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Axis Salary Account</v>
+        <v>HDFC Rewards Card</v>
       </c>
       <c r="B83" t="str">
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="C83">
-        <v>98000</v>
+        <v>2350</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-01-01</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E83" t="str">
-        <v>Salary</v>
+        <v>Entertainment</v>
       </c>
       <c r="F83" t="str">
         <v/>
       </c>
       <c r="G83" t="str">
-        <v>Employer Payroll</v>
+        <v>BookMyShow</v>
       </c>
       <c r="H83" t="str">
-        <v>Monthly salary credit</v>
+        <v>Weekend entertainment</v>
       </c>
       <c r="I83" t="str">
-        <v>Bank Transfer</v>
+        <v>Card</v>
       </c>
       <c r="J83" t="str">
-        <v>salary,monthly</v>
+        <v>fun,weekend</v>
       </c>
     </row>
     <row r="84">
@@ -4013,28 +4013,28 @@
         <v>Expense</v>
       </c>
       <c r="C84">
-        <v>28000</v>
+        <v>1300</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-01-03</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E84" t="str">
-        <v>Rent</v>
+        <v>Health</v>
       </c>
       <c r="F84" t="str">
         <v/>
       </c>
       <c r="G84" t="str">
-        <v>Sunrise Residency</v>
+        <v>Apollo Pharmacy</v>
       </c>
       <c r="H84" t="str">
-        <v>Monthly apartment rent</v>
+        <v>Health and pharmacy</v>
       </c>
       <c r="I84" t="str">
         <v>UPI</v>
       </c>
       <c r="J84" t="str">
-        <v>housing,fixed</v>
+        <v>health,care</v>
       </c>
     </row>
     <row r="85">
@@ -4042,31 +4042,31 @@
         <v>Axis Salary Account</v>
       </c>
       <c r="B85" t="str">
-        <v>Expense</v>
+        <v>Transfer</v>
       </c>
       <c r="C85">
-        <v>3200</v>
+        <v>22000</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-01-04</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E85" t="str">
-        <v>Utilities</v>
+        <v/>
       </c>
       <c r="F85" t="str">
-        <v/>
+        <v>Emergency Savings</v>
       </c>
       <c r="G85" t="str">
-        <v>BESCOM</v>
+        <v>Self Transfer</v>
       </c>
       <c r="H85" t="str">
-        <v>Electricity bill</v>
+        <v>Move to emergency fund</v>
       </c>
       <c r="I85" t="str">
-        <v>Net Banking</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="J85" t="str">
-        <v>utilities,bill</v>
+        <v>saving,transfer</v>
       </c>
     </row>
     <row r="86">
@@ -4074,31 +4074,31 @@
         <v>Axis Salary Account</v>
       </c>
       <c r="B86" t="str">
-        <v>Expense</v>
+        <v>Transfer</v>
       </c>
       <c r="C86">
-        <v>1199</v>
+        <v>6000</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-01-05</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E86" t="str">
-        <v>Utilities</v>
+        <v/>
       </c>
       <c r="F86" t="str">
-        <v/>
+        <v>Cash Wallet</v>
       </c>
       <c r="G86" t="str">
-        <v>Airtel Fiber</v>
+        <v>Self Transfer</v>
       </c>
       <c r="H86" t="str">
-        <v>Internet payment</v>
+        <v>Save for Japan trip</v>
       </c>
       <c r="I86" t="str">
-        <v>UPI</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="J86" t="str">
-        <v>internet,utility</v>
+        <v>goal,travel</v>
       </c>
     </row>
     <row r="87">
@@ -4109,28 +4109,28 @@
         <v>Expense</v>
       </c>
       <c r="C87">
-        <v>4800</v>
+        <v>2500</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-01-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E87" t="str">
-        <v>Food</v>
+        <v>Transport</v>
       </c>
       <c r="F87" t="str">
         <v/>
       </c>
       <c r="G87" t="str">
-        <v>BigBasket</v>
+        <v>ATM Withdrawal</v>
       </c>
       <c r="H87" t="str">
-        <v>Groceries stock-up</v>
+        <v>Cash for local expenses</v>
       </c>
       <c r="I87" t="str">
-        <v>Card</v>
+        <v>ATM</v>
       </c>
       <c r="J87" t="str">
-        <v>groceries,home</v>
+        <v>cash,atm</v>
       </c>
     </row>
     <row r="88">
@@ -4141,28 +4141,28 @@
         <v>Expense</v>
       </c>
       <c r="C88">
-        <v>420</v>
+        <v>8200</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-01-07</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E88" t="str">
-        <v>Transport</v>
+        <v>Shopping</v>
       </c>
       <c r="F88" t="str">
         <v/>
       </c>
       <c r="G88" t="str">
-        <v>Uber</v>
+        <v>HDFC Card Payment</v>
       </c>
       <c r="H88" t="str">
-        <v>Office commute</v>
+        <v>Credit card bill payment</v>
       </c>
       <c r="I88" t="str">
-        <v>UPI</v>
+        <v>Net Banking</v>
       </c>
       <c r="J88" t="str">
-        <v>commute,cab</v>
+        <v>card,bill</v>
       </c>
     </row>
     <row r="89">
@@ -4170,2404 +4170,100 @@
         <v>Axis Salary Account</v>
       </c>
       <c r="B89" t="str">
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="C89">
-        <v>12500</v>
+        <v>7600</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-01-08</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E89" t="str">
-        <v>Freelance</v>
+        <v>Food</v>
       </c>
       <c r="F89" t="str">
         <v/>
       </c>
       <c r="G89" t="str">
-        <v>Product Design Client</v>
+        <v>Nature Basket</v>
       </c>
       <c r="H89" t="str">
-        <v>Freelance milestone payment</v>
+        <v>Premium groceries for guests</v>
       </c>
       <c r="I89" t="str">
-        <v>Bank Transfer</v>
+        <v>Card</v>
       </c>
       <c r="J89" t="str">
-        <v>freelance,design</v>
+        <v>food,hosting</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Axis Salary Account</v>
+        <v>HDFC Rewards Card</v>
       </c>
       <c r="B90" t="str">
-        <v>Transfer</v>
+        <v>Expense</v>
       </c>
       <c r="C90">
-        <v>3500</v>
+        <v>6400</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-01-09</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E90" t="str">
-        <v/>
+        <v>Shopping</v>
       </c>
       <c r="F90" t="str">
-        <v>Cash Wallet</v>
+        <v/>
       </c>
       <c r="G90" t="str">
-        <v>ATM Withdrawal</v>
+        <v>Myntra</v>
       </c>
       <c r="H90" t="str">
-        <v>Wallet cash top-up</v>
+        <v>Festive wardrobe refresh</v>
       </c>
       <c r="I90" t="str">
-        <v>Transfer</v>
+        <v>Card</v>
       </c>
       <c r="J90" t="str">
-        <v>cash,transfer</v>
+        <v>shopping,fashion</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Cash Wallet</v>
+        <v>Axis Salary Account</v>
       </c>
       <c r="B91" t="str">
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="C91">
-        <v>240</v>
+        <v>22000</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-01-10</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E91" t="str">
-        <v>Transport</v>
+        <v>Bonus</v>
       </c>
       <c r="F91" t="str">
         <v/>
       </c>
       <c r="G91" t="str">
-        <v>Auto Rickshaw</v>
+        <v>Performance Bonus</v>
       </c>
       <c r="H91" t="str">
-        <v>Local commute</v>
+        <v>Quarter-end bonus</v>
       </c>
       <c r="I91" t="str">
-        <v>Cash</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="J91" t="str">
-        <v>local,transport</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="str">
-        <v>HDFC Rewards Card</v>
-      </c>
-      <c r="B92" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C92">
-        <v>2199</v>
-      </c>
-      <c r="D92" t="str">
-        <v>2026-01-11</v>
-      </c>
-      <c r="E92" t="str">
-        <v>Shopping</v>
-      </c>
-      <c r="F92" t="str">
-        <v/>
-      </c>
-      <c r="G92" t="str">
-        <v>Amazon</v>
-      </c>
-      <c r="H92" t="str">
-        <v>Home office accessories</v>
-      </c>
-      <c r="I92" t="str">
-        <v>Credit Card</v>
-      </c>
-      <c r="J92" t="str">
-        <v>shopping,office</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B93" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C93">
-        <v>950</v>
-      </c>
-      <c r="D93" t="str">
-        <v>2026-01-12</v>
-      </c>
-      <c r="E93" t="str">
-        <v>Food</v>
-      </c>
-      <c r="F93" t="str">
-        <v/>
-      </c>
-      <c r="G93" t="str">
-        <v>Swiggy</v>
-      </c>
-      <c r="H93" t="str">
-        <v>Late dinner order</v>
-      </c>
-      <c r="I93" t="str">
-        <v>UPI</v>
-      </c>
-      <c r="J93" t="str">
-        <v>food,delivery</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="str">
-        <v>HDFC Rewards Card</v>
-      </c>
-      <c r="B94" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C94">
-        <v>499</v>
-      </c>
-      <c r="D94" t="str">
-        <v>2026-01-13</v>
-      </c>
-      <c r="E94" t="str">
-        <v>Entertainment</v>
-      </c>
-      <c r="F94" t="str">
-        <v/>
-      </c>
-      <c r="G94" t="str">
-        <v>Netflix</v>
-      </c>
-      <c r="H94" t="str">
-        <v>Monthly subscription</v>
-      </c>
-      <c r="I94" t="str">
-        <v>Credit Card</v>
-      </c>
-      <c r="J94" t="str">
-        <v>subscription,ott</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B95" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C95">
-        <v>680</v>
-      </c>
-      <c r="D95" t="str">
-        <v>2026-01-14</v>
-      </c>
-      <c r="E95" t="str">
-        <v>Transport</v>
-      </c>
-      <c r="F95" t="str">
-        <v/>
-      </c>
-      <c r="G95" t="str">
-        <v>Metro Card</v>
-      </c>
-      <c r="H95" t="str">
-        <v>Recharge</v>
-      </c>
-      <c r="I95" t="str">
-        <v>UPI</v>
-      </c>
-      <c r="J95" t="str">
-        <v>metro,commute</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B96" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C96">
-        <v>2750</v>
-      </c>
-      <c r="D96" t="str">
-        <v>2026-01-15</v>
-      </c>
-      <c r="E96" t="str">
-        <v>Food</v>
-      </c>
-      <c r="F96" t="str">
-        <v/>
-      </c>
-      <c r="G96" t="str">
-        <v>Reliance Fresh</v>
-      </c>
-      <c r="H96" t="str">
-        <v>Mid-month groceries</v>
-      </c>
-      <c r="I96" t="str">
-        <v>Card</v>
-      </c>
-      <c r="J96" t="str">
-        <v>groceries,weekly</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="str">
-        <v>HDFC Rewards Card</v>
-      </c>
-      <c r="B97" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C97">
-        <v>1899</v>
-      </c>
-      <c r="D97" t="str">
-        <v>2026-01-16</v>
-      </c>
-      <c r="E97" t="str">
-        <v>Shopping</v>
-      </c>
-      <c r="F97" t="str">
-        <v/>
-      </c>
-      <c r="G97" t="str">
-        <v>Myntra</v>
-      </c>
-      <c r="H97" t="str">
-        <v>Clothing order</v>
-      </c>
-      <c r="I97" t="str">
-        <v>Credit Card</v>
-      </c>
-      <c r="J97" t="str">
-        <v>shopping,fashion</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="str">
-        <v>Cash Wallet</v>
-      </c>
-      <c r="B98" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C98">
-        <v>160</v>
-      </c>
-      <c r="D98" t="str">
-        <v>2026-01-17</v>
-      </c>
-      <c r="E98" t="str">
-        <v>Food</v>
-      </c>
-      <c r="F98" t="str">
-        <v/>
-      </c>
-      <c r="G98" t="str">
-        <v>Tea Point</v>
-      </c>
-      <c r="H98" t="str">
-        <v>Snacks and tea</v>
-      </c>
-      <c r="I98" t="str">
-        <v>Cash</v>
-      </c>
-      <c r="J98" t="str">
-        <v>snacks,cash</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B99" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C99">
-        <v>1450</v>
-      </c>
-      <c r="D99" t="str">
-        <v>2026-01-18</v>
-      </c>
-      <c r="E99" t="str">
-        <v>Utilities</v>
-      </c>
-      <c r="F99" t="str">
-        <v/>
-      </c>
-      <c r="G99" t="str">
-        <v>Jio Mobile</v>
-      </c>
-      <c r="H99" t="str">
-        <v>Mobile recharge and add-ons</v>
-      </c>
-      <c r="I99" t="str">
-        <v>UPI</v>
-      </c>
-      <c r="J99" t="str">
-        <v>mobile,utility</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B100" t="str">
-        <v>Income</v>
-      </c>
-      <c r="C100">
-        <v>6000</v>
-      </c>
-      <c r="D100" t="str">
-        <v>2026-01-19</v>
-      </c>
-      <c r="E100" t="str">
-        <v>Others</v>
-      </c>
-      <c r="F100" t="str">
-        <v/>
-      </c>
-      <c r="G100" t="str">
-        <v>Cashback + Refunds</v>
-      </c>
-      <c r="H100" t="str">
-        <v>Credit card cashback and vendor refund</v>
-      </c>
-      <c r="I100" t="str">
-        <v>Bank Transfer</v>
-      </c>
-      <c r="J100" t="str">
-        <v>refund,cashback</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="str">
-        <v>HDFC Rewards Card</v>
-      </c>
-      <c r="B101" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C101">
-        <v>899</v>
-      </c>
-      <c r="D101" t="str">
-        <v>2026-01-20</v>
-      </c>
-      <c r="E101" t="str">
-        <v>Entertainment</v>
-      </c>
-      <c r="F101" t="str">
-        <v/>
-      </c>
-      <c r="G101" t="str">
-        <v>PVR Cinemas</v>
-      </c>
-      <c r="H101" t="str">
-        <v>Weekend movie</v>
-      </c>
-      <c r="I101" t="str">
-        <v>Credit Card</v>
-      </c>
-      <c r="J101" t="str">
-        <v>movie,leisure</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B102" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C102">
-        <v>2100</v>
-      </c>
-      <c r="D102" t="str">
-        <v>2026-01-21</v>
-      </c>
-      <c r="E102" t="str">
-        <v>Transport</v>
-      </c>
-      <c r="F102" t="str">
-        <v/>
-      </c>
-      <c r="G102" t="str">
-        <v>Indian Oil</v>
-      </c>
-      <c r="H102" t="str">
-        <v>Fuel refill</v>
-      </c>
-      <c r="I102" t="str">
-        <v>Card</v>
-      </c>
-      <c r="J102" t="str">
-        <v>fuel,car</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B103" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C103">
-        <v>3900</v>
-      </c>
-      <c r="D103" t="str">
-        <v>2026-01-22</v>
-      </c>
-      <c r="E103" t="str">
-        <v>Food</v>
-      </c>
-      <c r="F103" t="str">
-        <v/>
-      </c>
-      <c r="G103" t="str">
-        <v>DMart</v>
-      </c>
-      <c r="H103" t="str">
-        <v>Household and groceries</v>
-      </c>
-      <c r="I103" t="str">
-        <v>Card</v>
-      </c>
-      <c r="J103" t="str">
-        <v>groceries,household</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B104" t="str">
-        <v>Transfer</v>
-      </c>
-      <c r="C104">
-        <v>15000</v>
-      </c>
-      <c r="D104" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E104" t="str">
-        <v/>
-      </c>
-      <c r="F104" t="str">
-        <v>Emergency Savings</v>
-      </c>
-      <c r="G104" t="str">
-        <v>Savings Sweep</v>
-      </c>
-      <c r="H104" t="str">
-        <v>Move surplus into emergency savings</v>
-      </c>
-      <c r="I104" t="str">
-        <v>Transfer</v>
-      </c>
-      <c r="J104" t="str">
-        <v>savings,transfer</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v>Emergency Savings</v>
-      </c>
-      <c r="B105" t="str">
-        <v>Income</v>
-      </c>
-      <c r="C105">
-        <v>950</v>
-      </c>
-      <c r="D105" t="str">
-        <v>2026-01-24</v>
-      </c>
-      <c r="E105" t="str">
-        <v>Others</v>
-      </c>
-      <c r="F105" t="str">
-        <v/>
-      </c>
-      <c r="G105" t="str">
-        <v>Interest Credit</v>
-      </c>
-      <c r="H105" t="str">
-        <v>Monthly interest credit</v>
-      </c>
-      <c r="I105" t="str">
-        <v>Bank Transfer</v>
-      </c>
-      <c r="J105" t="str">
-        <v>interest,savings</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="str">
-        <v>HDFC Rewards Card</v>
-      </c>
-      <c r="B106" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C106">
-        <v>1799</v>
-      </c>
-      <c r="D106" t="str">
-        <v>2026-01-25</v>
-      </c>
-      <c r="E106" t="str">
-        <v>Shopping</v>
-      </c>
-      <c r="F106" t="str">
-        <v/>
-      </c>
-      <c r="G106" t="str">
-        <v>Croma</v>
-      </c>
-      <c r="H106" t="str">
-        <v>Electronics accessories</v>
-      </c>
-      <c r="I106" t="str">
-        <v>Credit Card</v>
-      </c>
-      <c r="J106" t="str">
-        <v>electronics,shopping</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B107" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C107">
-        <v>720</v>
-      </c>
-      <c r="D107" t="str">
-        <v>2026-01-26</v>
-      </c>
-      <c r="E107" t="str">
-        <v>Food</v>
-      </c>
-      <c r="F107" t="str">
-        <v/>
-      </c>
-      <c r="G107" t="str">
-        <v>Cafe Coffee Day</v>
-      </c>
-      <c r="H107" t="str">
-        <v>Client catch-up</v>
-      </c>
-      <c r="I107" t="str">
-        <v>UPI</v>
-      </c>
-      <c r="J107" t="str">
-        <v>coffee,meeting</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="str">
-        <v>Cash Wallet</v>
-      </c>
-      <c r="B108" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C108">
-        <v>310</v>
-      </c>
-      <c r="D108" t="str">
-        <v>2026-01-27</v>
-      </c>
-      <c r="E108" t="str">
-        <v>Food</v>
-      </c>
-      <c r="F108" t="str">
-        <v/>
-      </c>
-      <c r="G108" t="str">
-        <v>Street Food</v>
-      </c>
-      <c r="H108" t="str">
-        <v>Quick dinner</v>
-      </c>
-      <c r="I108" t="str">
-        <v>Cash</v>
-      </c>
-      <c r="J108" t="str">
-        <v>food,cash</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B109" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C109">
-        <v>1600</v>
-      </c>
-      <c r="D109" t="str">
-        <v>2026-01-28</v>
-      </c>
-      <c r="E109" t="str">
-        <v>Utilities</v>
-      </c>
-      <c r="F109" t="str">
-        <v/>
-      </c>
-      <c r="G109" t="str">
-        <v>Health Insurance</v>
-      </c>
-      <c r="H109" t="str">
-        <v>Insurance auto debit</v>
-      </c>
-      <c r="I109" t="str">
-        <v>Bank Transfer</v>
-      </c>
-      <c r="J109" t="str">
-        <v>insurance,health</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B110" t="str">
-        <v>Income</v>
-      </c>
-      <c r="C110">
-        <v>98000</v>
-      </c>
-      <c r="D110" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="E110" t="str">
-        <v>Salary</v>
-      </c>
-      <c r="F110" t="str">
-        <v/>
-      </c>
-      <c r="G110" t="str">
-        <v>Employer Payroll</v>
-      </c>
-      <c r="H110" t="str">
-        <v>Monthly salary credit</v>
-      </c>
-      <c r="I110" t="str">
-        <v>Bank Transfer</v>
-      </c>
-      <c r="J110" t="str">
-        <v>salary,monthly</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B111" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C111">
-        <v>28000</v>
-      </c>
-      <c r="D111" t="str">
-        <v>2026-02-03</v>
-      </c>
-      <c r="E111" t="str">
-        <v>Rent</v>
-      </c>
-      <c r="F111" t="str">
-        <v/>
-      </c>
-      <c r="G111" t="str">
-        <v>Sunrise Residency</v>
-      </c>
-      <c r="H111" t="str">
-        <v>Monthly apartment rent</v>
-      </c>
-      <c r="I111" t="str">
-        <v>UPI</v>
-      </c>
-      <c r="J111" t="str">
-        <v>housing,fixed</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B112" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C112">
-        <v>3200</v>
-      </c>
-      <c r="D112" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="E112" t="str">
-        <v>Utilities</v>
-      </c>
-      <c r="F112" t="str">
-        <v/>
-      </c>
-      <c r="G112" t="str">
-        <v>BESCOM</v>
-      </c>
-      <c r="H112" t="str">
-        <v>Electricity bill</v>
-      </c>
-      <c r="I112" t="str">
-        <v>Net Banking</v>
-      </c>
-      <c r="J112" t="str">
-        <v>utilities,bill</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B113" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C113">
-        <v>1199</v>
-      </c>
-      <c r="D113" t="str">
-        <v>2026-02-05</v>
-      </c>
-      <c r="E113" t="str">
-        <v>Utilities</v>
-      </c>
-      <c r="F113" t="str">
-        <v/>
-      </c>
-      <c r="G113" t="str">
-        <v>Airtel Fiber</v>
-      </c>
-      <c r="H113" t="str">
-        <v>Internet payment</v>
-      </c>
-      <c r="I113" t="str">
-        <v>UPI</v>
-      </c>
-      <c r="J113" t="str">
-        <v>internet,utility</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B114" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C114">
-        <v>4800</v>
-      </c>
-      <c r="D114" t="str">
-        <v>2026-02-06</v>
-      </c>
-      <c r="E114" t="str">
-        <v>Food</v>
-      </c>
-      <c r="F114" t="str">
-        <v/>
-      </c>
-      <c r="G114" t="str">
-        <v>BigBasket</v>
-      </c>
-      <c r="H114" t="str">
-        <v>Groceries stock-up</v>
-      </c>
-      <c r="I114" t="str">
-        <v>Card</v>
-      </c>
-      <c r="J114" t="str">
-        <v>groceries,home</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B115" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C115">
-        <v>420</v>
-      </c>
-      <c r="D115" t="str">
-        <v>2026-02-07</v>
-      </c>
-      <c r="E115" t="str">
-        <v>Transport</v>
-      </c>
-      <c r="F115" t="str">
-        <v/>
-      </c>
-      <c r="G115" t="str">
-        <v>Uber</v>
-      </c>
-      <c r="H115" t="str">
-        <v>Office commute</v>
-      </c>
-      <c r="I115" t="str">
-        <v>UPI</v>
-      </c>
-      <c r="J115" t="str">
-        <v>commute,cab</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B116" t="str">
-        <v>Income</v>
-      </c>
-      <c r="C116">
-        <v>12500</v>
-      </c>
-      <c r="D116" t="str">
-        <v>2026-02-08</v>
-      </c>
-      <c r="E116" t="str">
-        <v>Freelance</v>
-      </c>
-      <c r="F116" t="str">
-        <v/>
-      </c>
-      <c r="G116" t="str">
-        <v>Product Design Client</v>
-      </c>
-      <c r="H116" t="str">
-        <v>Freelance milestone payment</v>
-      </c>
-      <c r="I116" t="str">
-        <v>Bank Transfer</v>
-      </c>
-      <c r="J116" t="str">
-        <v>freelance,design</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B117" t="str">
-        <v>Transfer</v>
-      </c>
-      <c r="C117">
-        <v>3500</v>
-      </c>
-      <c r="D117" t="str">
-        <v>2026-02-09</v>
-      </c>
-      <c r="E117" t="str">
-        <v/>
-      </c>
-      <c r="F117" t="str">
-        <v>Cash Wallet</v>
-      </c>
-      <c r="G117" t="str">
-        <v>ATM Withdrawal</v>
-      </c>
-      <c r="H117" t="str">
-        <v>Wallet cash top-up</v>
-      </c>
-      <c r="I117" t="str">
-        <v>Transfer</v>
-      </c>
-      <c r="J117" t="str">
-        <v>cash,transfer</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="str">
-        <v>Cash Wallet</v>
-      </c>
-      <c r="B118" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C118">
-        <v>240</v>
-      </c>
-      <c r="D118" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="E118" t="str">
-        <v>Transport</v>
-      </c>
-      <c r="F118" t="str">
-        <v/>
-      </c>
-      <c r="G118" t="str">
-        <v>Auto Rickshaw</v>
-      </c>
-      <c r="H118" t="str">
-        <v>Local commute</v>
-      </c>
-      <c r="I118" t="str">
-        <v>Cash</v>
-      </c>
-      <c r="J118" t="str">
-        <v>local,transport</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="str">
-        <v>HDFC Rewards Card</v>
-      </c>
-      <c r="B119" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C119">
-        <v>2199</v>
-      </c>
-      <c r="D119" t="str">
-        <v>2026-02-11</v>
-      </c>
-      <c r="E119" t="str">
-        <v>Shopping</v>
-      </c>
-      <c r="F119" t="str">
-        <v/>
-      </c>
-      <c r="G119" t="str">
-        <v>Amazon</v>
-      </c>
-      <c r="H119" t="str">
-        <v>Home office accessories</v>
-      </c>
-      <c r="I119" t="str">
-        <v>Credit Card</v>
-      </c>
-      <c r="J119" t="str">
-        <v>shopping,office</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B120" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C120">
-        <v>950</v>
-      </c>
-      <c r="D120" t="str">
-        <v>2026-02-12</v>
-      </c>
-      <c r="E120" t="str">
-        <v>Food</v>
-      </c>
-      <c r="F120" t="str">
-        <v/>
-      </c>
-      <c r="G120" t="str">
-        <v>Swiggy</v>
-      </c>
-      <c r="H120" t="str">
-        <v>Late dinner order</v>
-      </c>
-      <c r="I120" t="str">
-        <v>UPI</v>
-      </c>
-      <c r="J120" t="str">
-        <v>food,delivery</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="str">
-        <v>HDFC Rewards Card</v>
-      </c>
-      <c r="B121" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C121">
-        <v>499</v>
-      </c>
-      <c r="D121" t="str">
-        <v>2026-02-13</v>
-      </c>
-      <c r="E121" t="str">
-        <v>Entertainment</v>
-      </c>
-      <c r="F121" t="str">
-        <v/>
-      </c>
-      <c r="G121" t="str">
-        <v>Netflix</v>
-      </c>
-      <c r="H121" t="str">
-        <v>Monthly subscription</v>
-      </c>
-      <c r="I121" t="str">
-        <v>Credit Card</v>
-      </c>
-      <c r="J121" t="str">
-        <v>subscription,ott</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B122" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C122">
-        <v>680</v>
-      </c>
-      <c r="D122" t="str">
-        <v>2026-02-14</v>
-      </c>
-      <c r="E122" t="str">
-        <v>Transport</v>
-      </c>
-      <c r="F122" t="str">
-        <v/>
-      </c>
-      <c r="G122" t="str">
-        <v>Metro Card</v>
-      </c>
-      <c r="H122" t="str">
-        <v>Recharge</v>
-      </c>
-      <c r="I122" t="str">
-        <v>UPI</v>
-      </c>
-      <c r="J122" t="str">
-        <v>metro,commute</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B123" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C123">
-        <v>2750</v>
-      </c>
-      <c r="D123" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E123" t="str">
-        <v>Food</v>
-      </c>
-      <c r="F123" t="str">
-        <v/>
-      </c>
-      <c r="G123" t="str">
-        <v>Reliance Fresh</v>
-      </c>
-      <c r="H123" t="str">
-        <v>Mid-month groceries</v>
-      </c>
-      <c r="I123" t="str">
-        <v>Card</v>
-      </c>
-      <c r="J123" t="str">
-        <v>groceries,weekly</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="str">
-        <v>HDFC Rewards Card</v>
-      </c>
-      <c r="B124" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C124">
-        <v>1899</v>
-      </c>
-      <c r="D124" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="E124" t="str">
-        <v>Shopping</v>
-      </c>
-      <c r="F124" t="str">
-        <v/>
-      </c>
-      <c r="G124" t="str">
-        <v>Myntra</v>
-      </c>
-      <c r="H124" t="str">
-        <v>Clothing order</v>
-      </c>
-      <c r="I124" t="str">
-        <v>Credit Card</v>
-      </c>
-      <c r="J124" t="str">
-        <v>shopping,fashion</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="str">
-        <v>Cash Wallet</v>
-      </c>
-      <c r="B125" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C125">
-        <v>160</v>
-      </c>
-      <c r="D125" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="E125" t="str">
-        <v>Food</v>
-      </c>
-      <c r="F125" t="str">
-        <v/>
-      </c>
-      <c r="G125" t="str">
-        <v>Tea Point</v>
-      </c>
-      <c r="H125" t="str">
-        <v>Snacks and tea</v>
-      </c>
-      <c r="I125" t="str">
-        <v>Cash</v>
-      </c>
-      <c r="J125" t="str">
-        <v>snacks,cash</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B126" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C126">
-        <v>1450</v>
-      </c>
-      <c r="D126" t="str">
-        <v>2026-02-18</v>
-      </c>
-      <c r="E126" t="str">
-        <v>Utilities</v>
-      </c>
-      <c r="F126" t="str">
-        <v/>
-      </c>
-      <c r="G126" t="str">
-        <v>Jio Mobile</v>
-      </c>
-      <c r="H126" t="str">
-        <v>Mobile recharge and add-ons</v>
-      </c>
-      <c r="I126" t="str">
-        <v>UPI</v>
-      </c>
-      <c r="J126" t="str">
-        <v>mobile,utility</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B127" t="str">
-        <v>Income</v>
-      </c>
-      <c r="C127">
-        <v>6000</v>
-      </c>
-      <c r="D127" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="E127" t="str">
-        <v>Others</v>
-      </c>
-      <c r="F127" t="str">
-        <v/>
-      </c>
-      <c r="G127" t="str">
-        <v>Cashback + Refunds</v>
-      </c>
-      <c r="H127" t="str">
-        <v>Credit card cashback and vendor refund</v>
-      </c>
-      <c r="I127" t="str">
-        <v>Bank Transfer</v>
-      </c>
-      <c r="J127" t="str">
-        <v>refund,cashback</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="str">
-        <v>HDFC Rewards Card</v>
-      </c>
-      <c r="B128" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C128">
-        <v>899</v>
-      </c>
-      <c r="D128" t="str">
-        <v>2026-02-20</v>
-      </c>
-      <c r="E128" t="str">
-        <v>Entertainment</v>
-      </c>
-      <c r="F128" t="str">
-        <v/>
-      </c>
-      <c r="G128" t="str">
-        <v>PVR Cinemas</v>
-      </c>
-      <c r="H128" t="str">
-        <v>Weekend movie</v>
-      </c>
-      <c r="I128" t="str">
-        <v>Credit Card</v>
-      </c>
-      <c r="J128" t="str">
-        <v>movie,leisure</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B129" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C129">
-        <v>2100</v>
-      </c>
-      <c r="D129" t="str">
-        <v>2026-02-21</v>
-      </c>
-      <c r="E129" t="str">
-        <v>Transport</v>
-      </c>
-      <c r="F129" t="str">
-        <v/>
-      </c>
-      <c r="G129" t="str">
-        <v>Indian Oil</v>
-      </c>
-      <c r="H129" t="str">
-        <v>Fuel refill</v>
-      </c>
-      <c r="I129" t="str">
-        <v>Card</v>
-      </c>
-      <c r="J129" t="str">
-        <v>fuel,car</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B130" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C130">
-        <v>3900</v>
-      </c>
-      <c r="D130" t="str">
-        <v>2026-02-22</v>
-      </c>
-      <c r="E130" t="str">
-        <v>Food</v>
-      </c>
-      <c r="F130" t="str">
-        <v/>
-      </c>
-      <c r="G130" t="str">
-        <v>DMart</v>
-      </c>
-      <c r="H130" t="str">
-        <v>Household and groceries</v>
-      </c>
-      <c r="I130" t="str">
-        <v>Card</v>
-      </c>
-      <c r="J130" t="str">
-        <v>groceries,household</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B131" t="str">
-        <v>Transfer</v>
-      </c>
-      <c r="C131">
-        <v>15000</v>
-      </c>
-      <c r="D131" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="E131" t="str">
-        <v/>
-      </c>
-      <c r="F131" t="str">
-        <v>Emergency Savings</v>
-      </c>
-      <c r="G131" t="str">
-        <v>Savings Sweep</v>
-      </c>
-      <c r="H131" t="str">
-        <v>Move surplus into emergency savings</v>
-      </c>
-      <c r="I131" t="str">
-        <v>Transfer</v>
-      </c>
-      <c r="J131" t="str">
-        <v>savings,transfer</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="str">
-        <v>Emergency Savings</v>
-      </c>
-      <c r="B132" t="str">
-        <v>Income</v>
-      </c>
-      <c r="C132">
-        <v>950</v>
-      </c>
-      <c r="D132" t="str">
-        <v>2026-02-24</v>
-      </c>
-      <c r="E132" t="str">
-        <v>Others</v>
-      </c>
-      <c r="F132" t="str">
-        <v/>
-      </c>
-      <c r="G132" t="str">
-        <v>Interest Credit</v>
-      </c>
-      <c r="H132" t="str">
-        <v>Monthly interest credit</v>
-      </c>
-      <c r="I132" t="str">
-        <v>Bank Transfer</v>
-      </c>
-      <c r="J132" t="str">
-        <v>interest,savings</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="str">
-        <v>HDFC Rewards Card</v>
-      </c>
-      <c r="B133" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C133">
-        <v>1799</v>
-      </c>
-      <c r="D133" t="str">
-        <v>2026-02-25</v>
-      </c>
-      <c r="E133" t="str">
-        <v>Shopping</v>
-      </c>
-      <c r="F133" t="str">
-        <v/>
-      </c>
-      <c r="G133" t="str">
-        <v>Croma</v>
-      </c>
-      <c r="H133" t="str">
-        <v>Electronics accessories</v>
-      </c>
-      <c r="I133" t="str">
-        <v>Credit Card</v>
-      </c>
-      <c r="J133" t="str">
-        <v>electronics,shopping</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B134" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C134">
-        <v>720</v>
-      </c>
-      <c r="D134" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="E134" t="str">
-        <v>Food</v>
-      </c>
-      <c r="F134" t="str">
-        <v/>
-      </c>
-      <c r="G134" t="str">
-        <v>Cafe Coffee Day</v>
-      </c>
-      <c r="H134" t="str">
-        <v>Client catch-up</v>
-      </c>
-      <c r="I134" t="str">
-        <v>UPI</v>
-      </c>
-      <c r="J134" t="str">
-        <v>coffee,meeting</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="str">
-        <v>Cash Wallet</v>
-      </c>
-      <c r="B135" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C135">
-        <v>310</v>
-      </c>
-      <c r="D135" t="str">
-        <v>2026-02-27</v>
-      </c>
-      <c r="E135" t="str">
-        <v>Food</v>
-      </c>
-      <c r="F135" t="str">
-        <v/>
-      </c>
-      <c r="G135" t="str">
-        <v>Street Food</v>
-      </c>
-      <c r="H135" t="str">
-        <v>Quick dinner</v>
-      </c>
-      <c r="I135" t="str">
-        <v>Cash</v>
-      </c>
-      <c r="J135" t="str">
-        <v>food,cash</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B136" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C136">
-        <v>1600</v>
-      </c>
-      <c r="D136" t="str">
-        <v>2026-02-28</v>
-      </c>
-      <c r="E136" t="str">
-        <v>Utilities</v>
-      </c>
-      <c r="F136" t="str">
-        <v/>
-      </c>
-      <c r="G136" t="str">
-        <v>Health Insurance</v>
-      </c>
-      <c r="H136" t="str">
-        <v>Insurance auto debit</v>
-      </c>
-      <c r="I136" t="str">
-        <v>Bank Transfer</v>
-      </c>
-      <c r="J136" t="str">
-        <v>insurance,health</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B137" t="str">
-        <v>Income</v>
-      </c>
-      <c r="C137">
-        <v>98000</v>
-      </c>
-      <c r="D137" t="str">
-        <v>2026-03-01</v>
-      </c>
-      <c r="E137" t="str">
-        <v>Salary</v>
-      </c>
-      <c r="F137" t="str">
-        <v/>
-      </c>
-      <c r="G137" t="str">
-        <v>Employer Payroll</v>
-      </c>
-      <c r="H137" t="str">
-        <v>Monthly salary credit</v>
-      </c>
-      <c r="I137" t="str">
-        <v>Bank Transfer</v>
-      </c>
-      <c r="J137" t="str">
-        <v>salary,monthly</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B138" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C138">
-        <v>28000</v>
-      </c>
-      <c r="D138" t="str">
-        <v>2026-03-03</v>
-      </c>
-      <c r="E138" t="str">
-        <v>Rent</v>
-      </c>
-      <c r="F138" t="str">
-        <v/>
-      </c>
-      <c r="G138" t="str">
-        <v>Sunrise Residency</v>
-      </c>
-      <c r="H138" t="str">
-        <v>Monthly apartment rent</v>
-      </c>
-      <c r="I138" t="str">
-        <v>UPI</v>
-      </c>
-      <c r="J138" t="str">
-        <v>housing,fixed</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B139" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C139">
-        <v>3200</v>
-      </c>
-      <c r="D139" t="str">
-        <v>2026-03-04</v>
-      </c>
-      <c r="E139" t="str">
-        <v>Utilities</v>
-      </c>
-      <c r="F139" t="str">
-        <v/>
-      </c>
-      <c r="G139" t="str">
-        <v>BESCOM</v>
-      </c>
-      <c r="H139" t="str">
-        <v>Electricity bill</v>
-      </c>
-      <c r="I139" t="str">
-        <v>Net Banking</v>
-      </c>
-      <c r="J139" t="str">
-        <v>utilities,bill</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B140" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C140">
-        <v>1199</v>
-      </c>
-      <c r="D140" t="str">
-        <v>2026-03-05</v>
-      </c>
-      <c r="E140" t="str">
-        <v>Utilities</v>
-      </c>
-      <c r="F140" t="str">
-        <v/>
-      </c>
-      <c r="G140" t="str">
-        <v>Airtel Fiber</v>
-      </c>
-      <c r="H140" t="str">
-        <v>Internet payment</v>
-      </c>
-      <c r="I140" t="str">
-        <v>UPI</v>
-      </c>
-      <c r="J140" t="str">
-        <v>internet,utility</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B141" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C141">
-        <v>4800</v>
-      </c>
-      <c r="D141" t="str">
-        <v>2026-03-06</v>
-      </c>
-      <c r="E141" t="str">
-        <v>Food</v>
-      </c>
-      <c r="F141" t="str">
-        <v/>
-      </c>
-      <c r="G141" t="str">
-        <v>BigBasket</v>
-      </c>
-      <c r="H141" t="str">
-        <v>Groceries stock-up</v>
-      </c>
-      <c r="I141" t="str">
-        <v>Card</v>
-      </c>
-      <c r="J141" t="str">
-        <v>groceries,home</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B142" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C142">
-        <v>420</v>
-      </c>
-      <c r="D142" t="str">
-        <v>2026-03-07</v>
-      </c>
-      <c r="E142" t="str">
-        <v>Transport</v>
-      </c>
-      <c r="F142" t="str">
-        <v/>
-      </c>
-      <c r="G142" t="str">
-        <v>Uber</v>
-      </c>
-      <c r="H142" t="str">
-        <v>Office commute</v>
-      </c>
-      <c r="I142" t="str">
-        <v>UPI</v>
-      </c>
-      <c r="J142" t="str">
-        <v>commute,cab</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B143" t="str">
-        <v>Income</v>
-      </c>
-      <c r="C143">
-        <v>12500</v>
-      </c>
-      <c r="D143" t="str">
-        <v>2026-03-08</v>
-      </c>
-      <c r="E143" t="str">
-        <v>Freelance</v>
-      </c>
-      <c r="F143" t="str">
-        <v/>
-      </c>
-      <c r="G143" t="str">
-        <v>Product Design Client</v>
-      </c>
-      <c r="H143" t="str">
-        <v>Freelance milestone payment</v>
-      </c>
-      <c r="I143" t="str">
-        <v>Bank Transfer</v>
-      </c>
-      <c r="J143" t="str">
-        <v>freelance,design</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B144" t="str">
-        <v>Transfer</v>
-      </c>
-      <c r="C144">
-        <v>3500</v>
-      </c>
-      <c r="D144" t="str">
-        <v>2026-03-09</v>
-      </c>
-      <c r="E144" t="str">
-        <v/>
-      </c>
-      <c r="F144" t="str">
-        <v>Cash Wallet</v>
-      </c>
-      <c r="G144" t="str">
-        <v>ATM Withdrawal</v>
-      </c>
-      <c r="H144" t="str">
-        <v>Wallet cash top-up</v>
-      </c>
-      <c r="I144" t="str">
-        <v>Transfer</v>
-      </c>
-      <c r="J144" t="str">
-        <v>cash,transfer</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="str">
-        <v>Cash Wallet</v>
-      </c>
-      <c r="B145" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C145">
-        <v>240</v>
-      </c>
-      <c r="D145" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="E145" t="str">
-        <v>Transport</v>
-      </c>
-      <c r="F145" t="str">
-        <v/>
-      </c>
-      <c r="G145" t="str">
-        <v>Auto Rickshaw</v>
-      </c>
-      <c r="H145" t="str">
-        <v>Local commute</v>
-      </c>
-      <c r="I145" t="str">
-        <v>Cash</v>
-      </c>
-      <c r="J145" t="str">
-        <v>local,transport</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="str">
-        <v>HDFC Rewards Card</v>
-      </c>
-      <c r="B146" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C146">
-        <v>2199</v>
-      </c>
-      <c r="D146" t="str">
-        <v>2026-03-11</v>
-      </c>
-      <c r="E146" t="str">
-        <v>Shopping</v>
-      </c>
-      <c r="F146" t="str">
-        <v/>
-      </c>
-      <c r="G146" t="str">
-        <v>Amazon</v>
-      </c>
-      <c r="H146" t="str">
-        <v>Home office accessories</v>
-      </c>
-      <c r="I146" t="str">
-        <v>Credit Card</v>
-      </c>
-      <c r="J146" t="str">
-        <v>shopping,office</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B147" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C147">
-        <v>950</v>
-      </c>
-      <c r="D147" t="str">
-        <v>2026-03-12</v>
-      </c>
-      <c r="E147" t="str">
-        <v>Food</v>
-      </c>
-      <c r="F147" t="str">
-        <v/>
-      </c>
-      <c r="G147" t="str">
-        <v>Swiggy</v>
-      </c>
-      <c r="H147" t="str">
-        <v>Late dinner order</v>
-      </c>
-      <c r="I147" t="str">
-        <v>UPI</v>
-      </c>
-      <c r="J147" t="str">
-        <v>food,delivery</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="str">
-        <v>HDFC Rewards Card</v>
-      </c>
-      <c r="B148" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C148">
-        <v>499</v>
-      </c>
-      <c r="D148" t="str">
-        <v>2026-03-13</v>
-      </c>
-      <c r="E148" t="str">
-        <v>Entertainment</v>
-      </c>
-      <c r="F148" t="str">
-        <v/>
-      </c>
-      <c r="G148" t="str">
-        <v>Netflix</v>
-      </c>
-      <c r="H148" t="str">
-        <v>Monthly subscription</v>
-      </c>
-      <c r="I148" t="str">
-        <v>Credit Card</v>
-      </c>
-      <c r="J148" t="str">
-        <v>subscription,ott</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B149" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C149">
-        <v>680</v>
-      </c>
-      <c r="D149" t="str">
-        <v>2026-03-14</v>
-      </c>
-      <c r="E149" t="str">
-        <v>Transport</v>
-      </c>
-      <c r="F149" t="str">
-        <v/>
-      </c>
-      <c r="G149" t="str">
-        <v>Metro Card</v>
-      </c>
-      <c r="H149" t="str">
-        <v>Recharge</v>
-      </c>
-      <c r="I149" t="str">
-        <v>UPI</v>
-      </c>
-      <c r="J149" t="str">
-        <v>metro,commute</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B150" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C150">
-        <v>2750</v>
-      </c>
-      <c r="D150" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="E150" t="str">
-        <v>Food</v>
-      </c>
-      <c r="F150" t="str">
-        <v/>
-      </c>
-      <c r="G150" t="str">
-        <v>Reliance Fresh</v>
-      </c>
-      <c r="H150" t="str">
-        <v>Mid-month groceries</v>
-      </c>
-      <c r="I150" t="str">
-        <v>Card</v>
-      </c>
-      <c r="J150" t="str">
-        <v>groceries,weekly</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="str">
-        <v>HDFC Rewards Card</v>
-      </c>
-      <c r="B151" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C151">
-        <v>1899</v>
-      </c>
-      <c r="D151" t="str">
-        <v>2026-03-16</v>
-      </c>
-      <c r="E151" t="str">
-        <v>Shopping</v>
-      </c>
-      <c r="F151" t="str">
-        <v/>
-      </c>
-      <c r="G151" t="str">
-        <v>Myntra</v>
-      </c>
-      <c r="H151" t="str">
-        <v>Clothing order</v>
-      </c>
-      <c r="I151" t="str">
-        <v>Credit Card</v>
-      </c>
-      <c r="J151" t="str">
-        <v>shopping,fashion</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="str">
-        <v>Cash Wallet</v>
-      </c>
-      <c r="B152" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C152">
-        <v>160</v>
-      </c>
-      <c r="D152" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="E152" t="str">
-        <v>Food</v>
-      </c>
-      <c r="F152" t="str">
-        <v/>
-      </c>
-      <c r="G152" t="str">
-        <v>Tea Point</v>
-      </c>
-      <c r="H152" t="str">
-        <v>Snacks and tea</v>
-      </c>
-      <c r="I152" t="str">
-        <v>Cash</v>
-      </c>
-      <c r="J152" t="str">
-        <v>snacks,cash</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B153" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C153">
-        <v>1450</v>
-      </c>
-      <c r="D153" t="str">
-        <v>2026-03-18</v>
-      </c>
-      <c r="E153" t="str">
-        <v>Utilities</v>
-      </c>
-      <c r="F153" t="str">
-        <v/>
-      </c>
-      <c r="G153" t="str">
-        <v>Jio Mobile</v>
-      </c>
-      <c r="H153" t="str">
-        <v>Mobile recharge and add-ons</v>
-      </c>
-      <c r="I153" t="str">
-        <v>UPI</v>
-      </c>
-      <c r="J153" t="str">
-        <v>mobile,utility</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B154" t="str">
-        <v>Income</v>
-      </c>
-      <c r="C154">
-        <v>6000</v>
-      </c>
-      <c r="D154" t="str">
-        <v>2026-03-19</v>
-      </c>
-      <c r="E154" t="str">
-        <v>Others</v>
-      </c>
-      <c r="F154" t="str">
-        <v/>
-      </c>
-      <c r="G154" t="str">
-        <v>Cashback + Refunds</v>
-      </c>
-      <c r="H154" t="str">
-        <v>Credit card cashback and vendor refund</v>
-      </c>
-      <c r="I154" t="str">
-        <v>Bank Transfer</v>
-      </c>
-      <c r="J154" t="str">
-        <v>refund,cashback</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="str">
-        <v>HDFC Rewards Card</v>
-      </c>
-      <c r="B155" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C155">
-        <v>899</v>
-      </c>
-      <c r="D155" t="str">
-        <v>2026-03-20</v>
-      </c>
-      <c r="E155" t="str">
-        <v>Entertainment</v>
-      </c>
-      <c r="F155" t="str">
-        <v/>
-      </c>
-      <c r="G155" t="str">
-        <v>PVR Cinemas</v>
-      </c>
-      <c r="H155" t="str">
-        <v>Weekend movie</v>
-      </c>
-      <c r="I155" t="str">
-        <v>Credit Card</v>
-      </c>
-      <c r="J155" t="str">
-        <v>movie,leisure</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B156" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C156">
-        <v>2100</v>
-      </c>
-      <c r="D156" t="str">
-        <v>2026-03-21</v>
-      </c>
-      <c r="E156" t="str">
-        <v>Transport</v>
-      </c>
-      <c r="F156" t="str">
-        <v/>
-      </c>
-      <c r="G156" t="str">
-        <v>Indian Oil</v>
-      </c>
-      <c r="H156" t="str">
-        <v>Fuel refill</v>
-      </c>
-      <c r="I156" t="str">
-        <v>Card</v>
-      </c>
-      <c r="J156" t="str">
-        <v>fuel,car</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B157" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C157">
-        <v>3900</v>
-      </c>
-      <c r="D157" t="str">
-        <v>2026-03-22</v>
-      </c>
-      <c r="E157" t="str">
-        <v>Food</v>
-      </c>
-      <c r="F157" t="str">
-        <v/>
-      </c>
-      <c r="G157" t="str">
-        <v>DMart</v>
-      </c>
-      <c r="H157" t="str">
-        <v>Household and groceries</v>
-      </c>
-      <c r="I157" t="str">
-        <v>Card</v>
-      </c>
-      <c r="J157" t="str">
-        <v>groceries,household</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B158" t="str">
-        <v>Transfer</v>
-      </c>
-      <c r="C158">
-        <v>15000</v>
-      </c>
-      <c r="D158" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E158" t="str">
-        <v/>
-      </c>
-      <c r="F158" t="str">
-        <v>Emergency Savings</v>
-      </c>
-      <c r="G158" t="str">
-        <v>Savings Sweep</v>
-      </c>
-      <c r="H158" t="str">
-        <v>Move surplus into emergency savings</v>
-      </c>
-      <c r="I158" t="str">
-        <v>Transfer</v>
-      </c>
-      <c r="J158" t="str">
-        <v>savings,transfer</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="str">
-        <v>Emergency Savings</v>
-      </c>
-      <c r="B159" t="str">
-        <v>Income</v>
-      </c>
-      <c r="C159">
-        <v>950</v>
-      </c>
-      <c r="D159" t="str">
-        <v>2026-03-24</v>
-      </c>
-      <c r="E159" t="str">
-        <v>Others</v>
-      </c>
-      <c r="F159" t="str">
-        <v/>
-      </c>
-      <c r="G159" t="str">
-        <v>Interest Credit</v>
-      </c>
-      <c r="H159" t="str">
-        <v>Monthly interest credit</v>
-      </c>
-      <c r="I159" t="str">
-        <v>Bank Transfer</v>
-      </c>
-      <c r="J159" t="str">
-        <v>interest,savings</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="str">
-        <v>HDFC Rewards Card</v>
-      </c>
-      <c r="B160" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C160">
-        <v>1799</v>
-      </c>
-      <c r="D160" t="str">
-        <v>2026-03-25</v>
-      </c>
-      <c r="E160" t="str">
-        <v>Shopping</v>
-      </c>
-      <c r="F160" t="str">
-        <v/>
-      </c>
-      <c r="G160" t="str">
-        <v>Croma</v>
-      </c>
-      <c r="H160" t="str">
-        <v>Electronics accessories</v>
-      </c>
-      <c r="I160" t="str">
-        <v>Credit Card</v>
-      </c>
-      <c r="J160" t="str">
-        <v>electronics,shopping</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B161" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C161">
-        <v>720</v>
-      </c>
-      <c r="D161" t="str">
-        <v>2026-03-26</v>
-      </c>
-      <c r="E161" t="str">
-        <v>Food</v>
-      </c>
-      <c r="F161" t="str">
-        <v/>
-      </c>
-      <c r="G161" t="str">
-        <v>Cafe Coffee Day</v>
-      </c>
-      <c r="H161" t="str">
-        <v>Client catch-up</v>
-      </c>
-      <c r="I161" t="str">
-        <v>UPI</v>
-      </c>
-      <c r="J161" t="str">
-        <v>coffee,meeting</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="str">
-        <v>Cash Wallet</v>
-      </c>
-      <c r="B162" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C162">
-        <v>310</v>
-      </c>
-      <c r="D162" t="str">
-        <v>2026-03-27</v>
-      </c>
-      <c r="E162" t="str">
-        <v>Food</v>
-      </c>
-      <c r="F162" t="str">
-        <v/>
-      </c>
-      <c r="G162" t="str">
-        <v>Street Food</v>
-      </c>
-      <c r="H162" t="str">
-        <v>Quick dinner</v>
-      </c>
-      <c r="I162" t="str">
-        <v>Cash</v>
-      </c>
-      <c r="J162" t="str">
-        <v>food,cash</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="str">
-        <v>Axis Salary Account</v>
-      </c>
-      <c r="B163" t="str">
-        <v>Expense</v>
-      </c>
-      <c r="C163">
-        <v>1600</v>
-      </c>
-      <c r="D163" t="str">
-        <v>2026-03-28</v>
-      </c>
-      <c r="E163" t="str">
-        <v>Utilities</v>
-      </c>
-      <c r="F163" t="str">
-        <v/>
-      </c>
-      <c r="G163" t="str">
-        <v>Health Insurance</v>
-      </c>
-      <c r="H163" t="str">
-        <v>Insurance auto debit</v>
-      </c>
-      <c r="I163" t="str">
-        <v>Bank Transfer</v>
-      </c>
-      <c r="J163" t="str">
-        <v>insurance,health</v>
+        <v>bonus,income</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J163"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J91"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/sample-onboarding-import.xlsx
+++ b/public/sample-onboarding-import.xlsx
@@ -404,72 +404,72 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Name</v>
+        <v>name</v>
       </c>
       <c r="B1" t="str">
-        <v>Type</v>
+        <v>type</v>
       </c>
       <c r="C1" t="str">
-        <v>OpeningBalance</v>
+        <v>openingBalance</v>
       </c>
       <c r="D1" t="str">
-        <v>InstitutionName</v>
+        <v>institutionName</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B2" t="str">
         <v>Bank</v>
       </c>
       <c r="C2">
-        <v>125000</v>
+        <v>42000</v>
       </c>
       <c r="D2" t="str">
-        <v>Axis Bank</v>
+        <v>HDFC Bank</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>Reserve Savings</v>
       </c>
       <c r="B3" t="str">
-        <v>CreditCard</v>
+        <v>Savings</v>
       </c>
       <c r="C3">
-        <v>-12000</v>
+        <v>65000</v>
       </c>
       <c r="D3" t="str">
-        <v>HDFC Bank</v>
+        <v>ICICI Bank</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Cash Wallet</v>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="B4" t="str">
-        <v>CashWallet</v>
+        <v>CreditCard</v>
       </c>
       <c r="C4">
-        <v>4500</v>
+        <v>-4500</v>
       </c>
       <c r="D4" t="str">
-        <v>Cash</v>
+        <v>Axis Bank</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Emergency Savings</v>
+        <v>Pocket Cash</v>
       </c>
       <c r="B5" t="str">
-        <v>Savings</v>
+        <v>CashWallet</v>
       </c>
       <c r="C5">
-        <v>180000</v>
+        <v>2500</v>
       </c>
       <c r="D5" t="str">
-        <v>ICICI Bank</v>
+        <v>Wallet</v>
       </c>
     </row>
   </sheetData>
@@ -481,34 +481,31 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:E43"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Category</v>
+        <v>category</v>
       </c>
       <c r="B1" t="str">
-        <v>Amount</v>
+        <v>amount</v>
       </c>
       <c r="C1" t="str">
-        <v>Month</v>
+        <v>month</v>
       </c>
       <c r="D1" t="str">
-        <v>Year</v>
+        <v>year</v>
       </c>
       <c r="E1" t="str">
-        <v>AlertThresholdPercent</v>
-      </c>
-      <c r="F1" t="str">
-        <v>AccountName</v>
+        <v>alertThresholdPercent</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Food</v>
+        <v>Rent</v>
       </c>
       <c r="B2">
-        <v>12000</v>
+        <v>20000</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -519,16 +516,13 @@
       <c r="E2">
         <v>80</v>
       </c>
-      <c r="F2" t="str">
-        <v>Axis Salary Account</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Transport</v>
+        <v>Groceries</v>
       </c>
       <c r="B3">
-        <v>7000</v>
+        <v>9000</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -539,16 +533,13 @@
       <c r="E3">
         <v>80</v>
       </c>
-      <c r="F3" t="str">
-        <v>Axis Salary Account</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Shopping</v>
+        <v>Dining</v>
       </c>
       <c r="B4">
-        <v>9000</v>
+        <v>5200</v>
       </c>
       <c r="C4">
         <v>10</v>
@@ -557,18 +548,15 @@
         <v>2025</v>
       </c>
       <c r="E4">
-        <v>85</v>
-      </c>
-      <c r="F4" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Utilities</v>
+        <v>Transport</v>
       </c>
       <c r="B5">
-        <v>6000</v>
+        <v>4200</v>
       </c>
       <c r="C5">
         <v>10</v>
@@ -579,16 +567,13 @@
       <c r="E5">
         <v>80</v>
       </c>
-      <c r="F5" t="str">
-        <v>Axis Salary Account</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Entertainment</v>
+        <v>Utilities</v>
       </c>
       <c r="B6">
-        <v>5000</v>
+        <v>4300</v>
       </c>
       <c r="C6">
         <v>10</v>
@@ -597,18 +582,15 @@
         <v>2025</v>
       </c>
       <c r="E6">
-        <v>85</v>
-      </c>
-      <c r="F6" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Health</v>
+        <v>Shopping</v>
       </c>
       <c r="B7">
-        <v>4500</v>
+        <v>6200</v>
       </c>
       <c r="C7">
         <v>10</v>
@@ -619,19 +601,16 @@
       <c r="E7">
         <v>80</v>
       </c>
-      <c r="F7" t="str">
-        <v>Axis Salary Account</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Food</v>
+        <v>Entertainment</v>
       </c>
       <c r="B8">
-        <v>12000</v>
+        <v>2400</v>
       </c>
       <c r="C8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D8">
         <v>2025</v>
@@ -639,16 +618,13 @@
       <c r="E8">
         <v>80</v>
       </c>
-      <c r="F8" t="str">
-        <v>Axis Salary Account</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Transport</v>
+        <v>Rent</v>
       </c>
       <c r="B9">
-        <v>7000</v>
+        <v>20000</v>
       </c>
       <c r="C9">
         <v>11</v>
@@ -659,13 +635,10 @@
       <c r="E9">
         <v>80</v>
       </c>
-      <c r="F9" t="str">
-        <v>Axis Salary Account</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Shopping</v>
+        <v>Groceries</v>
       </c>
       <c r="B10">
         <v>9000</v>
@@ -677,18 +650,15 @@
         <v>2025</v>
       </c>
       <c r="E10">
-        <v>85</v>
-      </c>
-      <c r="F10" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Utilities</v>
+        <v>Dining</v>
       </c>
       <c r="B11">
-        <v>6000</v>
+        <v>5200</v>
       </c>
       <c r="C11">
         <v>11</v>
@@ -699,16 +669,13 @@
       <c r="E11">
         <v>80</v>
       </c>
-      <c r="F11" t="str">
-        <v>Axis Salary Account</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Entertainment</v>
+        <v>Transport</v>
       </c>
       <c r="B12">
-        <v>5000</v>
+        <v>4200</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -717,18 +684,15 @@
         <v>2025</v>
       </c>
       <c r="E12">
-        <v>85</v>
-      </c>
-      <c r="F12" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Health</v>
+        <v>Utilities</v>
       </c>
       <c r="B13">
-        <v>4500</v>
+        <v>4300</v>
       </c>
       <c r="C13">
         <v>11</v>
@@ -739,19 +703,16 @@
       <c r="E13">
         <v>80</v>
       </c>
-      <c r="F13" t="str">
-        <v>Axis Salary Account</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Food</v>
+        <v>Shopping</v>
       </c>
       <c r="B14">
-        <v>12000</v>
+        <v>6200</v>
       </c>
       <c r="C14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D14">
         <v>2025</v>
@@ -759,19 +720,16 @@
       <c r="E14">
         <v>80</v>
       </c>
-      <c r="F14" t="str">
-        <v>Axis Salary Account</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Transport</v>
+        <v>Entertainment</v>
       </c>
       <c r="B15">
-        <v>7000</v>
+        <v>2400</v>
       </c>
       <c r="C15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D15">
         <v>2025</v>
@@ -779,16 +737,13 @@
       <c r="E15">
         <v>80</v>
       </c>
-      <c r="F15" t="str">
-        <v>Axis Salary Account</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Shopping</v>
+        <v>Rent</v>
       </c>
       <c r="B16">
-        <v>9000</v>
+        <v>20000</v>
       </c>
       <c r="C16">
         <v>12</v>
@@ -797,18 +752,15 @@
         <v>2025</v>
       </c>
       <c r="E16">
-        <v>85</v>
-      </c>
-      <c r="F16" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Utilities</v>
+        <v>Groceries</v>
       </c>
       <c r="B17">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="C17">
         <v>12</v>
@@ -819,16 +771,13 @@
       <c r="E17">
         <v>80</v>
       </c>
-      <c r="F17" t="str">
-        <v>Axis Salary Account</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Entertainment</v>
+        <v>Dining</v>
       </c>
       <c r="B18">
-        <v>5000</v>
+        <v>5200</v>
       </c>
       <c r="C18">
         <v>12</v>
@@ -837,18 +786,15 @@
         <v>2025</v>
       </c>
       <c r="E18">
-        <v>85</v>
-      </c>
-      <c r="F18" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Health</v>
+        <v>Transport</v>
       </c>
       <c r="B19">
-        <v>4500</v>
+        <v>4200</v>
       </c>
       <c r="C19">
         <v>12</v>
@@ -859,76 +805,64 @@
       <c r="E19">
         <v>80</v>
       </c>
-      <c r="F19" t="str">
-        <v>Axis Salary Account</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Food</v>
+        <v>Utilities</v>
       </c>
       <c r="B20">
-        <v>12000</v>
+        <v>4300</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D20">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E20">
         <v>80</v>
       </c>
-      <c r="F20" t="str">
-        <v>Axis Salary Account</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Transport</v>
+        <v>Shopping</v>
       </c>
       <c r="B21">
-        <v>7000</v>
+        <v>6200</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D21">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E21">
         <v>80</v>
       </c>
-      <c r="F21" t="str">
-        <v>Axis Salary Account</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Shopping</v>
+        <v>Entertainment</v>
       </c>
       <c r="B22">
-        <v>9000</v>
+        <v>2400</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D22">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E22">
-        <v>85</v>
-      </c>
-      <c r="F22" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Utilities</v>
+        <v>Rent</v>
       </c>
       <c r="B23">
-        <v>6000</v>
+        <v>20000</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -939,16 +873,13 @@
       <c r="E23">
         <v>80</v>
       </c>
-      <c r="F23" t="str">
-        <v>Axis Salary Account</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Entertainment</v>
+        <v>Groceries</v>
       </c>
       <c r="B24">
-        <v>5000</v>
+        <v>9000</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -957,18 +888,15 @@
         <v>2026</v>
       </c>
       <c r="E24">
-        <v>85</v>
-      </c>
-      <c r="F24" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Health</v>
+        <v>Dining</v>
       </c>
       <c r="B25">
-        <v>4500</v>
+        <v>5200</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -979,19 +907,16 @@
       <c r="E25">
         <v>80</v>
       </c>
-      <c r="F25" t="str">
-        <v>Axis Salary Account</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Food</v>
+        <v>Transport</v>
       </c>
       <c r="B26">
-        <v>12000</v>
+        <v>4200</v>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26">
         <v>2026</v>
@@ -999,28 +924,22 @@
       <c r="E26">
         <v>80</v>
       </c>
-      <c r="F26" t="str">
-        <v>Axis Salary Account</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Transport</v>
+        <v>Utilities</v>
       </c>
       <c r="B27">
-        <v>7000</v>
+        <v>4300</v>
       </c>
       <c r="C27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27">
         <v>2026</v>
       </c>
       <c r="E27">
         <v>80</v>
-      </c>
-      <c r="F27" t="str">
-        <v>Axis Salary Account</v>
       </c>
     </row>
     <row r="28">
@@ -1028,30 +947,27 @@
         <v>Shopping</v>
       </c>
       <c r="B28">
-        <v>9000</v>
+        <v>6200</v>
       </c>
       <c r="C28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28">
         <v>2026</v>
       </c>
       <c r="E28">
-        <v>85</v>
-      </c>
-      <c r="F28" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Utilities</v>
+        <v>Entertainment</v>
       </c>
       <c r="B29">
-        <v>6000</v>
+        <v>2400</v>
       </c>
       <c r="C29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29">
         <v>2026</v>
@@ -1059,16 +975,13 @@
       <c r="E29">
         <v>80</v>
       </c>
-      <c r="F29" t="str">
-        <v>Axis Salary Account</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Entertainment</v>
+        <v>Rent</v>
       </c>
       <c r="B30">
-        <v>5000</v>
+        <v>20000</v>
       </c>
       <c r="C30">
         <v>2</v>
@@ -1077,18 +990,15 @@
         <v>2026</v>
       </c>
       <c r="E30">
-        <v>85</v>
-      </c>
-      <c r="F30" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Health</v>
+        <v>Groceries</v>
       </c>
       <c r="B31">
-        <v>4500</v>
+        <v>9000</v>
       </c>
       <c r="C31">
         <v>2</v>
@@ -1099,28 +1009,22 @@
       <c r="E31">
         <v>80</v>
       </c>
-      <c r="F31" t="str">
-        <v>Axis Salary Account</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Food</v>
+        <v>Dining</v>
       </c>
       <c r="B32">
-        <v>15000</v>
+        <v>5200</v>
       </c>
       <c r="C32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D32">
         <v>2026</v>
       </c>
       <c r="E32">
         <v>80</v>
-      </c>
-      <c r="F32" t="str">
-        <v>Axis Salary Account</v>
       </c>
     </row>
     <row r="33">
@@ -1128,10 +1032,10 @@
         <v>Transport</v>
       </c>
       <c r="B33">
-        <v>7000</v>
+        <v>4200</v>
       </c>
       <c r="C33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D33">
         <v>2026</v>
@@ -1139,48 +1043,39 @@
       <c r="E33">
         <v>80</v>
       </c>
-      <c r="F33" t="str">
-        <v>Axis Salary Account</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Shopping</v>
+        <v>Utilities</v>
       </c>
       <c r="B34">
-        <v>11000</v>
+        <v>4300</v>
       </c>
       <c r="C34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D34">
         <v>2026</v>
       </c>
       <c r="E34">
-        <v>85</v>
-      </c>
-      <c r="F34" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Utilities</v>
+        <v>Shopping</v>
       </c>
       <c r="B35">
-        <v>6000</v>
+        <v>6200</v>
       </c>
       <c r="C35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D35">
         <v>2026</v>
       </c>
       <c r="E35">
         <v>80</v>
-      </c>
-      <c r="F35" t="str">
-        <v>Axis Salary Account</v>
       </c>
     </row>
     <row r="36">
@@ -1188,27 +1083,24 @@
         <v>Entertainment</v>
       </c>
       <c r="B36">
-        <v>5000</v>
+        <v>2400</v>
       </c>
       <c r="C36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D36">
         <v>2026</v>
       </c>
       <c r="E36">
-        <v>85</v>
-      </c>
-      <c r="F36" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Health</v>
+        <v>Rent</v>
       </c>
       <c r="B37">
-        <v>4500</v>
+        <v>20000</v>
       </c>
       <c r="C37">
         <v>3</v>
@@ -1219,13 +1111,112 @@
       <c r="E37">
         <v>80</v>
       </c>
-      <c r="F37" t="str">
-        <v>Axis Salary Account</v>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Groceries</v>
+      </c>
+      <c r="B38">
+        <v>9000</v>
+      </c>
+      <c r="C38">
+        <v>3</v>
+      </c>
+      <c r="D38">
+        <v>2026</v>
+      </c>
+      <c r="E38">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Dining</v>
+      </c>
+      <c r="B39">
+        <v>5200</v>
+      </c>
+      <c r="C39">
+        <v>3</v>
+      </c>
+      <c r="D39">
+        <v>2026</v>
+      </c>
+      <c r="E39">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Transport</v>
+      </c>
+      <c r="B40">
+        <v>4200</v>
+      </c>
+      <c r="C40">
+        <v>3</v>
+      </c>
+      <c r="D40">
+        <v>2026</v>
+      </c>
+      <c r="E40">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Utilities</v>
+      </c>
+      <c r="B41">
+        <v>4300</v>
+      </c>
+      <c r="C41">
+        <v>3</v>
+      </c>
+      <c r="D41">
+        <v>2026</v>
+      </c>
+      <c r="E41">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Shopping</v>
+      </c>
+      <c r="B42">
+        <v>6200</v>
+      </c>
+      <c r="C42">
+        <v>3</v>
+      </c>
+      <c r="D42">
+        <v>2026</v>
+      </c>
+      <c r="E42">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Entertainment</v>
+      </c>
+      <c r="B43">
+        <v>2400</v>
+      </c>
+      <c r="C43">
+        <v>3</v>
+      </c>
+      <c r="D43">
+        <v>2026</v>
+      </c>
+      <c r="E43">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F37"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E43"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1236,28 +1227,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Name</v>
+        <v>name</v>
       </c>
       <c r="B1" t="str">
-        <v>TargetAmount</v>
+        <v>targetAmount</v>
       </c>
       <c r="C1" t="str">
-        <v>CurrentAmount</v>
+        <v>currentAmount</v>
       </c>
       <c r="D1" t="str">
-        <v>TargetDate</v>
+        <v>targetDate</v>
       </c>
       <c r="E1" t="str">
-        <v>LinkedAccountName</v>
+        <v>linkedAccountName</v>
       </c>
       <c r="F1" t="str">
-        <v>Icon</v>
+        <v>icon</v>
       </c>
       <c r="G1" t="str">
-        <v>Color</v>
+        <v>color</v>
       </c>
       <c r="H1" t="str">
-        <v>Status</v>
+        <v>status</v>
       </c>
     </row>
     <row r="2">
@@ -1265,22 +1256,22 @@
         <v>Emergency Fund</v>
       </c>
       <c r="B2">
-        <v>350000</v>
+        <v>150000</v>
       </c>
       <c r="C2">
-        <v>225000</v>
+        <v>86000</v>
       </c>
       <c r="D2" t="str">
         <v>2026-12-31</v>
       </c>
       <c r="E2" t="str">
-        <v>Emergency Savings</v>
+        <v>Reserve Savings</v>
       </c>
       <c r="F2" t="str">
-        <v>shield</v>
+        <v>target</v>
       </c>
       <c r="G2" t="str">
-        <v>#2EA05F</v>
+        <v>#2ea05f</v>
       </c>
       <c r="H2" t="str">
         <v>active</v>
@@ -1288,25 +1279,25 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Japan Vacation</v>
+        <v>Japan Escape</v>
       </c>
       <c r="B3">
-        <v>180000</v>
+        <v>90000</v>
       </c>
       <c r="C3">
-        <v>76000</v>
+        <v>24000</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-15</v>
+        <v>2027-02-28</v>
       </c>
       <c r="E3" t="str">
-        <v>Axis Salary Account</v>
+        <v>Reserve Savings</v>
       </c>
       <c r="F3" t="str">
-        <v>plane</v>
+        <v>travel</v>
       </c>
       <c r="G3" t="str">
-        <v>#3C97F4</v>
+        <v>#d9a73c</v>
       </c>
       <c r="H3" t="str">
         <v>active</v>
@@ -1314,25 +1305,25 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>New Laptop</v>
+        <v>Laptop Upgrade</v>
       </c>
       <c r="B4">
-        <v>140000</v>
+        <v>120000</v>
       </c>
       <c r="C4">
-        <v>52000</v>
+        <v>32000</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-07-30</v>
+        <v>2026-08-15</v>
       </c>
       <c r="E4" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="F4" t="str">
-        <v>laptop</v>
+        <v>education</v>
       </c>
       <c r="G4" t="str">
-        <v>#6A63FF</v>
+        <v>#2f6fbe</v>
       </c>
       <c r="H4" t="str">
         <v>active</v>
@@ -1347,52 +1338,52 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J91"/>
+  <dimension ref="A1:J135"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>AccountName</v>
+        <v>accountName</v>
       </c>
       <c r="B1" t="str">
-        <v>Type</v>
+        <v>type</v>
       </c>
       <c r="C1" t="str">
-        <v>Amount</v>
+        <v>amount</v>
       </c>
       <c r="D1" t="str">
-        <v>Date</v>
+        <v>date</v>
       </c>
       <c r="E1" t="str">
-        <v>Category</v>
+        <v>category</v>
       </c>
       <c r="F1" t="str">
-        <v>TransferAccountName</v>
+        <v>transferAccountName</v>
       </c>
       <c r="G1" t="str">
-        <v>Merchant</v>
+        <v>merchant</v>
       </c>
       <c r="H1" t="str">
-        <v>Note</v>
+        <v>note</v>
       </c>
       <c r="I1" t="str">
-        <v>PaymentMethod</v>
+        <v>paymentMethod</v>
       </c>
       <c r="J1" t="str">
-        <v>Tags</v>
+        <v>tags</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B2" t="str">
         <v>Income</v>
       </c>
       <c r="C2">
-        <v>98000</v>
+        <v>70000</v>
       </c>
       <c r="D2" t="str">
-        <v>2025-09-30</v>
+        <v>2025-10-01</v>
       </c>
       <c r="E2" t="str">
         <v>Salary</v>
@@ -1401,7 +1392,7 @@
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>Employer Payroll</v>
+        <v>Amiti Labs Payroll</v>
       </c>
       <c r="H2" t="str">
         <v>Monthly salary credit</v>
@@ -1410,21 +1401,21 @@
         <v>Bank Transfer</v>
       </c>
       <c r="J2" t="str">
-        <v>salary,monthly</v>
+        <v>salary, fixed-income</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B3" t="str">
         <v>Income</v>
       </c>
       <c r="C3">
-        <v>12000</v>
+        <v>8000</v>
       </c>
       <c r="D3" t="str">
-        <v>2025-10-17</v>
+        <v>2025-10-16</v>
       </c>
       <c r="E3" t="str">
         <v>Freelance</v>
@@ -1433,30 +1424,30 @@
         <v/>
       </c>
       <c r="G3" t="str">
-        <v>Consulting Client</v>
+        <v>Client Retainer</v>
       </c>
       <c r="H3" t="str">
-        <v>Side project payout</v>
+        <v>Side project invoice settlement</v>
       </c>
       <c r="I3" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="J3" t="str">
-        <v>freelance,side-income</v>
+        <v>freelance, variable-income</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B4" t="str">
         <v>Expense</v>
       </c>
       <c r="C4">
-        <v>28000</v>
+        <v>18000</v>
       </c>
       <c r="D4" t="str">
-        <v>2025-10-02</v>
+        <v>2025-10-03</v>
       </c>
       <c r="E4" t="str">
         <v>Rent</v>
@@ -1465,21 +1456,21 @@
         <v/>
       </c>
       <c r="G4" t="str">
-        <v>Sunrise Residency</v>
+        <v>Skyline Residency</v>
       </c>
       <c r="H4" t="str">
         <v>Monthly apartment rent</v>
       </c>
       <c r="I4" t="str">
-        <v>UPI</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="J4" t="str">
-        <v>housing,fixed</v>
+        <v>housing, fixed</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B5" t="str">
         <v>Expense</v>
@@ -1488,7 +1479,7 @@
         <v>3200</v>
       </c>
       <c r="D5" t="str">
-        <v>2025-10-03</v>
+        <v>2025-10-05</v>
       </c>
       <c r="E5" t="str">
         <v>Utilities</v>
@@ -1497,318 +1488,318 @@
         <v/>
       </c>
       <c r="G5" t="str">
-        <v>BESCOM</v>
+        <v>City Power + FiberNet</v>
       </c>
       <c r="H5" t="str">
-        <v>Electricity bill</v>
+        <v>Electricity and internet bundle</v>
       </c>
       <c r="I5" t="str">
-        <v>Net Banking</v>
+        <v>Auto Debit</v>
       </c>
       <c r="J5" t="str">
-        <v>utilities,bill</v>
+        <v>utilities, fixed</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B6" t="str">
         <v>Expense</v>
       </c>
       <c r="C6">
-        <v>1199</v>
+        <v>1976</v>
       </c>
       <c r="D6" t="str">
-        <v>2025-10-04</v>
+        <v>2025-10-07</v>
       </c>
       <c r="E6" t="str">
-        <v>Utilities</v>
+        <v>Groceries</v>
       </c>
       <c r="F6" t="str">
         <v/>
       </c>
       <c r="G6" t="str">
-        <v>Airtel Fiber</v>
+        <v>Fresh Basket</v>
       </c>
       <c r="H6" t="str">
-        <v>Internet payment</v>
+        <v>Weekly household groceries</v>
       </c>
       <c r="I6" t="str">
         <v>UPI</v>
       </c>
       <c r="J6" t="str">
-        <v>internet,utility</v>
+        <v>groceries, household</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B7" t="str">
         <v>Expense</v>
       </c>
       <c r="C7">
-        <v>4700</v>
+        <v>1824</v>
       </c>
       <c r="D7" t="str">
-        <v>2025-10-05</v>
+        <v>2025-10-12</v>
       </c>
       <c r="E7" t="str">
-        <v>Food</v>
+        <v>Groceries</v>
       </c>
       <c r="F7" t="str">
         <v/>
       </c>
       <c r="G7" t="str">
-        <v>BigBasket</v>
+        <v>Green Cart</v>
       </c>
       <c r="H7" t="str">
-        <v>Groceries stock-up</v>
+        <v>Produce and dairy run</v>
       </c>
       <c r="I7" t="str">
-        <v>Card</v>
+        <v>Debit Card</v>
       </c>
       <c r="J7" t="str">
-        <v>groceries,home</v>
+        <v>groceries, household</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B8" t="str">
         <v>Expense</v>
       </c>
       <c r="C8">
-        <v>2400</v>
+        <v>2052</v>
       </c>
       <c r="D8" t="str">
-        <v>2025-10-11</v>
+        <v>2025-10-19</v>
       </c>
       <c r="E8" t="str">
-        <v>Food</v>
+        <v>Groceries</v>
       </c>
       <c r="F8" t="str">
         <v/>
       </c>
       <c r="G8" t="str">
-        <v>Swiggy</v>
+        <v>Fresh Basket</v>
       </c>
       <c r="H8" t="str">
-        <v>Dining and delivery</v>
+        <v>Weekly household groceries</v>
       </c>
       <c r="I8" t="str">
         <v>UPI</v>
       </c>
       <c r="J8" t="str">
-        <v>food,lifestyle</v>
+        <v>groceries, household</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B9" t="str">
         <v>Expense</v>
       </c>
       <c r="C9">
-        <v>3100</v>
+        <v>1748</v>
       </c>
       <c r="D9" t="str">
-        <v>2025-10-08</v>
+        <v>2025-10-26</v>
       </c>
       <c r="E9" t="str">
-        <v>Transport</v>
+        <v>Groceries</v>
       </c>
       <c r="F9" t="str">
         <v/>
       </c>
       <c r="G9" t="str">
-        <v>Uber</v>
+        <v>Green Cart</v>
       </c>
       <c r="H9" t="str">
-        <v>Office commute</v>
+        <v>Produce and dairy run</v>
       </c>
       <c r="I9" t="str">
-        <v>UPI</v>
+        <v>Debit Card</v>
       </c>
       <c r="J9" t="str">
-        <v>transport,commute</v>
+        <v>groceries, household</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B10" t="str">
-        <v>Expense</v>
+        <v>Transfer</v>
       </c>
       <c r="C10">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="D10" t="str">
-        <v>2025-10-13</v>
+        <v>2025-10-06</v>
       </c>
       <c r="E10" t="str">
-        <v>Shopping</v>
+        <v/>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>Pocket Cash</v>
       </c>
       <c r="G10" t="str">
-        <v>Amazon</v>
+        <v>Pocket Cash</v>
       </c>
       <c r="H10" t="str">
-        <v>Shopping order</v>
+        <v>Monthly cash wallet top-up</v>
       </c>
       <c r="I10" t="str">
-        <v>Card</v>
+        <v>Transfer</v>
       </c>
       <c r="J10" t="str">
-        <v>shopping,online</v>
+        <v>cash</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B11" t="str">
-        <v>Expense</v>
+        <v>Transfer</v>
       </c>
       <c r="C11">
-        <v>1700</v>
+        <v>6000</v>
       </c>
       <c r="D11" t="str">
-        <v>2025-10-19</v>
+        <v>2025-10-08</v>
       </c>
       <c r="E11" t="str">
-        <v>Entertainment</v>
+        <v/>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>Reserve Savings</v>
       </c>
       <c r="G11" t="str">
-        <v>BookMyShow</v>
+        <v>Reserve Savings</v>
       </c>
       <c r="H11" t="str">
-        <v>Weekend entertainment</v>
+        <v>Move money to savings goal bucket</v>
       </c>
       <c r="I11" t="str">
-        <v>Card</v>
+        <v>Transfer</v>
       </c>
       <c r="J11" t="str">
-        <v>fun,weekend</v>
+        <v>savings, goal</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B12" t="str">
-        <v>Expense</v>
+        <v>Transfer</v>
       </c>
       <c r="C12">
-        <v>900</v>
+        <v>6800</v>
       </c>
       <c r="D12" t="str">
-        <v>2025-10-21</v>
+        <v>2025-10-27</v>
       </c>
       <c r="E12" t="str">
-        <v>Health</v>
+        <v/>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="G12" t="str">
-        <v>Apollo Pharmacy</v>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="H12" t="str">
-        <v>Health and pharmacy</v>
+        <v>Credit card bill payment</v>
       </c>
       <c r="I12" t="str">
-        <v>UPI</v>
+        <v>Transfer</v>
       </c>
       <c r="J12" t="str">
-        <v>health,care</v>
+        <v>credit-card, payment</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Axis Salary Account</v>
+        <v>Pocket Cash</v>
       </c>
       <c r="B13" t="str">
-        <v>Transfer</v>
+        <v>Expense</v>
       </c>
       <c r="C13">
-        <v>17000</v>
+        <v>484</v>
       </c>
       <c r="D13" t="str">
-        <v>2025-10-06</v>
+        <v>2025-10-09</v>
       </c>
       <c r="E13" t="str">
-        <v/>
+        <v>Transport</v>
       </c>
       <c r="F13" t="str">
-        <v>Emergency Savings</v>
+        <v/>
       </c>
       <c r="G13" t="str">
-        <v>Self Transfer</v>
+        <v>Metro Card</v>
       </c>
       <c r="H13" t="str">
-        <v>Move to emergency fund</v>
+        <v>Local commute top-up</v>
       </c>
       <c r="I13" t="str">
-        <v>Bank Transfer</v>
+        <v>Cash</v>
       </c>
       <c r="J13" t="str">
-        <v>saving,transfer</v>
+        <v>transport, commute</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Axis Salary Account</v>
+        <v>Pocket Cash</v>
       </c>
       <c r="B14" t="str">
-        <v>Transfer</v>
+        <v>Expense</v>
       </c>
       <c r="C14">
-        <v>3500</v>
+        <v>616</v>
       </c>
       <c r="D14" t="str">
-        <v>2025-10-23</v>
+        <v>2025-10-14</v>
       </c>
       <c r="E14" t="str">
-        <v/>
+        <v>Transport</v>
       </c>
       <c r="F14" t="str">
-        <v>Cash Wallet</v>
+        <v/>
       </c>
       <c r="G14" t="str">
-        <v>Self Transfer</v>
+        <v>Ride Now</v>
       </c>
       <c r="H14" t="str">
-        <v>Save for Japan trip</v>
+        <v>Auto and cab rides</v>
       </c>
       <c r="I14" t="str">
-        <v>Bank Transfer</v>
+        <v>Cash</v>
       </c>
       <c r="J14" t="str">
-        <v>goal,travel</v>
+        <v>transport, commute</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Axis Salary Account</v>
+        <v>Pocket Cash</v>
       </c>
       <c r="B15" t="str">
         <v>Expense</v>
       </c>
       <c r="C15">
-        <v>2500</v>
+        <v>528</v>
       </c>
       <c r="D15" t="str">
-        <v>2025-10-07</v>
+        <v>2025-10-21</v>
       </c>
       <c r="E15" t="str">
         <v>Transport</v>
@@ -1817,1022 +1808,1022 @@
         <v/>
       </c>
       <c r="G15" t="str">
-        <v>ATM Withdrawal</v>
+        <v>Metro Card</v>
       </c>
       <c r="H15" t="str">
-        <v>Cash for local expenses</v>
+        <v>Local commute top-up</v>
       </c>
       <c r="I15" t="str">
-        <v>ATM</v>
+        <v>Cash</v>
       </c>
       <c r="J15" t="str">
-        <v>cash,atm</v>
+        <v>transport, commute</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Axis Salary Account</v>
+        <v>Pocket Cash</v>
       </c>
       <c r="B16" t="str">
         <v>Expense</v>
       </c>
       <c r="C16">
-        <v>6200</v>
+        <v>572</v>
       </c>
       <c r="D16" t="str">
-        <v>2025-10-25</v>
+        <v>2025-10-28</v>
       </c>
       <c r="E16" t="str">
-        <v>Shopping</v>
+        <v>Transport</v>
       </c>
       <c r="F16" t="str">
         <v/>
       </c>
       <c r="G16" t="str">
-        <v>HDFC Card Payment</v>
+        <v>Ride Now</v>
       </c>
       <c r="H16" t="str">
-        <v>Credit card bill payment</v>
+        <v>Auto and cab rides</v>
       </c>
       <c r="I16" t="str">
-        <v>Net Banking</v>
+        <v>Cash</v>
       </c>
       <c r="J16" t="str">
-        <v>card,bill</v>
+        <v>transport, commute</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Axis Salary Account</v>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="B17" t="str">
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="C17">
-        <v>99500</v>
+        <v>1976</v>
       </c>
       <c r="D17" t="str">
-        <v>2025-10-31</v>
+        <v>2025-10-10</v>
       </c>
       <c r="E17" t="str">
-        <v>Salary</v>
+        <v>Dining</v>
       </c>
       <c r="F17" t="str">
         <v/>
       </c>
       <c r="G17" t="str">
-        <v>Employer Payroll</v>
+        <v>Swiggy</v>
       </c>
       <c r="H17" t="str">
-        <v>Monthly salary credit</v>
+        <v>Weekend takeout</v>
       </c>
       <c r="I17" t="str">
-        <v>Bank Transfer</v>
+        <v>Credit Card</v>
       </c>
       <c r="J17" t="str">
-        <v>salary,monthly</v>
+        <v>food, lifestyle</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Axis Salary Account</v>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="B18" t="str">
         <v>Expense</v>
       </c>
       <c r="C18">
-        <v>28000</v>
+        <v>1612</v>
       </c>
       <c r="D18" t="str">
-        <v>2025-11-02</v>
+        <v>2025-10-18</v>
       </c>
       <c r="E18" t="str">
-        <v>Rent</v>
+        <v>Dining</v>
       </c>
       <c r="F18" t="str">
         <v/>
       </c>
       <c r="G18" t="str">
-        <v>Sunrise Residency</v>
+        <v>Blue Oven</v>
       </c>
       <c r="H18" t="str">
-        <v>Monthly apartment rent</v>
+        <v>Casual dinner with friends</v>
       </c>
       <c r="I18" t="str">
-        <v>UPI</v>
+        <v>Credit Card</v>
       </c>
       <c r="J18" t="str">
-        <v>housing,fixed</v>
+        <v>food, lifestyle</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Axis Salary Account</v>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="B19" t="str">
         <v>Expense</v>
       </c>
       <c r="C19">
-        <v>3290</v>
+        <v>1612</v>
       </c>
       <c r="D19" t="str">
-        <v>2025-11-03</v>
+        <v>2025-10-24</v>
       </c>
       <c r="E19" t="str">
-        <v>Utilities</v>
+        <v>Dining</v>
       </c>
       <c r="F19" t="str">
         <v/>
       </c>
       <c r="G19" t="str">
-        <v>BESCOM</v>
+        <v>Late Night Bowl</v>
       </c>
       <c r="H19" t="str">
-        <v>Electricity bill</v>
+        <v>Quick dining order</v>
       </c>
       <c r="I19" t="str">
-        <v>Net Banking</v>
+        <v>Credit Card</v>
       </c>
       <c r="J19" t="str">
-        <v>utilities,bill</v>
+        <v>food, lifestyle</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Axis Salary Account</v>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="B20" t="str">
         <v>Expense</v>
       </c>
       <c r="C20">
-        <v>1199</v>
+        <v>2016</v>
       </c>
       <c r="D20" t="str">
-        <v>2025-11-04</v>
+        <v>2025-10-11</v>
       </c>
       <c r="E20" t="str">
-        <v>Utilities</v>
+        <v>Shopping</v>
       </c>
       <c r="F20" t="str">
         <v/>
       </c>
       <c r="G20" t="str">
-        <v>Airtel Fiber</v>
+        <v>UrbanCart</v>
       </c>
       <c r="H20" t="str">
-        <v>Internet payment</v>
+        <v>Lifestyle and home essentials</v>
       </c>
       <c r="I20" t="str">
-        <v>UPI</v>
+        <v>Credit Card</v>
       </c>
       <c r="J20" t="str">
-        <v>internet,utility</v>
+        <v>shopping</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Axis Salary Account</v>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="B21" t="str">
         <v>Expense</v>
       </c>
       <c r="C21">
-        <v>4950</v>
+        <v>1584</v>
       </c>
       <c r="D21" t="str">
-        <v>2025-11-05</v>
+        <v>2025-10-23</v>
       </c>
       <c r="E21" t="str">
-        <v>Food</v>
+        <v>Shopping</v>
       </c>
       <c r="F21" t="str">
         <v/>
       </c>
       <c r="G21" t="str">
-        <v>BigBasket</v>
+        <v>Daily Mart</v>
       </c>
       <c r="H21" t="str">
-        <v>Groceries stock-up</v>
+        <v>Personal care and extras</v>
       </c>
       <c r="I21" t="str">
-        <v>Card</v>
+        <v>Credit Card</v>
       </c>
       <c r="J21" t="str">
-        <v>groceries,home</v>
+        <v>shopping</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Axis Salary Account</v>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="B22" t="str">
         <v>Expense</v>
       </c>
       <c r="C22">
-        <v>2560</v>
+        <v>695</v>
       </c>
       <c r="D22" t="str">
-        <v>2025-11-11</v>
+        <v>2025-10-13</v>
       </c>
       <c r="E22" t="str">
-        <v>Food</v>
+        <v>Entertainment</v>
       </c>
       <c r="F22" t="str">
         <v/>
       </c>
       <c r="G22" t="str">
-        <v>Swiggy</v>
+        <v>Netflix + Prime</v>
       </c>
       <c r="H22" t="str">
-        <v>Dining and delivery</v>
+        <v>Digital subscription stack</v>
       </c>
       <c r="I22" t="str">
-        <v>UPI</v>
+        <v>Credit Card</v>
       </c>
       <c r="J22" t="str">
-        <v>food,lifestyle</v>
+        <v>subscription, entertainment</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Axis Salary Account</v>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="B23" t="str">
         <v>Expense</v>
       </c>
       <c r="C23">
-        <v>3280</v>
+        <v>503</v>
       </c>
       <c r="D23" t="str">
-        <v>2025-11-08</v>
+        <v>2025-10-20</v>
       </c>
       <c r="E23" t="str">
-        <v>Transport</v>
+        <v>Entertainment</v>
       </c>
       <c r="F23" t="str">
         <v/>
       </c>
       <c r="G23" t="str">
-        <v>Uber</v>
+        <v>Spotify + YouTube</v>
       </c>
       <c r="H23" t="str">
-        <v>Office commute</v>
+        <v>Digital subscription stack</v>
       </c>
       <c r="I23" t="str">
-        <v>UPI</v>
+        <v>Credit Card</v>
       </c>
       <c r="J23" t="str">
-        <v>transport,commute</v>
+        <v>subscription, entertainment</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B24" t="str">
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="C24">
-        <v>1940</v>
+        <v>70000</v>
       </c>
       <c r="D24" t="str">
-        <v>2025-11-13</v>
+        <v>2025-11-01</v>
       </c>
       <c r="E24" t="str">
-        <v>Shopping</v>
+        <v>Salary</v>
       </c>
       <c r="F24" t="str">
         <v/>
       </c>
       <c r="G24" t="str">
-        <v>Amazon</v>
+        <v>Amiti Labs Payroll</v>
       </c>
       <c r="H24" t="str">
-        <v>Shopping order</v>
+        <v>Monthly salary credit</v>
       </c>
       <c r="I24" t="str">
-        <v>Card</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="J24" t="str">
-        <v>shopping,online</v>
+        <v>salary, fixed-income</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B25" t="str">
         <v>Expense</v>
       </c>
       <c r="C25">
-        <v>1830</v>
+        <v>18000</v>
       </c>
       <c r="D25" t="str">
-        <v>2025-11-19</v>
+        <v>2025-11-03</v>
       </c>
       <c r="E25" t="str">
-        <v>Entertainment</v>
+        <v>Rent</v>
       </c>
       <c r="F25" t="str">
         <v/>
       </c>
       <c r="G25" t="str">
-        <v>BookMyShow</v>
+        <v>Skyline Residency</v>
       </c>
       <c r="H25" t="str">
-        <v>Weekend entertainment</v>
+        <v>Monthly apartment rent</v>
       </c>
       <c r="I25" t="str">
-        <v>Card</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="J25" t="str">
-        <v>fun,weekend</v>
+        <v>housing, fixed</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B26" t="str">
         <v>Expense</v>
       </c>
       <c r="C26">
-        <v>980</v>
+        <v>3300</v>
       </c>
       <c r="D26" t="str">
-        <v>2025-11-21</v>
+        <v>2025-11-05</v>
       </c>
       <c r="E26" t="str">
-        <v>Health</v>
+        <v>Utilities</v>
       </c>
       <c r="F26" t="str">
         <v/>
       </c>
       <c r="G26" t="str">
-        <v>Apollo Pharmacy</v>
+        <v>City Power + FiberNet</v>
       </c>
       <c r="H26" t="str">
-        <v>Health and pharmacy</v>
+        <v>Electricity and internet bundle</v>
       </c>
       <c r="I26" t="str">
-        <v>UPI</v>
+        <v>Auto Debit</v>
       </c>
       <c r="J26" t="str">
-        <v>health,care</v>
+        <v>utilities, fixed</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B27" t="str">
-        <v>Transfer</v>
+        <v>Expense</v>
       </c>
       <c r="C27">
-        <v>18000</v>
+        <v>2054</v>
       </c>
       <c r="D27" t="str">
-        <v>2025-11-06</v>
+        <v>2025-11-07</v>
       </c>
       <c r="E27" t="str">
-        <v/>
+        <v>Groceries</v>
       </c>
       <c r="F27" t="str">
-        <v>Emergency Savings</v>
+        <v/>
       </c>
       <c r="G27" t="str">
-        <v>Self Transfer</v>
+        <v>Fresh Basket</v>
       </c>
       <c r="H27" t="str">
-        <v>Move to emergency fund</v>
+        <v>Weekly household groceries</v>
       </c>
       <c r="I27" t="str">
-        <v>Bank Transfer</v>
+        <v>UPI</v>
       </c>
       <c r="J27" t="str">
-        <v>saving,transfer</v>
+        <v>groceries, household</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B28" t="str">
-        <v>Transfer</v>
+        <v>Expense</v>
       </c>
       <c r="C28">
-        <v>4000</v>
+        <v>1896</v>
       </c>
       <c r="D28" t="str">
-        <v>2025-11-23</v>
+        <v>2025-11-12</v>
       </c>
       <c r="E28" t="str">
-        <v/>
+        <v>Groceries</v>
       </c>
       <c r="F28" t="str">
-        <v>Cash Wallet</v>
+        <v/>
       </c>
       <c r="G28" t="str">
-        <v>Self Transfer</v>
+        <v>Green Cart</v>
       </c>
       <c r="H28" t="str">
-        <v>Save for Japan trip</v>
+        <v>Produce and dairy run</v>
       </c>
       <c r="I28" t="str">
-        <v>Bank Transfer</v>
+        <v>Debit Card</v>
       </c>
       <c r="J28" t="str">
-        <v>goal,travel</v>
+        <v>groceries, household</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B29" t="str">
         <v>Expense</v>
       </c>
       <c r="C29">
-        <v>2500</v>
+        <v>2133</v>
       </c>
       <c r="D29" t="str">
-        <v>2025-11-07</v>
+        <v>2025-11-19</v>
       </c>
       <c r="E29" t="str">
-        <v>Transport</v>
+        <v>Groceries</v>
       </c>
       <c r="F29" t="str">
         <v/>
       </c>
       <c r="G29" t="str">
-        <v>ATM Withdrawal</v>
+        <v>Fresh Basket</v>
       </c>
       <c r="H29" t="str">
-        <v>Cash for local expenses</v>
+        <v>Weekly household groceries</v>
       </c>
       <c r="I29" t="str">
-        <v>ATM</v>
+        <v>UPI</v>
       </c>
       <c r="J29" t="str">
-        <v>cash,atm</v>
+        <v>groceries, household</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B30" t="str">
         <v>Expense</v>
       </c>
       <c r="C30">
-        <v>6600</v>
+        <v>1817</v>
       </c>
       <c r="D30" t="str">
-        <v>2025-11-25</v>
+        <v>2025-11-26</v>
       </c>
       <c r="E30" t="str">
-        <v>Shopping</v>
+        <v>Groceries</v>
       </c>
       <c r="F30" t="str">
         <v/>
       </c>
       <c r="G30" t="str">
-        <v>HDFC Card Payment</v>
+        <v>Green Cart</v>
       </c>
       <c r="H30" t="str">
-        <v>Credit card bill payment</v>
+        <v>Produce and dairy run</v>
       </c>
       <c r="I30" t="str">
-        <v>Net Banking</v>
+        <v>Debit Card</v>
       </c>
       <c r="J30" t="str">
-        <v>card,bill</v>
+        <v>groceries, household</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B31" t="str">
-        <v>Income</v>
+        <v>Transfer</v>
       </c>
       <c r="C31">
-        <v>101000</v>
+        <v>1500</v>
       </c>
       <c r="D31" t="str">
-        <v>2025-11-30</v>
+        <v>2025-11-06</v>
       </c>
       <c r="E31" t="str">
-        <v>Salary</v>
+        <v/>
       </c>
       <c r="F31" t="str">
-        <v/>
+        <v>Pocket Cash</v>
       </c>
       <c r="G31" t="str">
-        <v>Employer Payroll</v>
+        <v>Pocket Cash</v>
       </c>
       <c r="H31" t="str">
-        <v>Monthly salary credit</v>
+        <v>Monthly cash wallet top-up</v>
       </c>
       <c r="I31" t="str">
-        <v>Bank Transfer</v>
+        <v>Transfer</v>
       </c>
       <c r="J31" t="str">
-        <v>salary,monthly</v>
+        <v>cash</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B32" t="str">
-        <v>Income</v>
+        <v>Transfer</v>
       </c>
       <c r="C32">
-        <v>13200</v>
+        <v>6500</v>
       </c>
       <c r="D32" t="str">
-        <v>2025-12-17</v>
+        <v>2025-11-08</v>
       </c>
       <c r="E32" t="str">
-        <v>Freelance</v>
+        <v/>
       </c>
       <c r="F32" t="str">
-        <v/>
+        <v>Reserve Savings</v>
       </c>
       <c r="G32" t="str">
-        <v>Consulting Client</v>
+        <v>Reserve Savings</v>
       </c>
       <c r="H32" t="str">
-        <v>Side project payout</v>
+        <v>Move money to savings goal bucket</v>
       </c>
       <c r="I32" t="str">
-        <v>Bank Transfer</v>
+        <v>Transfer</v>
       </c>
       <c r="J32" t="str">
-        <v>freelance,side-income</v>
+        <v>savings, goal</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B33" t="str">
-        <v>Expense</v>
+        <v>Transfer</v>
       </c>
       <c r="C33">
-        <v>28000</v>
+        <v>7200</v>
       </c>
       <c r="D33" t="str">
-        <v>2025-12-02</v>
+        <v>2025-11-27</v>
       </c>
       <c r="E33" t="str">
-        <v>Rent</v>
+        <v/>
       </c>
       <c r="F33" t="str">
-        <v/>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="G33" t="str">
-        <v>Sunrise Residency</v>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="H33" t="str">
-        <v>Monthly apartment rent</v>
+        <v>Credit card bill payment</v>
       </c>
       <c r="I33" t="str">
-        <v>UPI</v>
+        <v>Transfer</v>
       </c>
       <c r="J33" t="str">
-        <v>housing,fixed</v>
+        <v>credit-card, payment</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Axis Salary Account</v>
+        <v>Pocket Cash</v>
       </c>
       <c r="B34" t="str">
         <v>Expense</v>
       </c>
       <c r="C34">
-        <v>3380</v>
+        <v>528</v>
       </c>
       <c r="D34" t="str">
-        <v>2025-12-03</v>
+        <v>2025-11-09</v>
       </c>
       <c r="E34" t="str">
-        <v>Utilities</v>
+        <v>Transport</v>
       </c>
       <c r="F34" t="str">
         <v/>
       </c>
       <c r="G34" t="str">
-        <v>BESCOM</v>
+        <v>Metro Card</v>
       </c>
       <c r="H34" t="str">
-        <v>Electricity bill</v>
+        <v>Local commute top-up</v>
       </c>
       <c r="I34" t="str">
-        <v>Net Banking</v>
+        <v>Cash</v>
       </c>
       <c r="J34" t="str">
-        <v>utilities,bill</v>
+        <v>transport, commute</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Axis Salary Account</v>
+        <v>Pocket Cash</v>
       </c>
       <c r="B35" t="str">
         <v>Expense</v>
       </c>
       <c r="C35">
-        <v>1199</v>
+        <v>672</v>
       </c>
       <c r="D35" t="str">
-        <v>2025-12-04</v>
+        <v>2025-11-14</v>
       </c>
       <c r="E35" t="str">
-        <v>Utilities</v>
+        <v>Transport</v>
       </c>
       <c r="F35" t="str">
         <v/>
       </c>
       <c r="G35" t="str">
-        <v>Airtel Fiber</v>
+        <v>Ride Now</v>
       </c>
       <c r="H35" t="str">
-        <v>Internet payment</v>
+        <v>Auto and cab rides</v>
       </c>
       <c r="I35" t="str">
-        <v>UPI</v>
+        <v>Cash</v>
       </c>
       <c r="J35" t="str">
-        <v>internet,utility</v>
+        <v>transport, commute</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Axis Salary Account</v>
+        <v>Pocket Cash</v>
       </c>
       <c r="B36" t="str">
         <v>Expense</v>
       </c>
       <c r="C36">
-        <v>5200</v>
+        <v>576</v>
       </c>
       <c r="D36" t="str">
-        <v>2025-12-05</v>
+        <v>2025-11-21</v>
       </c>
       <c r="E36" t="str">
-        <v>Food</v>
+        <v>Transport</v>
       </c>
       <c r="F36" t="str">
         <v/>
       </c>
       <c r="G36" t="str">
-        <v>BigBasket</v>
+        <v>Metro Card</v>
       </c>
       <c r="H36" t="str">
-        <v>Groceries stock-up</v>
+        <v>Local commute top-up</v>
       </c>
       <c r="I36" t="str">
-        <v>Card</v>
+        <v>Cash</v>
       </c>
       <c r="J36" t="str">
-        <v>groceries,home</v>
+        <v>transport, commute</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Axis Salary Account</v>
+        <v>Pocket Cash</v>
       </c>
       <c r="B37" t="str">
         <v>Expense</v>
       </c>
       <c r="C37">
-        <v>2720</v>
+        <v>624</v>
       </c>
       <c r="D37" t="str">
-        <v>2025-12-11</v>
+        <v>2025-11-28</v>
       </c>
       <c r="E37" t="str">
-        <v>Food</v>
+        <v>Transport</v>
       </c>
       <c r="F37" t="str">
         <v/>
       </c>
       <c r="G37" t="str">
-        <v>Swiggy</v>
+        <v>Ride Now</v>
       </c>
       <c r="H37" t="str">
-        <v>Dining and delivery</v>
+        <v>Auto and cab rides</v>
       </c>
       <c r="I37" t="str">
-        <v>UPI</v>
+        <v>Cash</v>
       </c>
       <c r="J37" t="str">
-        <v>food,lifestyle</v>
+        <v>transport, commute</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Axis Salary Account</v>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="B38" t="str">
         <v>Expense</v>
       </c>
       <c r="C38">
-        <v>3460</v>
+        <v>1824</v>
       </c>
       <c r="D38" t="str">
-        <v>2025-12-08</v>
+        <v>2025-11-10</v>
       </c>
       <c r="E38" t="str">
-        <v>Transport</v>
+        <v>Dining</v>
       </c>
       <c r="F38" t="str">
         <v/>
       </c>
       <c r="G38" t="str">
-        <v>Uber</v>
+        <v>Swiggy</v>
       </c>
       <c r="H38" t="str">
-        <v>Office commute</v>
+        <v>Weekend takeout</v>
       </c>
       <c r="I38" t="str">
-        <v>UPI</v>
+        <v>Credit Card</v>
       </c>
       <c r="J38" t="str">
-        <v>transport,commute</v>
+        <v>food, lifestyle</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="B39" t="str">
         <v>Expense</v>
       </c>
       <c r="C39">
-        <v>2080</v>
+        <v>1488</v>
       </c>
       <c r="D39" t="str">
-        <v>2025-12-13</v>
+        <v>2025-11-18</v>
       </c>
       <c r="E39" t="str">
-        <v>Shopping</v>
+        <v>Dining</v>
       </c>
       <c r="F39" t="str">
         <v/>
       </c>
       <c r="G39" t="str">
-        <v>Amazon</v>
+        <v>Blue Oven</v>
       </c>
       <c r="H39" t="str">
-        <v>Shopping order</v>
+        <v>Casual dinner with friends</v>
       </c>
       <c r="I39" t="str">
-        <v>Card</v>
+        <v>Credit Card</v>
       </c>
       <c r="J39" t="str">
-        <v>shopping,online</v>
+        <v>food, lifestyle</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="B40" t="str">
         <v>Expense</v>
       </c>
       <c r="C40">
-        <v>1960</v>
+        <v>1488</v>
       </c>
       <c r="D40" t="str">
-        <v>2025-12-19</v>
+        <v>2025-11-24</v>
       </c>
       <c r="E40" t="str">
-        <v>Entertainment</v>
+        <v>Dining</v>
       </c>
       <c r="F40" t="str">
         <v/>
       </c>
       <c r="G40" t="str">
-        <v>BookMyShow</v>
+        <v>Late Night Bowl</v>
       </c>
       <c r="H40" t="str">
-        <v>Weekend entertainment</v>
+        <v>Quick dining order</v>
       </c>
       <c r="I40" t="str">
-        <v>Card</v>
+        <v>Credit Card</v>
       </c>
       <c r="J40" t="str">
-        <v>fun,weekend</v>
+        <v>food, lifestyle</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Axis Salary Account</v>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="B41" t="str">
         <v>Expense</v>
       </c>
       <c r="C41">
-        <v>4200</v>
+        <v>2352</v>
       </c>
       <c r="D41" t="str">
-        <v>2025-12-21</v>
+        <v>2025-11-11</v>
       </c>
       <c r="E41" t="str">
-        <v>Health</v>
+        <v>Shopping</v>
       </c>
       <c r="F41" t="str">
         <v/>
       </c>
       <c r="G41" t="str">
-        <v>Apollo Pharmacy</v>
+        <v>UrbanCart</v>
       </c>
       <c r="H41" t="str">
-        <v>Health and pharmacy</v>
+        <v>Lifestyle and home essentials</v>
       </c>
       <c r="I41" t="str">
-        <v>UPI</v>
+        <v>Credit Card</v>
       </c>
       <c r="J41" t="str">
-        <v>health,care</v>
+        <v>shopping</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Axis Salary Account</v>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="B42" t="str">
-        <v>Transfer</v>
+        <v>Expense</v>
       </c>
       <c r="C42">
-        <v>19000</v>
+        <v>1848</v>
       </c>
       <c r="D42" t="str">
-        <v>2025-12-06</v>
+        <v>2025-11-23</v>
       </c>
       <c r="E42" t="str">
-        <v/>
+        <v>Shopping</v>
       </c>
       <c r="F42" t="str">
-        <v>Emergency Savings</v>
+        <v/>
       </c>
       <c r="G42" t="str">
-        <v>Self Transfer</v>
+        <v>Daily Mart</v>
       </c>
       <c r="H42" t="str">
-        <v>Move to emergency fund</v>
+        <v>Personal care and extras</v>
       </c>
       <c r="I42" t="str">
-        <v>Bank Transfer</v>
+        <v>Credit Card</v>
       </c>
       <c r="J42" t="str">
-        <v>saving,transfer</v>
+        <v>shopping</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Axis Salary Account</v>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="B43" t="str">
-        <v>Transfer</v>
+        <v>Expense</v>
       </c>
       <c r="C43">
-        <v>4500</v>
+        <v>695</v>
       </c>
       <c r="D43" t="str">
-        <v>2025-12-23</v>
+        <v>2025-11-13</v>
       </c>
       <c r="E43" t="str">
-        <v/>
+        <v>Entertainment</v>
       </c>
       <c r="F43" t="str">
-        <v>Cash Wallet</v>
+        <v/>
       </c>
       <c r="G43" t="str">
-        <v>Self Transfer</v>
+        <v>Netflix + Prime</v>
       </c>
       <c r="H43" t="str">
-        <v>Save for Japan trip</v>
+        <v>Digital subscription stack</v>
       </c>
       <c r="I43" t="str">
-        <v>Bank Transfer</v>
+        <v>Credit Card</v>
       </c>
       <c r="J43" t="str">
-        <v>goal,travel</v>
+        <v>subscription, entertainment</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Axis Salary Account</v>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="B44" t="str">
         <v>Expense</v>
       </c>
       <c r="C44">
-        <v>2500</v>
+        <v>503</v>
       </c>
       <c r="D44" t="str">
-        <v>2025-12-07</v>
+        <v>2025-11-20</v>
       </c>
       <c r="E44" t="str">
-        <v>Transport</v>
+        <v>Entertainment</v>
       </c>
       <c r="F44" t="str">
         <v/>
       </c>
       <c r="G44" t="str">
-        <v>ATM Withdrawal</v>
+        <v>Spotify + YouTube</v>
       </c>
       <c r="H44" t="str">
-        <v>Cash for local expenses</v>
+        <v>Digital subscription stack</v>
       </c>
       <c r="I44" t="str">
-        <v>ATM</v>
+        <v>Credit Card</v>
       </c>
       <c r="J44" t="str">
-        <v>cash,atm</v>
+        <v>subscription, entertainment</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B45" t="str">
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="C45">
-        <v>7000</v>
+        <v>71000</v>
       </c>
       <c r="D45" t="str">
-        <v>2025-12-25</v>
+        <v>2025-12-01</v>
       </c>
       <c r="E45" t="str">
-        <v>Shopping</v>
+        <v>Salary</v>
       </c>
       <c r="F45" t="str">
         <v/>
       </c>
       <c r="G45" t="str">
-        <v>HDFC Card Payment</v>
+        <v>Amiti Labs Payroll</v>
       </c>
       <c r="H45" t="str">
-        <v>Credit card bill payment</v>
+        <v>Monthly salary credit</v>
       </c>
       <c r="I45" t="str">
-        <v>Net Banking</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="J45" t="str">
-        <v>card,bill</v>
+        <v>salary, fixed-income</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B46" t="str">
         <v>Income</v>
       </c>
       <c r="C46">
-        <v>102500</v>
+        <v>12000</v>
       </c>
       <c r="D46" t="str">
-        <v>2025-12-31</v>
+        <v>2025-12-16</v>
       </c>
       <c r="E46" t="str">
-        <v>Salary</v>
+        <v>Freelance</v>
       </c>
       <c r="F46" t="str">
         <v/>
       </c>
       <c r="G46" t="str">
-        <v>Employer Payroll</v>
+        <v>Client Retainer</v>
       </c>
       <c r="H46" t="str">
-        <v>Monthly salary credit</v>
+        <v>Side project invoice settlement</v>
       </c>
       <c r="I46" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="J46" t="str">
-        <v>salary,monthly</v>
+        <v>freelance, variable-income</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B47" t="str">
         <v>Expense</v>
       </c>
       <c r="C47">
-        <v>28000</v>
+        <v>18500</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-01-02</v>
+        <v>2025-12-03</v>
       </c>
       <c r="E47" t="str">
         <v>Rent</v>
@@ -2841,30 +2832,30 @@
         <v/>
       </c>
       <c r="G47" t="str">
-        <v>Sunrise Residency</v>
+        <v>Skyline Residency</v>
       </c>
       <c r="H47" t="str">
         <v>Monthly apartment rent</v>
       </c>
       <c r="I47" t="str">
-        <v>UPI</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="J47" t="str">
-        <v>housing,fixed</v>
+        <v>housing, fixed</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B48" t="str">
         <v>Expense</v>
       </c>
       <c r="C48">
-        <v>3470</v>
+        <v>3400</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-01-03</v>
+        <v>2025-12-05</v>
       </c>
       <c r="E48" t="str">
         <v>Utilities</v>
@@ -2873,318 +2864,318 @@
         <v/>
       </c>
       <c r="G48" t="str">
-        <v>BESCOM</v>
+        <v>City Power + FiberNet</v>
       </c>
       <c r="H48" t="str">
-        <v>Electricity bill</v>
+        <v>Electricity and internet bundle</v>
       </c>
       <c r="I48" t="str">
-        <v>Net Banking</v>
+        <v>Auto Debit</v>
       </c>
       <c r="J48" t="str">
-        <v>utilities,bill</v>
+        <v>utilities, fixed</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B49" t="str">
         <v>Expense</v>
       </c>
       <c r="C49">
-        <v>1199</v>
+        <v>2106</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-01-04</v>
+        <v>2025-12-07</v>
       </c>
       <c r="E49" t="str">
-        <v>Utilities</v>
+        <v>Groceries</v>
       </c>
       <c r="F49" t="str">
         <v/>
       </c>
       <c r="G49" t="str">
-        <v>Airtel Fiber</v>
+        <v>Fresh Basket</v>
       </c>
       <c r="H49" t="str">
-        <v>Internet payment</v>
+        <v>Weekly household groceries</v>
       </c>
       <c r="I49" t="str">
         <v>UPI</v>
       </c>
       <c r="J49" t="str">
-        <v>internet,utility</v>
+        <v>groceries, household</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B50" t="str">
         <v>Expense</v>
       </c>
       <c r="C50">
-        <v>5450</v>
+        <v>1944</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-01-05</v>
+        <v>2025-12-12</v>
       </c>
       <c r="E50" t="str">
-        <v>Food</v>
+        <v>Groceries</v>
       </c>
       <c r="F50" t="str">
         <v/>
       </c>
       <c r="G50" t="str">
-        <v>BigBasket</v>
+        <v>Green Cart</v>
       </c>
       <c r="H50" t="str">
-        <v>Groceries stock-up</v>
+        <v>Produce and dairy run</v>
       </c>
       <c r="I50" t="str">
-        <v>Card</v>
+        <v>Debit Card</v>
       </c>
       <c r="J50" t="str">
-        <v>groceries,home</v>
+        <v>groceries, household</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B51" t="str">
         <v>Expense</v>
       </c>
       <c r="C51">
-        <v>2880</v>
+        <v>2187</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-01-11</v>
+        <v>2025-12-19</v>
       </c>
       <c r="E51" t="str">
-        <v>Food</v>
+        <v>Groceries</v>
       </c>
       <c r="F51" t="str">
         <v/>
       </c>
       <c r="G51" t="str">
-        <v>Swiggy</v>
+        <v>Fresh Basket</v>
       </c>
       <c r="H51" t="str">
-        <v>Dining and delivery</v>
+        <v>Weekly household groceries</v>
       </c>
       <c r="I51" t="str">
         <v>UPI</v>
       </c>
       <c r="J51" t="str">
-        <v>food,lifestyle</v>
+        <v>groceries, household</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B52" t="str">
         <v>Expense</v>
       </c>
       <c r="C52">
-        <v>3640</v>
+        <v>1863</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-01-08</v>
+        <v>2025-12-26</v>
       </c>
       <c r="E52" t="str">
-        <v>Transport</v>
+        <v>Groceries</v>
       </c>
       <c r="F52" t="str">
         <v/>
       </c>
       <c r="G52" t="str">
-        <v>Uber</v>
+        <v>Green Cart</v>
       </c>
       <c r="H52" t="str">
-        <v>Office commute</v>
+        <v>Produce and dairy run</v>
       </c>
       <c r="I52" t="str">
-        <v>UPI</v>
+        <v>Debit Card</v>
       </c>
       <c r="J52" t="str">
-        <v>transport,commute</v>
+        <v>groceries, household</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B53" t="str">
-        <v>Expense</v>
+        <v>Transfer</v>
       </c>
       <c r="C53">
-        <v>2220</v>
+        <v>1800</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-01-13</v>
+        <v>2025-12-06</v>
       </c>
       <c r="E53" t="str">
-        <v>Shopping</v>
+        <v/>
       </c>
       <c r="F53" t="str">
-        <v/>
+        <v>Pocket Cash</v>
       </c>
       <c r="G53" t="str">
-        <v>Amazon</v>
+        <v>Pocket Cash</v>
       </c>
       <c r="H53" t="str">
-        <v>Shopping order</v>
+        <v>Monthly cash wallet top-up</v>
       </c>
       <c r="I53" t="str">
-        <v>Card</v>
+        <v>Transfer</v>
       </c>
       <c r="J53" t="str">
-        <v>shopping,online</v>
+        <v>cash</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B54" t="str">
-        <v>Expense</v>
+        <v>Transfer</v>
       </c>
       <c r="C54">
-        <v>2090</v>
+        <v>7000</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-01-19</v>
+        <v>2025-12-08</v>
       </c>
       <c r="E54" t="str">
-        <v>Entertainment</v>
+        <v/>
       </c>
       <c r="F54" t="str">
-        <v/>
+        <v>Reserve Savings</v>
       </c>
       <c r="G54" t="str">
-        <v>BookMyShow</v>
+        <v>Reserve Savings</v>
       </c>
       <c r="H54" t="str">
-        <v>Weekend entertainment</v>
+        <v>Move money to savings goal bucket</v>
       </c>
       <c r="I54" t="str">
-        <v>Card</v>
+        <v>Transfer</v>
       </c>
       <c r="J54" t="str">
-        <v>fun,weekend</v>
+        <v>savings, goal</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B55" t="str">
-        <v>Expense</v>
+        <v>Transfer</v>
       </c>
       <c r="C55">
-        <v>1140</v>
+        <v>8400</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-01-21</v>
+        <v>2025-12-27</v>
       </c>
       <c r="E55" t="str">
-        <v>Health</v>
+        <v/>
       </c>
       <c r="F55" t="str">
-        <v/>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="G55" t="str">
-        <v>Apollo Pharmacy</v>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="H55" t="str">
-        <v>Health and pharmacy</v>
+        <v>Credit card bill payment</v>
       </c>
       <c r="I55" t="str">
-        <v>UPI</v>
+        <v>Transfer</v>
       </c>
       <c r="J55" t="str">
-        <v>health,care</v>
+        <v>credit-card, payment</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Axis Salary Account</v>
+        <v>Pocket Cash</v>
       </c>
       <c r="B56" t="str">
-        <v>Transfer</v>
+        <v>Expense</v>
       </c>
       <c r="C56">
-        <v>20000</v>
+        <v>550</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-01-06</v>
+        <v>2025-12-09</v>
       </c>
       <c r="E56" t="str">
-        <v/>
+        <v>Transport</v>
       </c>
       <c r="F56" t="str">
-        <v>Emergency Savings</v>
+        <v/>
       </c>
       <c r="G56" t="str">
-        <v>Self Transfer</v>
+        <v>Metro Card</v>
       </c>
       <c r="H56" t="str">
-        <v>Move to emergency fund</v>
+        <v>Local commute top-up</v>
       </c>
       <c r="I56" t="str">
-        <v>Bank Transfer</v>
+        <v>Cash</v>
       </c>
       <c r="J56" t="str">
-        <v>saving,transfer</v>
+        <v>transport, commute</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Axis Salary Account</v>
+        <v>Pocket Cash</v>
       </c>
       <c r="B57" t="str">
-        <v>Transfer</v>
+        <v>Expense</v>
       </c>
       <c r="C57">
-        <v>5000</v>
+        <v>700</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-01-23</v>
+        <v>2025-12-14</v>
       </c>
       <c r="E57" t="str">
-        <v/>
+        <v>Transport</v>
       </c>
       <c r="F57" t="str">
-        <v>Cash Wallet</v>
+        <v/>
       </c>
       <c r="G57" t="str">
-        <v>Self Transfer</v>
+        <v>Ride Now</v>
       </c>
       <c r="H57" t="str">
-        <v>Save for Japan trip</v>
+        <v>Auto and cab rides</v>
       </c>
       <c r="I57" t="str">
-        <v>Bank Transfer</v>
+        <v>Cash</v>
       </c>
       <c r="J57" t="str">
-        <v>goal,travel</v>
+        <v>transport, commute</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Axis Salary Account</v>
+        <v>Pocket Cash</v>
       </c>
       <c r="B58" t="str">
         <v>Expense</v>
       </c>
       <c r="C58">
-        <v>2500</v>
+        <v>600</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-01-07</v>
+        <v>2025-12-21</v>
       </c>
       <c r="E58" t="str">
         <v>Transport</v>
@@ -3193,734 +3184,734 @@
         <v/>
       </c>
       <c r="G58" t="str">
-        <v>ATM Withdrawal</v>
+        <v>Metro Card</v>
       </c>
       <c r="H58" t="str">
-        <v>Cash for local expenses</v>
+        <v>Local commute top-up</v>
       </c>
       <c r="I58" t="str">
-        <v>ATM</v>
+        <v>Cash</v>
       </c>
       <c r="J58" t="str">
-        <v>cash,atm</v>
+        <v>transport, commute</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Axis Salary Account</v>
+        <v>Pocket Cash</v>
       </c>
       <c r="B59" t="str">
         <v>Expense</v>
       </c>
       <c r="C59">
-        <v>7400</v>
+        <v>650</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-01-25</v>
+        <v>2025-12-28</v>
       </c>
       <c r="E59" t="str">
-        <v>Shopping</v>
+        <v>Transport</v>
       </c>
       <c r="F59" t="str">
         <v/>
       </c>
       <c r="G59" t="str">
-        <v>HDFC Card Payment</v>
+        <v>Ride Now</v>
       </c>
       <c r="H59" t="str">
-        <v>Credit card bill payment</v>
+        <v>Auto and cab rides</v>
       </c>
       <c r="I59" t="str">
-        <v>Net Banking</v>
+        <v>Cash</v>
       </c>
       <c r="J59" t="str">
-        <v>card,bill</v>
+        <v>transport, commute</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Axis Salary Account</v>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="B60" t="str">
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="C60">
-        <v>104000</v>
+        <v>2014</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-01-31</v>
+        <v>2025-12-10</v>
       </c>
       <c r="E60" t="str">
-        <v>Salary</v>
+        <v>Dining</v>
       </c>
       <c r="F60" t="str">
         <v/>
       </c>
       <c r="G60" t="str">
-        <v>Employer Payroll</v>
+        <v>Swiggy</v>
       </c>
       <c r="H60" t="str">
-        <v>Monthly salary credit</v>
+        <v>Weekend takeout</v>
       </c>
       <c r="I60" t="str">
-        <v>Bank Transfer</v>
+        <v>Credit Card</v>
       </c>
       <c r="J60" t="str">
-        <v>salary,monthly</v>
+        <v>food, lifestyle</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Axis Salary Account</v>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="B61" t="str">
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="C61">
-        <v>14400</v>
+        <v>1643</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-02-17</v>
+        <v>2025-12-18</v>
       </c>
       <c r="E61" t="str">
-        <v>Freelance</v>
+        <v>Dining</v>
       </c>
       <c r="F61" t="str">
         <v/>
       </c>
       <c r="G61" t="str">
-        <v>Consulting Client</v>
+        <v>Blue Oven</v>
       </c>
       <c r="H61" t="str">
-        <v>Side project payout</v>
+        <v>Casual dinner with friends</v>
       </c>
       <c r="I61" t="str">
-        <v>Bank Transfer</v>
+        <v>Credit Card</v>
       </c>
       <c r="J61" t="str">
-        <v>freelance,side-income</v>
+        <v>food, lifestyle</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Axis Salary Account</v>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="B62" t="str">
         <v>Expense</v>
       </c>
       <c r="C62">
-        <v>28000</v>
+        <v>1643</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-02-02</v>
+        <v>2025-12-24</v>
       </c>
       <c r="E62" t="str">
-        <v>Rent</v>
+        <v>Dining</v>
       </c>
       <c r="F62" t="str">
         <v/>
       </c>
       <c r="G62" t="str">
-        <v>Sunrise Residency</v>
+        <v>Late Night Bowl</v>
       </c>
       <c r="H62" t="str">
-        <v>Monthly apartment rent</v>
+        <v>Quick dining order</v>
       </c>
       <c r="I62" t="str">
-        <v>UPI</v>
+        <v>Credit Card</v>
       </c>
       <c r="J62" t="str">
-        <v>housing,fixed</v>
+        <v>food, lifestyle</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Axis Salary Account</v>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="B63" t="str">
         <v>Expense</v>
       </c>
       <c r="C63">
-        <v>3560</v>
+        <v>3248</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-02-03</v>
+        <v>2025-12-11</v>
       </c>
       <c r="E63" t="str">
-        <v>Utilities</v>
+        <v>Shopping</v>
       </c>
       <c r="F63" t="str">
         <v/>
       </c>
       <c r="G63" t="str">
-        <v>BESCOM</v>
+        <v>UrbanCart</v>
       </c>
       <c r="H63" t="str">
-        <v>Electricity bill</v>
+        <v>Lifestyle and home essentials</v>
       </c>
       <c r="I63" t="str">
-        <v>Net Banking</v>
+        <v>Credit Card</v>
       </c>
       <c r="J63" t="str">
-        <v>utilities,bill</v>
+        <v>shopping</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Axis Salary Account</v>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="B64" t="str">
         <v>Expense</v>
       </c>
       <c r="C64">
-        <v>1199</v>
+        <v>2552</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-02-04</v>
+        <v>2025-12-23</v>
       </c>
       <c r="E64" t="str">
-        <v>Utilities</v>
+        <v>Shopping</v>
       </c>
       <c r="F64" t="str">
         <v/>
       </c>
       <c r="G64" t="str">
-        <v>Airtel Fiber</v>
+        <v>Daily Mart</v>
       </c>
       <c r="H64" t="str">
-        <v>Internet payment</v>
+        <v>Personal care and extras</v>
       </c>
       <c r="I64" t="str">
-        <v>UPI</v>
+        <v>Credit Card</v>
       </c>
       <c r="J64" t="str">
-        <v>internet,utility</v>
+        <v>shopping</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Axis Salary Account</v>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="B65" t="str">
         <v>Expense</v>
       </c>
       <c r="C65">
-        <v>5700</v>
+        <v>868</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-02-05</v>
+        <v>2025-12-13</v>
       </c>
       <c r="E65" t="str">
-        <v>Food</v>
+        <v>Entertainment</v>
       </c>
       <c r="F65" t="str">
         <v/>
       </c>
       <c r="G65" t="str">
-        <v>BigBasket</v>
+        <v>Netflix + Prime</v>
       </c>
       <c r="H65" t="str">
-        <v>Groceries stock-up</v>
+        <v>Digital subscription stack</v>
       </c>
       <c r="I65" t="str">
-        <v>Card</v>
+        <v>Credit Card</v>
       </c>
       <c r="J65" t="str">
-        <v>groceries,home</v>
+        <v>subscription, entertainment</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Axis Salary Account</v>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="B66" t="str">
         <v>Expense</v>
       </c>
       <c r="C66">
-        <v>3040</v>
+        <v>629</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-02-11</v>
+        <v>2025-12-20</v>
       </c>
       <c r="E66" t="str">
-        <v>Food</v>
+        <v>Entertainment</v>
       </c>
       <c r="F66" t="str">
         <v/>
       </c>
       <c r="G66" t="str">
-        <v>Swiggy</v>
+        <v>Spotify + YouTube</v>
       </c>
       <c r="H66" t="str">
-        <v>Dining and delivery</v>
+        <v>Digital subscription stack</v>
       </c>
       <c r="I66" t="str">
-        <v>UPI</v>
+        <v>Credit Card</v>
       </c>
       <c r="J66" t="str">
-        <v>food,lifestyle</v>
+        <v>subscription, entertainment</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Axis Salary Account</v>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="B67" t="str">
         <v>Expense</v>
       </c>
       <c r="C67">
-        <v>3820</v>
+        <v>1800</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-02-08</v>
+        <v>2025-12-15</v>
       </c>
       <c r="E67" t="str">
-        <v>Transport</v>
+        <v>Health</v>
       </c>
       <c r="F67" t="str">
         <v/>
       </c>
       <c r="G67" t="str">
-        <v>Uber</v>
+        <v>CarePlus Clinic</v>
       </c>
       <c r="H67" t="str">
-        <v>Office commute</v>
+        <v>Preventive checkup and medicines</v>
       </c>
       <c r="I67" t="str">
-        <v>UPI</v>
+        <v>Credit Card</v>
       </c>
       <c r="J67" t="str">
-        <v>transport,commute</v>
+        <v>health</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B68" t="str">
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="C68">
-        <v>2600</v>
+        <v>72000</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-02-13</v>
+        <v>2026-01-01</v>
       </c>
       <c r="E68" t="str">
-        <v>Shopping</v>
+        <v>Salary</v>
       </c>
       <c r="F68" t="str">
         <v/>
       </c>
       <c r="G68" t="str">
-        <v>Amazon</v>
+        <v>Amiti Labs Payroll</v>
       </c>
       <c r="H68" t="str">
-        <v>Shopping order</v>
+        <v>Monthly salary credit</v>
       </c>
       <c r="I68" t="str">
-        <v>Card</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="J68" t="str">
-        <v>shopping,online</v>
+        <v>salary, fixed-income</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B69" t="str">
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="C69">
-        <v>2220</v>
+        <v>9500</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-02-19</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E69" t="str">
-        <v>Entertainment</v>
+        <v>Freelance</v>
       </c>
       <c r="F69" t="str">
         <v/>
       </c>
       <c r="G69" t="str">
-        <v>BookMyShow</v>
+        <v>Client Retainer</v>
       </c>
       <c r="H69" t="str">
-        <v>Weekend entertainment</v>
+        <v>Side project invoice settlement</v>
       </c>
       <c r="I69" t="str">
-        <v>Card</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="J69" t="str">
-        <v>fun,weekend</v>
+        <v>freelance, variable-income</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B70" t="str">
         <v>Expense</v>
       </c>
       <c r="C70">
-        <v>1220</v>
+        <v>18500</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-02-21</v>
+        <v>2026-01-03</v>
       </c>
       <c r="E70" t="str">
-        <v>Health</v>
+        <v>Rent</v>
       </c>
       <c r="F70" t="str">
         <v/>
       </c>
       <c r="G70" t="str">
-        <v>Apollo Pharmacy</v>
+        <v>Skyline Residency</v>
       </c>
       <c r="H70" t="str">
-        <v>Health and pharmacy</v>
+        <v>Monthly apartment rent</v>
       </c>
       <c r="I70" t="str">
-        <v>UPI</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="J70" t="str">
-        <v>health,care</v>
+        <v>housing, fixed</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B71" t="str">
-        <v>Transfer</v>
+        <v>Expense</v>
       </c>
       <c r="C71">
-        <v>21000</v>
+        <v>3500</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-02-06</v>
+        <v>2026-01-05</v>
       </c>
       <c r="E71" t="str">
-        <v/>
+        <v>Utilities</v>
       </c>
       <c r="F71" t="str">
-        <v>Emergency Savings</v>
+        <v/>
       </c>
       <c r="G71" t="str">
-        <v>Self Transfer</v>
+        <v>City Power + FiberNet</v>
       </c>
       <c r="H71" t="str">
-        <v>Move to emergency fund</v>
+        <v>Electricity and internet bundle</v>
       </c>
       <c r="I71" t="str">
-        <v>Bank Transfer</v>
+        <v>Auto Debit</v>
       </c>
       <c r="J71" t="str">
-        <v>saving,transfer</v>
+        <v>utilities, fixed</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B72" t="str">
-        <v>Transfer</v>
+        <v>Expense</v>
       </c>
       <c r="C72">
-        <v>5500</v>
+        <v>2080</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-02-23</v>
+        <v>2026-01-07</v>
       </c>
       <c r="E72" t="str">
-        <v/>
+        <v>Groceries</v>
       </c>
       <c r="F72" t="str">
-        <v>Cash Wallet</v>
+        <v/>
       </c>
       <c r="G72" t="str">
-        <v>Self Transfer</v>
+        <v>Fresh Basket</v>
       </c>
       <c r="H72" t="str">
-        <v>Save for Japan trip</v>
+        <v>Weekly household groceries</v>
       </c>
       <c r="I72" t="str">
-        <v>Bank Transfer</v>
+        <v>UPI</v>
       </c>
       <c r="J72" t="str">
-        <v>goal,travel</v>
+        <v>groceries, household</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B73" t="str">
         <v>Expense</v>
       </c>
       <c r="C73">
-        <v>2500</v>
+        <v>1920</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-02-07</v>
+        <v>2026-01-12</v>
       </c>
       <c r="E73" t="str">
-        <v>Transport</v>
+        <v>Groceries</v>
       </c>
       <c r="F73" t="str">
         <v/>
       </c>
       <c r="G73" t="str">
-        <v>ATM Withdrawal</v>
+        <v>Green Cart</v>
       </c>
       <c r="H73" t="str">
-        <v>Cash for local expenses</v>
+        <v>Produce and dairy run</v>
       </c>
       <c r="I73" t="str">
-        <v>ATM</v>
+        <v>Debit Card</v>
       </c>
       <c r="J73" t="str">
-        <v>cash,atm</v>
+        <v>groceries, household</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B74" t="str">
         <v>Expense</v>
       </c>
       <c r="C74">
-        <v>7800</v>
+        <v>2160</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-02-25</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E74" t="str">
-        <v>Shopping</v>
+        <v>Groceries</v>
       </c>
       <c r="F74" t="str">
         <v/>
       </c>
       <c r="G74" t="str">
-        <v>HDFC Card Payment</v>
+        <v>Fresh Basket</v>
       </c>
       <c r="H74" t="str">
-        <v>Credit card bill payment</v>
+        <v>Weekly household groceries</v>
       </c>
       <c r="I74" t="str">
-        <v>Net Banking</v>
+        <v>UPI</v>
       </c>
       <c r="J74" t="str">
-        <v>card,bill</v>
+        <v>groceries, household</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B75" t="str">
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="C75">
-        <v>105500</v>
+        <v>1840</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-02-28</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E75" t="str">
-        <v>Salary</v>
+        <v>Groceries</v>
       </c>
       <c r="F75" t="str">
         <v/>
       </c>
       <c r="G75" t="str">
-        <v>Employer Payroll</v>
+        <v>Green Cart</v>
       </c>
       <c r="H75" t="str">
-        <v>Monthly salary credit</v>
+        <v>Produce and dairy run</v>
       </c>
       <c r="I75" t="str">
-        <v>Bank Transfer</v>
+        <v>Debit Card</v>
       </c>
       <c r="J75" t="str">
-        <v>salary,monthly</v>
+        <v>groceries, household</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B76" t="str">
-        <v>Expense</v>
+        <v>Transfer</v>
       </c>
       <c r="C76">
-        <v>28000</v>
+        <v>1800</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-03-02</v>
+        <v>2026-01-06</v>
       </c>
       <c r="E76" t="str">
-        <v>Rent</v>
+        <v/>
       </c>
       <c r="F76" t="str">
-        <v/>
+        <v>Pocket Cash</v>
       </c>
       <c r="G76" t="str">
-        <v>Sunrise Residency</v>
+        <v>Pocket Cash</v>
       </c>
       <c r="H76" t="str">
-        <v>Monthly apartment rent</v>
+        <v>Monthly cash wallet top-up</v>
       </c>
       <c r="I76" t="str">
-        <v>UPI</v>
+        <v>Transfer</v>
       </c>
       <c r="J76" t="str">
-        <v>housing,fixed</v>
+        <v>cash</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B77" t="str">
-        <v>Expense</v>
+        <v>Transfer</v>
       </c>
       <c r="C77">
-        <v>3650</v>
+        <v>8000</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-03-03</v>
+        <v>2026-01-08</v>
       </c>
       <c r="E77" t="str">
-        <v>Utilities</v>
+        <v/>
       </c>
       <c r="F77" t="str">
-        <v/>
+        <v>Reserve Savings</v>
       </c>
       <c r="G77" t="str">
-        <v>BESCOM</v>
+        <v>Reserve Savings</v>
       </c>
       <c r="H77" t="str">
-        <v>Electricity bill</v>
+        <v>Move money to savings goal bucket</v>
       </c>
       <c r="I77" t="str">
-        <v>Net Banking</v>
+        <v>Transfer</v>
       </c>
       <c r="J77" t="str">
-        <v>utilities,bill</v>
+        <v>savings, goal</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B78" t="str">
-        <v>Expense</v>
+        <v>Transfer</v>
       </c>
       <c r="C78">
-        <v>1199</v>
+        <v>7900</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-03-04</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E78" t="str">
-        <v>Utilities</v>
+        <v/>
       </c>
       <c r="F78" t="str">
-        <v/>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="G78" t="str">
-        <v>Airtel Fiber</v>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="H78" t="str">
-        <v>Internet payment</v>
+        <v>Credit card bill payment</v>
       </c>
       <c r="I78" t="str">
-        <v>UPI</v>
+        <v>Transfer</v>
       </c>
       <c r="J78" t="str">
-        <v>internet,utility</v>
+        <v>credit-card, payment</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Axis Salary Account</v>
+        <v>Pocket Cash</v>
       </c>
       <c r="B79" t="str">
         <v>Expense</v>
       </c>
       <c r="C79">
-        <v>6900</v>
+        <v>594</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-03-05</v>
+        <v>2026-01-09</v>
       </c>
       <c r="E79" t="str">
-        <v>Food</v>
+        <v>Transport</v>
       </c>
       <c r="F79" t="str">
         <v/>
       </c>
       <c r="G79" t="str">
-        <v>BigBasket</v>
+        <v>Metro Card</v>
       </c>
       <c r="H79" t="str">
-        <v>Groceries stock-up</v>
+        <v>Local commute top-up</v>
       </c>
       <c r="I79" t="str">
-        <v>Card</v>
+        <v>Cash</v>
       </c>
       <c r="J79" t="str">
-        <v>groceries,home</v>
+        <v>transport, commute</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Axis Salary Account</v>
+        <v>Pocket Cash</v>
       </c>
       <c r="B80" t="str">
         <v>Expense</v>
       </c>
       <c r="C80">
-        <v>5200</v>
+        <v>756</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-03-11</v>
+        <v>2026-01-14</v>
       </c>
       <c r="E80" t="str">
-        <v>Food</v>
+        <v>Transport</v>
       </c>
       <c r="F80" t="str">
         <v/>
       </c>
       <c r="G80" t="str">
-        <v>Swiggy</v>
+        <v>Ride Now</v>
       </c>
       <c r="H80" t="str">
-        <v>Dining and delivery</v>
+        <v>Auto and cab rides</v>
       </c>
       <c r="I80" t="str">
-        <v>UPI</v>
+        <v>Cash</v>
       </c>
       <c r="J80" t="str">
-        <v>food,lifestyle</v>
+        <v>transport, commute</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Axis Salary Account</v>
+        <v>Pocket Cash</v>
       </c>
       <c r="B81" t="str">
         <v>Expense</v>
       </c>
       <c r="C81">
-        <v>4000</v>
+        <v>648</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-03-08</v>
+        <v>2026-01-21</v>
       </c>
       <c r="E81" t="str">
         <v>Transport</v>
@@ -3929,341 +3920,1749 @@
         <v/>
       </c>
       <c r="G81" t="str">
-        <v>Uber</v>
+        <v>Metro Card</v>
       </c>
       <c r="H81" t="str">
-        <v>Office commute</v>
+        <v>Local commute top-up</v>
       </c>
       <c r="I81" t="str">
-        <v>UPI</v>
+        <v>Cash</v>
       </c>
       <c r="J81" t="str">
-        <v>transport,commute</v>
+        <v>transport, commute</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>Pocket Cash</v>
       </c>
       <c r="B82" t="str">
         <v>Expense</v>
       </c>
       <c r="C82">
-        <v>8800</v>
+        <v>702</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-03-13</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E82" t="str">
-        <v>Shopping</v>
+        <v>Transport</v>
       </c>
       <c r="F82" t="str">
         <v/>
       </c>
       <c r="G82" t="str">
-        <v>Amazon</v>
+        <v>Ride Now</v>
       </c>
       <c r="H82" t="str">
-        <v>Shopping order</v>
+        <v>Auto and cab rides</v>
       </c>
       <c r="I82" t="str">
-        <v>Card</v>
+        <v>Cash</v>
       </c>
       <c r="J82" t="str">
-        <v>shopping,online</v>
+        <v>transport, commute</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="B83" t="str">
         <v>Expense</v>
       </c>
       <c r="C83">
-        <v>2350</v>
+        <v>1710</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-03-19</v>
+        <v>2026-01-10</v>
       </c>
       <c r="E83" t="str">
-        <v>Entertainment</v>
+        <v>Dining</v>
       </c>
       <c r="F83" t="str">
         <v/>
       </c>
       <c r="G83" t="str">
-        <v>BookMyShow</v>
+        <v>Swiggy</v>
       </c>
       <c r="H83" t="str">
-        <v>Weekend entertainment</v>
+        <v>Weekend takeout</v>
       </c>
       <c r="I83" t="str">
-        <v>Card</v>
+        <v>Credit Card</v>
       </c>
       <c r="J83" t="str">
-        <v>fun,weekend</v>
+        <v>food, lifestyle</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Axis Salary Account</v>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="B84" t="str">
         <v>Expense</v>
       </c>
       <c r="C84">
-        <v>1300</v>
+        <v>1395</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-03-21</v>
+        <v>2026-01-18</v>
       </c>
       <c r="E84" t="str">
-        <v>Health</v>
+        <v>Dining</v>
       </c>
       <c r="F84" t="str">
         <v/>
       </c>
       <c r="G84" t="str">
-        <v>Apollo Pharmacy</v>
+        <v>Blue Oven</v>
       </c>
       <c r="H84" t="str">
-        <v>Health and pharmacy</v>
+        <v>Casual dinner with friends</v>
       </c>
       <c r="I84" t="str">
-        <v>UPI</v>
+        <v>Credit Card</v>
       </c>
       <c r="J84" t="str">
-        <v>health,care</v>
+        <v>food, lifestyle</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Axis Salary Account</v>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="B85" t="str">
-        <v>Transfer</v>
+        <v>Expense</v>
       </c>
       <c r="C85">
-        <v>22000</v>
+        <v>1395</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-03-06</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E85" t="str">
-        <v/>
+        <v>Dining</v>
       </c>
       <c r="F85" t="str">
-        <v>Emergency Savings</v>
+        <v/>
       </c>
       <c r="G85" t="str">
-        <v>Self Transfer</v>
+        <v>Late Night Bowl</v>
       </c>
       <c r="H85" t="str">
-        <v>Move to emergency fund</v>
+        <v>Quick dining order</v>
       </c>
       <c r="I85" t="str">
-        <v>Bank Transfer</v>
+        <v>Credit Card</v>
       </c>
       <c r="J85" t="str">
-        <v>saving,transfer</v>
+        <v>food, lifestyle</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Axis Salary Account</v>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="B86" t="str">
-        <v>Transfer</v>
+        <v>Expense</v>
       </c>
       <c r="C86">
-        <v>6000</v>
+        <v>2856</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-03-23</v>
+        <v>2026-01-11</v>
       </c>
       <c r="E86" t="str">
-        <v/>
+        <v>Shopping</v>
       </c>
       <c r="F86" t="str">
-        <v>Cash Wallet</v>
+        <v/>
       </c>
       <c r="G86" t="str">
-        <v>Self Transfer</v>
+        <v>UrbanCart</v>
       </c>
       <c r="H86" t="str">
-        <v>Save for Japan trip</v>
+        <v>Lifestyle and home essentials</v>
       </c>
       <c r="I86" t="str">
-        <v>Bank Transfer</v>
+        <v>Credit Card</v>
       </c>
       <c r="J86" t="str">
-        <v>goal,travel</v>
+        <v>shopping</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Axis Salary Account</v>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="B87" t="str">
         <v>Expense</v>
       </c>
       <c r="C87">
-        <v>2500</v>
+        <v>2244</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-03-07</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E87" t="str">
-        <v>Transport</v>
+        <v>Shopping</v>
       </c>
       <c r="F87" t="str">
         <v/>
       </c>
       <c r="G87" t="str">
-        <v>ATM Withdrawal</v>
+        <v>Daily Mart</v>
       </c>
       <c r="H87" t="str">
-        <v>Cash for local expenses</v>
+        <v>Personal care and extras</v>
       </c>
       <c r="I87" t="str">
-        <v>ATM</v>
+        <v>Credit Card</v>
       </c>
       <c r="J87" t="str">
-        <v>cash,atm</v>
+        <v>shopping</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Axis Salary Account</v>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="B88" t="str">
         <v>Expense</v>
       </c>
       <c r="C88">
-        <v>8200</v>
+        <v>868</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-03-25</v>
+        <v>2026-01-13</v>
       </c>
       <c r="E88" t="str">
-        <v>Shopping</v>
+        <v>Entertainment</v>
       </c>
       <c r="F88" t="str">
         <v/>
       </c>
       <c r="G88" t="str">
-        <v>HDFC Card Payment</v>
+        <v>Netflix + Prime</v>
       </c>
       <c r="H88" t="str">
-        <v>Credit card bill payment</v>
+        <v>Digital subscription stack</v>
       </c>
       <c r="I88" t="str">
-        <v>Net Banking</v>
+        <v>Credit Card</v>
       </c>
       <c r="J88" t="str">
-        <v>card,bill</v>
+        <v>subscription, entertainment</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Axis Salary Account</v>
+        <v>Atlas Credit Card</v>
       </c>
       <c r="B89" t="str">
         <v>Expense</v>
       </c>
       <c r="C89">
-        <v>7600</v>
+        <v>629</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-03-26</v>
+        <v>2026-01-20</v>
       </c>
       <c r="E89" t="str">
-        <v>Food</v>
+        <v>Entertainment</v>
       </c>
       <c r="F89" t="str">
         <v/>
       </c>
       <c r="G89" t="str">
-        <v>Nature Basket</v>
+        <v>Spotify + YouTube</v>
       </c>
       <c r="H89" t="str">
-        <v>Premium groceries for guests</v>
+        <v>Digital subscription stack</v>
       </c>
       <c r="I89" t="str">
-        <v>Card</v>
+        <v>Credit Card</v>
       </c>
       <c r="J89" t="str">
-        <v>food,hosting</v>
+        <v>subscription, entertainment</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>HDFC Rewards Card</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B90" t="str">
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="C90">
-        <v>6400</v>
+        <v>72000</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-03-27</v>
+        <v>2026-02-01</v>
       </c>
       <c r="E90" t="str">
-        <v>Shopping</v>
+        <v>Salary</v>
       </c>
       <c r="F90" t="str">
         <v/>
       </c>
       <c r="G90" t="str">
-        <v>Myntra</v>
+        <v>Amiti Labs Payroll</v>
       </c>
       <c r="H90" t="str">
-        <v>Festive wardrobe refresh</v>
+        <v>Monthly salary credit</v>
       </c>
       <c r="I90" t="str">
-        <v>Card</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="J90" t="str">
-        <v>shopping,fashion</v>
+        <v>salary, fixed-income</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Axis Salary Account</v>
+        <v>Horizon Checking</v>
       </c>
       <c r="B91" t="str">
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="C91">
-        <v>22000</v>
+        <v>19000</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-03-28</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E91" t="str">
-        <v>Bonus</v>
+        <v>Rent</v>
       </c>
       <c r="F91" t="str">
         <v/>
       </c>
       <c r="G91" t="str">
-        <v>Performance Bonus</v>
+        <v>Skyline Residency</v>
       </c>
       <c r="H91" t="str">
-        <v>Quarter-end bonus</v>
+        <v>Monthly apartment rent</v>
       </c>
       <c r="I91" t="str">
         <v>Bank Transfer</v>
       </c>
       <c r="J91" t="str">
-        <v>bonus,income</v>
+        <v>housing, fixed</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>Horizon Checking</v>
+      </c>
+      <c r="B92" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C92">
+        <v>3400</v>
+      </c>
+      <c r="D92" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="E92" t="str">
+        <v>Utilities</v>
+      </c>
+      <c r="F92" t="str">
+        <v/>
+      </c>
+      <c r="G92" t="str">
+        <v>City Power + FiberNet</v>
+      </c>
+      <c r="H92" t="str">
+        <v>Electricity and internet bundle</v>
+      </c>
+      <c r="I92" t="str">
+        <v>Auto Debit</v>
+      </c>
+      <c r="J92" t="str">
+        <v>utilities, fixed</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>Horizon Checking</v>
+      </c>
+      <c r="B93" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C93">
+        <v>2028</v>
+      </c>
+      <c r="D93" t="str">
+        <v>2026-02-07</v>
+      </c>
+      <c r="E93" t="str">
+        <v>Groceries</v>
+      </c>
+      <c r="F93" t="str">
+        <v/>
+      </c>
+      <c r="G93" t="str">
+        <v>Fresh Basket</v>
+      </c>
+      <c r="H93" t="str">
+        <v>Weekly household groceries</v>
+      </c>
+      <c r="I93" t="str">
+        <v>UPI</v>
+      </c>
+      <c r="J93" t="str">
+        <v>groceries, household</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>Horizon Checking</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C94">
+        <v>1872</v>
+      </c>
+      <c r="D94" t="str">
+        <v>2026-02-12</v>
+      </c>
+      <c r="E94" t="str">
+        <v>Groceries</v>
+      </c>
+      <c r="F94" t="str">
+        <v/>
+      </c>
+      <c r="G94" t="str">
+        <v>Green Cart</v>
+      </c>
+      <c r="H94" t="str">
+        <v>Produce and dairy run</v>
+      </c>
+      <c r="I94" t="str">
+        <v>Debit Card</v>
+      </c>
+      <c r="J94" t="str">
+        <v>groceries, household</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>Horizon Checking</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C95">
+        <v>2106</v>
+      </c>
+      <c r="D95" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="E95" t="str">
+        <v>Groceries</v>
+      </c>
+      <c r="F95" t="str">
+        <v/>
+      </c>
+      <c r="G95" t="str">
+        <v>Fresh Basket</v>
+      </c>
+      <c r="H95" t="str">
+        <v>Weekly household groceries</v>
+      </c>
+      <c r="I95" t="str">
+        <v>UPI</v>
+      </c>
+      <c r="J95" t="str">
+        <v>groceries, household</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>Horizon Checking</v>
+      </c>
+      <c r="B96" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C96">
+        <v>1794</v>
+      </c>
+      <c r="D96" t="str">
+        <v>2026-02-26</v>
+      </c>
+      <c r="E96" t="str">
+        <v>Groceries</v>
+      </c>
+      <c r="F96" t="str">
+        <v/>
+      </c>
+      <c r="G96" t="str">
+        <v>Green Cart</v>
+      </c>
+      <c r="H96" t="str">
+        <v>Produce and dairy run</v>
+      </c>
+      <c r="I96" t="str">
+        <v>Debit Card</v>
+      </c>
+      <c r="J96" t="str">
+        <v>groceries, household</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>Horizon Checking</v>
+      </c>
+      <c r="B97" t="str">
+        <v>Transfer</v>
+      </c>
+      <c r="C97">
+        <v>1800</v>
+      </c>
+      <c r="D97" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
+        <v>Pocket Cash</v>
+      </c>
+      <c r="G97" t="str">
+        <v>Pocket Cash</v>
+      </c>
+      <c r="H97" t="str">
+        <v>Monthly cash wallet top-up</v>
+      </c>
+      <c r="I97" t="str">
+        <v>Transfer</v>
+      </c>
+      <c r="J97" t="str">
+        <v>cash</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>Horizon Checking</v>
+      </c>
+      <c r="B98" t="str">
+        <v>Transfer</v>
+      </c>
+      <c r="C98">
+        <v>8500</v>
+      </c>
+      <c r="D98" t="str">
+        <v>2026-02-08</v>
+      </c>
+      <c r="E98" t="str">
+        <v/>
+      </c>
+      <c r="F98" t="str">
+        <v>Reserve Savings</v>
+      </c>
+      <c r="G98" t="str">
+        <v>Reserve Savings</v>
+      </c>
+      <c r="H98" t="str">
+        <v>Move money to savings goal bucket</v>
+      </c>
+      <c r="I98" t="str">
+        <v>Transfer</v>
+      </c>
+      <c r="J98" t="str">
+        <v>savings, goal</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>Horizon Checking</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Transfer</v>
+      </c>
+      <c r="C99">
+        <v>7600</v>
+      </c>
+      <c r="D99" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="E99" t="str">
+        <v/>
+      </c>
+      <c r="F99" t="str">
+        <v>Atlas Credit Card</v>
+      </c>
+      <c r="G99" t="str">
+        <v>Atlas Credit Card</v>
+      </c>
+      <c r="H99" t="str">
+        <v>Credit card bill payment</v>
+      </c>
+      <c r="I99" t="str">
+        <v>Transfer</v>
+      </c>
+      <c r="J99" t="str">
+        <v>credit-card, payment</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>Pocket Cash</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C100">
+        <v>572</v>
+      </c>
+      <c r="D100" t="str">
+        <v>2026-02-09</v>
+      </c>
+      <c r="E100" t="str">
+        <v>Transport</v>
+      </c>
+      <c r="F100" t="str">
+        <v/>
+      </c>
+      <c r="G100" t="str">
+        <v>Metro Card</v>
+      </c>
+      <c r="H100" t="str">
+        <v>Local commute top-up</v>
+      </c>
+      <c r="I100" t="str">
+        <v>Cash</v>
+      </c>
+      <c r="J100" t="str">
+        <v>transport, commute</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>Pocket Cash</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C101">
+        <v>728</v>
+      </c>
+      <c r="D101" t="str">
+        <v>2026-02-14</v>
+      </c>
+      <c r="E101" t="str">
+        <v>Transport</v>
+      </c>
+      <c r="F101" t="str">
+        <v/>
+      </c>
+      <c r="G101" t="str">
+        <v>Ride Now</v>
+      </c>
+      <c r="H101" t="str">
+        <v>Auto and cab rides</v>
+      </c>
+      <c r="I101" t="str">
+        <v>Cash</v>
+      </c>
+      <c r="J101" t="str">
+        <v>transport, commute</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>Pocket Cash</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C102">
+        <v>624</v>
+      </c>
+      <c r="D102" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="E102" t="str">
+        <v>Transport</v>
+      </c>
+      <c r="F102" t="str">
+        <v/>
+      </c>
+      <c r="G102" t="str">
+        <v>Metro Card</v>
+      </c>
+      <c r="H102" t="str">
+        <v>Local commute top-up</v>
+      </c>
+      <c r="I102" t="str">
+        <v>Cash</v>
+      </c>
+      <c r="J102" t="str">
+        <v>transport, commute</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Pocket Cash</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C103">
+        <v>676</v>
+      </c>
+      <c r="D103" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="E103" t="str">
+        <v>Transport</v>
+      </c>
+      <c r="F103" t="str">
+        <v/>
+      </c>
+      <c r="G103" t="str">
+        <v>Ride Now</v>
+      </c>
+      <c r="H103" t="str">
+        <v>Auto and cab rides</v>
+      </c>
+      <c r="I103" t="str">
+        <v>Cash</v>
+      </c>
+      <c r="J103" t="str">
+        <v>transport, commute</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Atlas Credit Card</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C104">
+        <v>1596</v>
+      </c>
+      <c r="D104" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="E104" t="str">
+        <v>Dining</v>
+      </c>
+      <c r="F104" t="str">
+        <v/>
+      </c>
+      <c r="G104" t="str">
+        <v>Swiggy</v>
+      </c>
+      <c r="H104" t="str">
+        <v>Weekend takeout</v>
+      </c>
+      <c r="I104" t="str">
+        <v>Credit Card</v>
+      </c>
+      <c r="J104" t="str">
+        <v>food, lifestyle</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>Atlas Credit Card</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C105">
+        <v>1302</v>
+      </c>
+      <c r="D105" t="str">
+        <v>2026-02-18</v>
+      </c>
+      <c r="E105" t="str">
+        <v>Dining</v>
+      </c>
+      <c r="F105" t="str">
+        <v/>
+      </c>
+      <c r="G105" t="str">
+        <v>Blue Oven</v>
+      </c>
+      <c r="H105" t="str">
+        <v>Casual dinner with friends</v>
+      </c>
+      <c r="I105" t="str">
+        <v>Credit Card</v>
+      </c>
+      <c r="J105" t="str">
+        <v>food, lifestyle</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>Atlas Credit Card</v>
+      </c>
+      <c r="B106" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C106">
+        <v>1302</v>
+      </c>
+      <c r="D106" t="str">
+        <v>2026-02-24</v>
+      </c>
+      <c r="E106" t="str">
+        <v>Dining</v>
+      </c>
+      <c r="F106" t="str">
+        <v/>
+      </c>
+      <c r="G106" t="str">
+        <v>Late Night Bowl</v>
+      </c>
+      <c r="H106" t="str">
+        <v>Quick dining order</v>
+      </c>
+      <c r="I106" t="str">
+        <v>Credit Card</v>
+      </c>
+      <c r="J106" t="str">
+        <v>food, lifestyle</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>Atlas Credit Card</v>
+      </c>
+      <c r="B107" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C107">
+        <v>2128</v>
+      </c>
+      <c r="D107" t="str">
+        <v>2026-02-11</v>
+      </c>
+      <c r="E107" t="str">
+        <v>Shopping</v>
+      </c>
+      <c r="F107" t="str">
+        <v/>
+      </c>
+      <c r="G107" t="str">
+        <v>UrbanCart</v>
+      </c>
+      <c r="H107" t="str">
+        <v>Lifestyle and home essentials</v>
+      </c>
+      <c r="I107" t="str">
+        <v>Credit Card</v>
+      </c>
+      <c r="J107" t="str">
+        <v>shopping</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>Atlas Credit Card</v>
+      </c>
+      <c r="B108" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C108">
+        <v>1672</v>
+      </c>
+      <c r="D108" t="str">
+        <v>2026-02-23</v>
+      </c>
+      <c r="E108" t="str">
+        <v>Shopping</v>
+      </c>
+      <c r="F108" t="str">
+        <v/>
+      </c>
+      <c r="G108" t="str">
+        <v>Daily Mart</v>
+      </c>
+      <c r="H108" t="str">
+        <v>Personal care and extras</v>
+      </c>
+      <c r="I108" t="str">
+        <v>Credit Card</v>
+      </c>
+      <c r="J108" t="str">
+        <v>shopping</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>Atlas Credit Card</v>
+      </c>
+      <c r="B109" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C109">
+        <v>695</v>
+      </c>
+      <c r="D109" t="str">
+        <v>2026-02-13</v>
+      </c>
+      <c r="E109" t="str">
+        <v>Entertainment</v>
+      </c>
+      <c r="F109" t="str">
+        <v/>
+      </c>
+      <c r="G109" t="str">
+        <v>Netflix + Prime</v>
+      </c>
+      <c r="H109" t="str">
+        <v>Digital subscription stack</v>
+      </c>
+      <c r="I109" t="str">
+        <v>Credit Card</v>
+      </c>
+      <c r="J109" t="str">
+        <v>subscription, entertainment</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>Atlas Credit Card</v>
+      </c>
+      <c r="B110" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C110">
+        <v>503</v>
+      </c>
+      <c r="D110" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="E110" t="str">
+        <v>Entertainment</v>
+      </c>
+      <c r="F110" t="str">
+        <v/>
+      </c>
+      <c r="G110" t="str">
+        <v>Spotify + YouTube</v>
+      </c>
+      <c r="H110" t="str">
+        <v>Digital subscription stack</v>
+      </c>
+      <c r="I110" t="str">
+        <v>Credit Card</v>
+      </c>
+      <c r="J110" t="str">
+        <v>subscription, entertainment</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>Horizon Checking</v>
+      </c>
+      <c r="B111" t="str">
+        <v>Income</v>
+      </c>
+      <c r="C111">
+        <v>72000</v>
+      </c>
+      <c r="D111" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="E111" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="F111" t="str">
+        <v/>
+      </c>
+      <c r="G111" t="str">
+        <v>Amiti Labs Payroll</v>
+      </c>
+      <c r="H111" t="str">
+        <v>Monthly salary credit</v>
+      </c>
+      <c r="I111" t="str">
+        <v>Bank Transfer</v>
+      </c>
+      <c r="J111" t="str">
+        <v>salary, fixed-income</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>Horizon Checking</v>
+      </c>
+      <c r="B112" t="str">
+        <v>Income</v>
+      </c>
+      <c r="C112">
+        <v>18500</v>
+      </c>
+      <c r="D112" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E112" t="str">
+        <v>Freelance</v>
+      </c>
+      <c r="F112" t="str">
+        <v/>
+      </c>
+      <c r="G112" t="str">
+        <v>Client Retainer</v>
+      </c>
+      <c r="H112" t="str">
+        <v>Side project invoice settlement</v>
+      </c>
+      <c r="I112" t="str">
+        <v>Bank Transfer</v>
+      </c>
+      <c r="J112" t="str">
+        <v>freelance, variable-income</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>Horizon Checking</v>
+      </c>
+      <c r="B113" t="str">
+        <v>Income</v>
+      </c>
+      <c r="C113">
+        <v>24000</v>
+      </c>
+      <c r="D113" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="E113" t="str">
+        <v>Bonus</v>
+      </c>
+      <c r="F113" t="str">
+        <v/>
+      </c>
+      <c r="G113" t="str">
+        <v>Annual Performance Bonus</v>
+      </c>
+      <c r="H113" t="str">
+        <v>Quarter-end reward payout</v>
+      </c>
+      <c r="I113" t="str">
+        <v>Bank Transfer</v>
+      </c>
+      <c r="J113" t="str">
+        <v>bonus, career</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>Horizon Checking</v>
+      </c>
+      <c r="B114" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C114">
+        <v>19500</v>
+      </c>
+      <c r="D114" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E114" t="str">
+        <v>Rent</v>
+      </c>
+      <c r="F114" t="str">
+        <v/>
+      </c>
+      <c r="G114" t="str">
+        <v>Skyline Residency</v>
+      </c>
+      <c r="H114" t="str">
+        <v>Monthly apartment rent</v>
+      </c>
+      <c r="I114" t="str">
+        <v>Bank Transfer</v>
+      </c>
+      <c r="J114" t="str">
+        <v>housing, fixed</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>Horizon Checking</v>
+      </c>
+      <c r="B115" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C115">
+        <v>3600</v>
+      </c>
+      <c r="D115" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="E115" t="str">
+        <v>Utilities</v>
+      </c>
+      <c r="F115" t="str">
+        <v/>
+      </c>
+      <c r="G115" t="str">
+        <v>City Power + FiberNet</v>
+      </c>
+      <c r="H115" t="str">
+        <v>Electricity and internet bundle</v>
+      </c>
+      <c r="I115" t="str">
+        <v>Auto Debit</v>
+      </c>
+      <c r="J115" t="str">
+        <v>utilities, fixed</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>Horizon Checking</v>
+      </c>
+      <c r="B116" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C116">
+        <v>1976</v>
+      </c>
+      <c r="D116" t="str">
+        <v>2026-03-07</v>
+      </c>
+      <c r="E116" t="str">
+        <v>Groceries</v>
+      </c>
+      <c r="F116" t="str">
+        <v/>
+      </c>
+      <c r="G116" t="str">
+        <v>Fresh Basket</v>
+      </c>
+      <c r="H116" t="str">
+        <v>Weekly household groceries</v>
+      </c>
+      <c r="I116" t="str">
+        <v>UPI</v>
+      </c>
+      <c r="J116" t="str">
+        <v>groceries, household</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>Horizon Checking</v>
+      </c>
+      <c r="B117" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C117">
+        <v>1824</v>
+      </c>
+      <c r="D117" t="str">
+        <v>2026-03-12</v>
+      </c>
+      <c r="E117" t="str">
+        <v>Groceries</v>
+      </c>
+      <c r="F117" t="str">
+        <v/>
+      </c>
+      <c r="G117" t="str">
+        <v>Green Cart</v>
+      </c>
+      <c r="H117" t="str">
+        <v>Produce and dairy run</v>
+      </c>
+      <c r="I117" t="str">
+        <v>Debit Card</v>
+      </c>
+      <c r="J117" t="str">
+        <v>groceries, household</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>Horizon Checking</v>
+      </c>
+      <c r="B118" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C118">
+        <v>2052</v>
+      </c>
+      <c r="D118" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="E118" t="str">
+        <v>Groceries</v>
+      </c>
+      <c r="F118" t="str">
+        <v/>
+      </c>
+      <c r="G118" t="str">
+        <v>Fresh Basket</v>
+      </c>
+      <c r="H118" t="str">
+        <v>Weekly household groceries</v>
+      </c>
+      <c r="I118" t="str">
+        <v>UPI</v>
+      </c>
+      <c r="J118" t="str">
+        <v>groceries, household</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>Horizon Checking</v>
+      </c>
+      <c r="B119" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C119">
+        <v>1748</v>
+      </c>
+      <c r="D119" t="str">
+        <v>2026-03-26</v>
+      </c>
+      <c r="E119" t="str">
+        <v>Groceries</v>
+      </c>
+      <c r="F119" t="str">
+        <v/>
+      </c>
+      <c r="G119" t="str">
+        <v>Green Cart</v>
+      </c>
+      <c r="H119" t="str">
+        <v>Produce and dairy run</v>
+      </c>
+      <c r="I119" t="str">
+        <v>Debit Card</v>
+      </c>
+      <c r="J119" t="str">
+        <v>groceries, household</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>Horizon Checking</v>
+      </c>
+      <c r="B120" t="str">
+        <v>Transfer</v>
+      </c>
+      <c r="C120">
+        <v>1700</v>
+      </c>
+      <c r="D120" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="E120" t="str">
+        <v/>
+      </c>
+      <c r="F120" t="str">
+        <v>Pocket Cash</v>
+      </c>
+      <c r="G120" t="str">
+        <v>Pocket Cash</v>
+      </c>
+      <c r="H120" t="str">
+        <v>Monthly cash wallet top-up</v>
+      </c>
+      <c r="I120" t="str">
+        <v>Transfer</v>
+      </c>
+      <c r="J120" t="str">
+        <v>cash</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>Horizon Checking</v>
+      </c>
+      <c r="B121" t="str">
+        <v>Transfer</v>
+      </c>
+      <c r="C121">
+        <v>9500</v>
+      </c>
+      <c r="D121" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="E121" t="str">
+        <v/>
+      </c>
+      <c r="F121" t="str">
+        <v>Reserve Savings</v>
+      </c>
+      <c r="G121" t="str">
+        <v>Reserve Savings</v>
+      </c>
+      <c r="H121" t="str">
+        <v>Move money to savings goal bucket</v>
+      </c>
+      <c r="I121" t="str">
+        <v>Transfer</v>
+      </c>
+      <c r="J121" t="str">
+        <v>savings, goal</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>Horizon Checking</v>
+      </c>
+      <c r="B122" t="str">
+        <v>Transfer</v>
+      </c>
+      <c r="C122">
+        <v>10800</v>
+      </c>
+      <c r="D122" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="E122" t="str">
+        <v/>
+      </c>
+      <c r="F122" t="str">
+        <v>Atlas Credit Card</v>
+      </c>
+      <c r="G122" t="str">
+        <v>Atlas Credit Card</v>
+      </c>
+      <c r="H122" t="str">
+        <v>Credit card bill payment</v>
+      </c>
+      <c r="I122" t="str">
+        <v>Transfer</v>
+      </c>
+      <c r="J122" t="str">
+        <v>credit-card, payment</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>Pocket Cash</v>
+      </c>
+      <c r="B123" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C123">
+        <v>506</v>
+      </c>
+      <c r="D123" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="E123" t="str">
+        <v>Transport</v>
+      </c>
+      <c r="F123" t="str">
+        <v/>
+      </c>
+      <c r="G123" t="str">
+        <v>Metro Card</v>
+      </c>
+      <c r="H123" t="str">
+        <v>Local commute top-up</v>
+      </c>
+      <c r="I123" t="str">
+        <v>Cash</v>
+      </c>
+      <c r="J123" t="str">
+        <v>transport, commute</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>Pocket Cash</v>
+      </c>
+      <c r="B124" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C124">
+        <v>644</v>
+      </c>
+      <c r="D124" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="E124" t="str">
+        <v>Transport</v>
+      </c>
+      <c r="F124" t="str">
+        <v/>
+      </c>
+      <c r="G124" t="str">
+        <v>Ride Now</v>
+      </c>
+      <c r="H124" t="str">
+        <v>Auto and cab rides</v>
+      </c>
+      <c r="I124" t="str">
+        <v>Cash</v>
+      </c>
+      <c r="J124" t="str">
+        <v>transport, commute</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>Pocket Cash</v>
+      </c>
+      <c r="B125" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C125">
+        <v>552</v>
+      </c>
+      <c r="D125" t="str">
+        <v>2026-03-21</v>
+      </c>
+      <c r="E125" t="str">
+        <v>Transport</v>
+      </c>
+      <c r="F125" t="str">
+        <v/>
+      </c>
+      <c r="G125" t="str">
+        <v>Metro Card</v>
+      </c>
+      <c r="H125" t="str">
+        <v>Local commute top-up</v>
+      </c>
+      <c r="I125" t="str">
+        <v>Cash</v>
+      </c>
+      <c r="J125" t="str">
+        <v>transport, commute</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>Pocket Cash</v>
+      </c>
+      <c r="B126" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C126">
+        <v>598</v>
+      </c>
+      <c r="D126" t="str">
+        <v>2026-03-28</v>
+      </c>
+      <c r="E126" t="str">
+        <v>Transport</v>
+      </c>
+      <c r="F126" t="str">
+        <v/>
+      </c>
+      <c r="G126" t="str">
+        <v>Ride Now</v>
+      </c>
+      <c r="H126" t="str">
+        <v>Auto and cab rides</v>
+      </c>
+      <c r="I126" t="str">
+        <v>Cash</v>
+      </c>
+      <c r="J126" t="str">
+        <v>transport, commute</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>Atlas Credit Card</v>
+      </c>
+      <c r="B127" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C127">
+        <v>988</v>
+      </c>
+      <c r="D127" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="E127" t="str">
+        <v>Dining</v>
+      </c>
+      <c r="F127" t="str">
+        <v/>
+      </c>
+      <c r="G127" t="str">
+        <v>Swiggy</v>
+      </c>
+      <c r="H127" t="str">
+        <v>Weekend takeout</v>
+      </c>
+      <c r="I127" t="str">
+        <v>Credit Card</v>
+      </c>
+      <c r="J127" t="str">
+        <v>food, lifestyle</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>Atlas Credit Card</v>
+      </c>
+      <c r="B128" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C128">
+        <v>806</v>
+      </c>
+      <c r="D128" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="E128" t="str">
+        <v>Dining</v>
+      </c>
+      <c r="F128" t="str">
+        <v/>
+      </c>
+      <c r="G128" t="str">
+        <v>Blue Oven</v>
+      </c>
+      <c r="H128" t="str">
+        <v>Casual dinner with friends</v>
+      </c>
+      <c r="I128" t="str">
+        <v>Credit Card</v>
+      </c>
+      <c r="J128" t="str">
+        <v>food, lifestyle</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>Atlas Credit Card</v>
+      </c>
+      <c r="B129" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C129">
+        <v>806</v>
+      </c>
+      <c r="D129" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="E129" t="str">
+        <v>Dining</v>
+      </c>
+      <c r="F129" t="str">
+        <v/>
+      </c>
+      <c r="G129" t="str">
+        <v>Late Night Bowl</v>
+      </c>
+      <c r="H129" t="str">
+        <v>Quick dining order</v>
+      </c>
+      <c r="I129" t="str">
+        <v>Credit Card</v>
+      </c>
+      <c r="J129" t="str">
+        <v>food, lifestyle</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>Atlas Credit Card</v>
+      </c>
+      <c r="B130" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C130">
+        <v>1288</v>
+      </c>
+      <c r="D130" t="str">
+        <v>2026-03-11</v>
+      </c>
+      <c r="E130" t="str">
+        <v>Shopping</v>
+      </c>
+      <c r="F130" t="str">
+        <v/>
+      </c>
+      <c r="G130" t="str">
+        <v>UrbanCart</v>
+      </c>
+      <c r="H130" t="str">
+        <v>Lifestyle and home essentials</v>
+      </c>
+      <c r="I130" t="str">
+        <v>Credit Card</v>
+      </c>
+      <c r="J130" t="str">
+        <v>shopping</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>Atlas Credit Card</v>
+      </c>
+      <c r="B131" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C131">
+        <v>1012</v>
+      </c>
+      <c r="D131" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="E131" t="str">
+        <v>Shopping</v>
+      </c>
+      <c r="F131" t="str">
+        <v/>
+      </c>
+      <c r="G131" t="str">
+        <v>Daily Mart</v>
+      </c>
+      <c r="H131" t="str">
+        <v>Personal care and extras</v>
+      </c>
+      <c r="I131" t="str">
+        <v>Credit Card</v>
+      </c>
+      <c r="J131" t="str">
+        <v>shopping</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>Atlas Credit Card</v>
+      </c>
+      <c r="B132" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C132">
+        <v>695</v>
+      </c>
+      <c r="D132" t="str">
+        <v>2026-03-13</v>
+      </c>
+      <c r="E132" t="str">
+        <v>Entertainment</v>
+      </c>
+      <c r="F132" t="str">
+        <v/>
+      </c>
+      <c r="G132" t="str">
+        <v>Netflix + Prime</v>
+      </c>
+      <c r="H132" t="str">
+        <v>Digital subscription stack</v>
+      </c>
+      <c r="I132" t="str">
+        <v>Credit Card</v>
+      </c>
+      <c r="J132" t="str">
+        <v>subscription, entertainment</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>Atlas Credit Card</v>
+      </c>
+      <c r="B133" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C133">
+        <v>503</v>
+      </c>
+      <c r="D133" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="E133" t="str">
+        <v>Entertainment</v>
+      </c>
+      <c r="F133" t="str">
+        <v/>
+      </c>
+      <c r="G133" t="str">
+        <v>Spotify + YouTube</v>
+      </c>
+      <c r="H133" t="str">
+        <v>Digital subscription stack</v>
+      </c>
+      <c r="I133" t="str">
+        <v>Credit Card</v>
+      </c>
+      <c r="J133" t="str">
+        <v>subscription, entertainment</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>Atlas Credit Card</v>
+      </c>
+      <c r="B134" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C134">
+        <v>1500</v>
+      </c>
+      <c r="D134" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="E134" t="str">
+        <v>Health</v>
+      </c>
+      <c r="F134" t="str">
+        <v/>
+      </c>
+      <c r="G134" t="str">
+        <v>CarePlus Clinic</v>
+      </c>
+      <c r="H134" t="str">
+        <v>Preventive checkup and medicines</v>
+      </c>
+      <c r="I134" t="str">
+        <v>Credit Card</v>
+      </c>
+      <c r="J134" t="str">
+        <v>health</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>Atlas Credit Card</v>
+      </c>
+      <c r="B135" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C135">
+        <v>21000</v>
+      </c>
+      <c r="D135" t="str">
+        <v>2026-03-12</v>
+      </c>
+      <c r="E135" t="str">
+        <v>Travel</v>
+      </c>
+      <c r="F135" t="str">
+        <v/>
+      </c>
+      <c r="G135" t="str">
+        <v>SkyHop Holidays</v>
+      </c>
+      <c r="H135" t="str">
+        <v>Advance booking for upcoming international trip</v>
+      </c>
+      <c r="I135" t="str">
+        <v>Credit Card</v>
+      </c>
+      <c r="J135" t="str">
+        <v>travel, planned</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J91"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J135"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/sample-onboarding-import.xlsx
+++ b/public/sample-onboarding-import.xlsx
@@ -7,6 +7,8 @@
     <sheet name="Budgets" sheetId="2" r:id="rId2"/>
     <sheet name="Goals" sheetId="3" r:id="rId3"/>
     <sheet name="Transactions" sheetId="4" r:id="rId4"/>
+    <sheet name="Recurring" sheetId="5" r:id="rId5"/>
+    <sheet name="Rules" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -5665,4 +5667,331 @@
     <ignoredError numberStoredAsText="1" sqref="A1:J135"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K5"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>title</v>
+      </c>
+      <c r="B1" t="str">
+        <v>type</v>
+      </c>
+      <c r="C1" t="str">
+        <v>amount</v>
+      </c>
+      <c r="D1" t="str">
+        <v>category</v>
+      </c>
+      <c r="E1" t="str">
+        <v>accountName</v>
+      </c>
+      <c r="F1" t="str">
+        <v>frequency</v>
+      </c>
+      <c r="G1" t="str">
+        <v>startDate</v>
+      </c>
+      <c r="H1" t="str">
+        <v>endDate</v>
+      </c>
+      <c r="I1" t="str">
+        <v>nextRunDate</v>
+      </c>
+      <c r="J1" t="str">
+        <v>autoCreateTransaction</v>
+      </c>
+      <c r="K1" t="str">
+        <v>isPaused</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Monthly Salary</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Income</v>
+      </c>
+      <c r="C2">
+        <v>72000</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Horizon Checking</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Monthly</v>
+      </c>
+      <c r="G2" t="str">
+        <v>2025-10-01</v>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="J2" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="K2" t="str">
+        <v>FALSE</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Apartment Rent</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C3">
+        <v>19500</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Rent</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Horizon Checking</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Monthly</v>
+      </c>
+      <c r="G3" t="str">
+        <v>2025-10-03</v>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="J3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="K3" t="str">
+        <v>FALSE</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Subscription Stack</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C4">
+        <v>1198</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Entertainment</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Atlas Credit Card</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Monthly</v>
+      </c>
+      <c r="G4" t="str">
+        <v>2025-10-13</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>2026-03-13</v>
+      </c>
+      <c r="J4" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="K4" t="str">
+        <v>FALSE</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Emergency Fund Transfer</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="C5">
+        <v>9500</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Others</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Horizon Checking</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Monthly</v>
+      </c>
+      <c r="G5" t="str">
+        <v>2025-10-08</v>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="J5" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="K5" t="str">
+        <v>FALSE</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:K5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H5"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>name</v>
+      </c>
+      <c r="B1" t="str">
+        <v>conditionField</v>
+      </c>
+      <c r="C1" t="str">
+        <v>conditionOperator</v>
+      </c>
+      <c r="D1" t="str">
+        <v>conditionValue</v>
+      </c>
+      <c r="E1" t="str">
+        <v>actionType</v>
+      </c>
+      <c r="F1" t="str">
+        <v>actionValue</v>
+      </c>
+      <c r="G1" t="str">
+        <v>priority</v>
+      </c>
+      <c r="H1" t="str">
+        <v>isActive</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Auto-tag food delivery</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Merchant</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Contains</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Swiggy</v>
+      </c>
+      <c r="E2" t="str">
+        <v>AddTag</v>
+      </c>
+      <c r="F2" t="str">
+        <v>food-delivery</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2" t="str">
+        <v>TRUE</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Map Fresh Basket to Groceries</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Merchant</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Contains</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Fresh Basket</v>
+      </c>
+      <c r="E3" t="str">
+        <v>SetCategory</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Groceries</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3" t="str">
+        <v>TRUE</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Flag large travel charges</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Category</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Equals</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Travel</v>
+      </c>
+      <c r="E4" t="str">
+        <v>TriggerAlert</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Review large travel expense</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="H4" t="str">
+        <v>TRUE</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Tag subscriptions</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Merchant</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Contains</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Netflix</v>
+      </c>
+      <c r="E5" t="str">
+        <v>AddTag</v>
+      </c>
+      <c r="F5" t="str">
+        <v>subscription</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5" t="str">
+        <v>TRUE</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/public/sample-onboarding-import.xlsx
+++ b/public/sample-onboarding-import.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -417,6 +417,9 @@
       <c r="D1" t="str">
         <v>institutionName</v>
       </c>
+      <c r="E1" t="str">
+        <v>creditLimit</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -459,6 +462,9 @@
       <c r="D4" t="str">
         <v>Axis Bank</v>
       </c>
+      <c r="E4">
+        <v>90000</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -476,7 +482,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/public/sample-onboarding-import.xlsx
+++ b/public/sample-onboarding-import.xlsx
@@ -457,7 +457,7 @@
         <v>CreditCard</v>
       </c>
       <c r="C4">
-        <v>-4500</v>
+        <v>0</v>
       </c>
       <c r="D4" t="str">
         <v>Axis Bank</v>

--- a/public/sample-onboarding-import.xlsx
+++ b/public/sample-onboarding-import.xlsx
@@ -418,7 +418,7 @@
         <v>institutionName</v>
       </c>
       <c r="E1" t="str">
-        <v>creditLimit</v>
+        <v>limit</v>
       </c>
     </row>
     <row r="2">
@@ -433,6 +433,9 @@
       </c>
       <c r="D2" t="str">
         <v>HDFC Bank</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -448,6 +451,9 @@
       <c r="D3" t="str">
         <v>ICICI Bank</v>
       </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -478,6 +484,9 @@
       </c>
       <c r="D5" t="str">
         <v>Wallet</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/public/sample-onboarding-import.xlsx
+++ b/public/sample-onboarding-import.xlsx
@@ -480,7 +480,7 @@
         <v>CashWallet</v>
       </c>
       <c r="C5">
-        <v>2500</v>
+        <v>3600</v>
       </c>
       <c r="D5" t="str">
         <v>Wallet</v>
@@ -1653,7 +1653,7 @@
         <v>Transfer</v>
       </c>
       <c r="C10">
-        <v>1500</v>
+        <v>1700</v>
       </c>
       <c r="D10" t="str">
         <v>2025-10-06</v>
@@ -2325,7 +2325,7 @@
         <v>Transfer</v>
       </c>
       <c r="C31">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="D31" t="str">
         <v>2025-11-06</v>
@@ -3029,7 +3029,7 @@
         <v>Transfer</v>
       </c>
       <c r="C53">
-        <v>1800</v>
+        <v>1900</v>
       </c>
       <c r="D53" t="str">
         <v>2025-12-06</v>
@@ -3765,7 +3765,7 @@
         <v>Transfer</v>
       </c>
       <c r="C76">
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-06</v>
@@ -4437,7 +4437,7 @@
         <v>Transfer</v>
       </c>
       <c r="C97">
-        <v>1800</v>
+        <v>2100</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-06</v>
@@ -5173,7 +5173,7 @@
         <v>Transfer</v>
       </c>
       <c r="C120">
-        <v>1700</v>
+        <v>2250</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-06</v>
